--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -672,7 +672,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Storefront (www.musticker.com/kr) + Admin panel (admin-panel.musticker.com) | Playwright + TypeScript | Workbook v1.1 | 2026-10-14</t>
+          <t>Storefront (www.musticker.com/kr) + Admin panel (admin-panel.musticker.com) | Playwright + TypeScript | Workbook v1.2 | 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Filter the Test Cases tab by Area, Priority, App or Automation. Only the orange-headed columns (Result, Defect ID, Tester, Executed On, Tester Notes) are for you to fill in.</t>
+          <t>Filter the Test Cases tab by Area, Priority, App or Automation. Only the orange-headed columns (Result, Defect ID, Tester, Executed On, Tester Notes) are for you to fill in. The Legacy ID column (Y) shows the ID a case had before workbook v1.2 (MS-V2-### / MS-ADM-###); it is for reference only.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Automated order placement on static-1 (dev-static-1): its checkout shows a Cloudflare bot check before payment that rejects automated browsers. MS-ADM-001 starts from a pre-placed seed order until the dev team exempts test traffic.</t>
+          <t>Automated order placement on static-1 (dev-static-1): its checkout shows a Cloudflare bot check before payment that rejects automated browsers. MS-ADMO-001 starts from a pre-placed seed order until the dev team exempts test traffic.</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Automated order placement on static-1 (Cloudflare check before payment). Admin cases in CI: the verification code needs a person - dev-static-1 has a tester OTP endpoint that could remove this (see MS-ADM-002), not used by the suite yet.</t>
+          <t>Automated order placement on static-1 (Cloudflare check before payment). Admin cases in CI: the verification code needs a person - dev-static-1 has a tester OTP endpoint that could remove this (see MS-ADMA-001), not used by the suite yet.</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X176"/>
+  <dimension ref="A1:Y176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2434,6 +2434,7 @@
     <col width="12" customWidth="1" min="21" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="28" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2557,11 +2558,16 @@
           <t>Tester Notes</t>
         </is>
       </c>
+      <c r="Y1" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legacy ID</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-001</t>
+          <t>MS-NAV-001</t>
         </is>
       </c>
       <c r="B2" s="25" t="inlineStr">
@@ -2641,7 +2647,7 @@
       </c>
       <c r="P2" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-001 homepage loads with critical public content</t>
+          <t>MS-NAV-001 homepage loads with critical public content</t>
         </is>
       </c>
       <c r="Q2" s="25" t="inlineStr">
@@ -2666,11 +2672,16 @@
       <c r="V2" s="15" t="n"/>
       <c r="W2" s="15" t="n"/>
       <c r="X2" s="15" t="n"/>
+      <c r="Y2" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-001</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-002</t>
+          <t>MS-NAV-002</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -2749,7 +2760,7 @@
       </c>
       <c r="P3" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-002 header navigation opens each category product menu</t>
+          <t>MS-NAV-002 header navigation opens each category product menu</t>
         </is>
       </c>
       <c r="Q3" s="25" t="inlineStr">
@@ -2774,11 +2785,16 @@
       <c r="V3" s="15" t="n"/>
       <c r="W3" s="15" t="n"/>
       <c r="X3" s="15" t="n"/>
+      <c r="Y3" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-002</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-003</t>
+          <t>MS-NAV-003</t>
         </is>
       </c>
       <c r="B4" s="25" t="inlineStr">
@@ -2857,7 +2873,7 @@
       </c>
       <c r="P4" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-003 header search opens and finds hologram sticker content</t>
+          <t>MS-NAV-003 header search opens and finds hologram sticker content</t>
         </is>
       </c>
       <c r="Q4" s="25" t="inlineStr">
@@ -2882,11 +2898,16 @@
       <c r="V4" s="15" t="n"/>
       <c r="W4" s="15" t="n"/>
       <c r="X4" s="15" t="n"/>
+      <c r="Y4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-003</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-004</t>
+          <t>MS-NAV-004</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -2964,7 +2985,7 @@
       </c>
       <c r="P5" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-004 empty cart opens without broken state</t>
+          <t>MS-NAV-004 empty cart opens without broken state</t>
         </is>
       </c>
       <c r="Q5" s="25" t="inlineStr">
@@ -2989,11 +3010,16 @@
       <c r="V5" s="15" t="n"/>
       <c r="W5" s="15" t="n"/>
       <c r="X5" s="15" t="n"/>
+      <c r="Y5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-004</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-005</t>
+          <t>MS-NAV-005</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
@@ -3071,7 +3097,7 @@
       </c>
       <c r="P6" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-005 account icon routes anonymous users to authentication</t>
+          <t>MS-NAV-005 account icon routes anonymous users to authentication</t>
         </is>
       </c>
       <c r="Q6" s="25" t="inlineStr">
@@ -3096,11 +3122,16 @@
       <c r="V6" s="15" t="n"/>
       <c r="W6" s="15" t="n"/>
       <c r="X6" s="15" t="n"/>
+      <c r="Y6" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-005</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-020</t>
+          <t>MS-NAV-006</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -3178,7 +3209,7 @@
       </c>
       <c r="P7" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-020 footer legal and support links are reachable</t>
+          <t>MS-NAV-006 footer legal and support links are reachable</t>
         </is>
       </c>
       <c r="Q7" s="25" t="inlineStr">
@@ -3203,11 +3234,16 @@
       <c r="V7" s="15" t="n"/>
       <c r="W7" s="15" t="n"/>
       <c r="X7" s="15" t="n"/>
+      <c r="Y7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-020</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-021</t>
+          <t>MS-NAV-007</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
@@ -3285,7 +3321,7 @@
       </c>
       <c r="P8" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-021 Korean locale control is stable</t>
+          <t>MS-NAV-007 Korean locale control is stable</t>
         </is>
       </c>
       <c r="Q8" s="25" t="inlineStr">
@@ -3298,7 +3334,7 @@
       </c>
       <c r="S8" s="25" t="inlineStr">
         <is>
-          <t>Conditional pass: with no KR button the test still passes on header visibility. It does not check that a locale menu opens or that Korean stays selected. Tags differ from test-case.md (@regression there, @smoke in code). The KR .locale-toggle button is a known color-contrast defect (see MS-V2-106).</t>
+          <t>Conditional pass: with no KR button the test still passes on header visibility. It does not check that a locale menu opens or that Korean stays selected. Tags differ from test-case.md (@regression there, @smoke in code). The KR .locale-toggle button is a known color-contrast defect (see MS-UX-004).</t>
         </is>
       </c>
       <c r="T8" s="14" t="inlineStr">
@@ -3310,11 +3346,16 @@
       <c r="V8" s="15" t="n"/>
       <c r="W8" s="15" t="n"/>
       <c r="X8" s="15" t="n"/>
+      <c r="Y8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-021</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-022</t>
+          <t>MS-NAV-008</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
@@ -3395,7 +3436,7 @@
       </c>
       <c r="P9" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-022 home, search, cart, product config, and inquiry work on mobile</t>
+          <t>MS-NAV-008 home, search, cart, product config, and inquiry work on mobile</t>
         </is>
       </c>
       <c r="Q9" s="25" t="inlineStr">
@@ -3420,11 +3461,16 @@
       <c r="V9" s="15" t="n"/>
       <c r="W9" s="15" t="n"/>
       <c r="X9" s="15" t="n"/>
+      <c r="Y9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-022</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-006</t>
+          <t>MS-DSC-001</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
@@ -3503,7 +3549,7 @@
       </c>
       <c r="P10" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-006 sticker category lists expected product links</t>
+          <t>MS-DSC-001 sticker category lists expected product links</t>
         </is>
       </c>
       <c r="Q10" s="25" t="inlineStr">
@@ -3528,11 +3574,16 @@
       <c r="V10" s="15" t="n"/>
       <c r="W10" s="15" t="n"/>
       <c r="X10" s="15" t="n"/>
+      <c r="Y10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-006</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-007</t>
+          <t>MS-DSC-002</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
@@ -3611,7 +3662,7 @@
       </c>
       <c r="P11" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-007 roll sticker category lists expected product links</t>
+          <t>MS-DSC-002 roll sticker category lists expected product links</t>
         </is>
       </c>
       <c r="Q11" s="25" t="inlineStr">
@@ -3636,11 +3687,16 @@
       <c r="V11" s="15" t="n"/>
       <c r="W11" s="15" t="n"/>
       <c r="X11" s="15" t="n"/>
+      <c r="Y11" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-007</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-008</t>
+          <t>MS-DSC-003</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
@@ -3719,7 +3775,7 @@
       </c>
       <c r="P12" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-008 sheet sticker category lists expected product links</t>
+          <t>MS-DSC-003 sheet sticker category lists expected product links</t>
         </is>
       </c>
       <c r="Q12" s="25" t="inlineStr">
@@ -3744,11 +3800,16 @@
       <c r="V12" s="15" t="n"/>
       <c r="W12" s="15" t="n"/>
       <c r="X12" s="15" t="n"/>
+      <c r="Y12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-008</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-015</t>
+          <t>MS-DSC-004</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
@@ -3827,7 +3888,7 @@
       </c>
       <c r="P13" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-015 FAQ topics and accordions are usable</t>
+          <t>MS-DSC-004 FAQ topics and accordions are usable</t>
         </is>
       </c>
       <c r="Q13" s="25" t="inlineStr">
@@ -3852,11 +3913,16 @@
       <c r="V13" s="15" t="n"/>
       <c r="W13" s="15" t="n"/>
       <c r="X13" s="15" t="n"/>
+      <c r="Y13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-015</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-016</t>
+          <t>MS-DSC-005</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
@@ -3935,7 +4001,7 @@
       </c>
       <c r="P14" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-016 FAQ search filters and resets content</t>
+          <t>MS-DSC-005 FAQ search filters and resets content</t>
         </is>
       </c>
       <c r="Q14" s="25" t="inlineStr">
@@ -3960,11 +4026,16 @@
       <c r="V14" s="15" t="n"/>
       <c r="W14" s="15" t="n"/>
       <c r="X14" s="15" t="n"/>
+      <c r="Y14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-016</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-039</t>
+          <t>MS-DSC-006</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -4043,7 +4114,7 @@
       </c>
       <c r="P15" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-039 about page loads hero, sub-nav, stats, and CTAs</t>
+          <t>MS-DSC-006 about page loads hero, sub-nav, stats, and CTAs</t>
         </is>
       </c>
       <c r="Q15" s="25" t="inlineStr">
@@ -4068,11 +4139,16 @@
       <c r="V15" s="15" t="n"/>
       <c r="W15" s="15" t="n"/>
       <c r="X15" s="15" t="n"/>
+      <c r="Y15" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-039</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-040</t>
+          <t>MS-DSC-007</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
@@ -4151,7 +4227,7 @@
       </c>
       <c r="P16" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-040 catalog page renders without error: ./stickers/sticker-sheet</t>
+          <t>MS-DSC-007 catalog page renders without error: ./stickers/sticker-sheet</t>
         </is>
       </c>
       <c r="Q16" s="25" t="inlineStr">
@@ -4176,11 +4252,16 @@
       <c r="V16" s="15" t="n"/>
       <c r="W16" s="15" t="n"/>
       <c r="X16" s="15" t="n"/>
+      <c r="Y16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-040</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-009</t>
+          <t>MS-CFG-001</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
@@ -4260,7 +4341,7 @@
       </c>
       <c r="P17" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-009 die-cut sticker supports size and quantity selection</t>
+          <t>MS-CFG-001 die-cut sticker supports size and quantity selection</t>
         </is>
       </c>
       <c r="Q17" s="25" t="inlineStr">
@@ -4285,11 +4366,16 @@
       <c r="V17" s="15" t="n"/>
       <c r="W17" s="15" t="n"/>
       <c r="X17" s="15" t="n"/>
+      <c r="Y17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-009</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-010</t>
+          <t>MS-CFG-002</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
@@ -4369,7 +4455,7 @@
       </c>
       <c r="P18" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-010 die-cut roll sticker supports size and quantity selection</t>
+          <t>MS-CFG-002 die-cut roll sticker supports size and quantity selection</t>
         </is>
       </c>
       <c r="Q18" s="25" t="inlineStr">
@@ -4382,7 +4468,7 @@
       </c>
       <c r="S18" s="25" t="inlineStr">
         <is>
-          <t>test-case.md mentions a per-unit price. The code only checks that some won amount is visible. The progression check is loose, as in MS-V2-009.</t>
+          <t>test-case.md mentions a per-unit price. The code only checks that some won amount is visible. The progression check is loose, as in MS-CFG-001.</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
@@ -4394,11 +4480,16 @@
       <c r="V18" s="15" t="n"/>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="15" t="n"/>
+      <c r="Y18" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-010</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-011</t>
+          <t>MS-CFG-003</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
@@ -4480,7 +4571,7 @@
       </c>
       <c r="P19" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-011 die-cut sheet sticker supports material, sheet size, and quantity selection</t>
+          <t>MS-CFG-003 die-cut sheet sticker supports material, sheet size, and quantity selection</t>
         </is>
       </c>
       <c r="Q19" s="25" t="inlineStr">
@@ -4505,11 +4596,16 @@
       <c r="V19" s="15" t="n"/>
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="15" t="n"/>
+      <c r="Y19" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-011</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-012</t>
+          <t>MS-CFG-004</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
@@ -4589,7 +4685,7 @@
       </c>
       <c r="P20" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-012 custom size and quantity controls are reachable</t>
+          <t>MS-CFG-004 custom size and quantity controls are reachable</t>
         </is>
       </c>
       <c r="Q20" s="25" t="inlineStr">
@@ -4615,11 +4711,16 @@
       <c r="V20" s="15" t="n"/>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="15" t="n"/>
+      <c r="Y20" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-012</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-013</t>
+          <t>MS-CFG-005</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
@@ -4697,7 +4798,7 @@
       </c>
       <c r="P21" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-013 product trust and delivery promises are visible</t>
+          <t>MS-CFG-005 product trust and delivery promises are visible</t>
         </is>
       </c>
       <c r="Q21" s="25" t="inlineStr">
@@ -4722,11 +4823,16 @@
       <c r="V21" s="15" t="n"/>
       <c r="W21" s="15" t="n"/>
       <c r="X21" s="15" t="n"/>
+      <c r="Y21" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-013</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-014</t>
+          <t>MS-CFG-006</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
@@ -4805,7 +4911,7 @@
       </c>
       <c r="P22" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-014 product review carousel is usable</t>
+          <t>MS-CFG-006 product review carousel is usable</t>
         </is>
       </c>
       <c r="Q22" s="25" t="inlineStr">
@@ -4830,11 +4936,16 @@
       <c r="V22" s="15" t="n"/>
       <c r="W22" s="15" t="n"/>
       <c r="X22" s="15" t="n"/>
+      <c r="Y22" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-014</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-050</t>
+          <t>MS-CFG-007</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
@@ -4915,7 +5026,7 @@
       </c>
       <c r="P23" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-050 원형 판스티커 supports material, size, and quantity selection through to cart</t>
+          <t>MS-CFG-007 원형 판스티커 supports material, size, and quantity selection through to cart</t>
         </is>
       </c>
       <c r="Q23" s="25" t="inlineStr">
@@ -4940,11 +5051,16 @@
       <c r="V23" s="15" t="n"/>
       <c r="W23" s="15" t="n"/>
       <c r="X23" s="15" t="n"/>
+      <c r="Y23" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-050</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-051</t>
+          <t>MS-CFG-008</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
@@ -5023,7 +5139,7 @@
       </c>
       <c r="P24" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-051 circle sheet sticker: custom individual size recalculates the whole quantity price ladder</t>
+          <t>MS-CFG-008 circle sheet sticker: custom individual size recalculates the whole quantity price ladder</t>
         </is>
       </c>
       <c r="Q24" s="25" t="inlineStr">
@@ -5036,7 +5152,7 @@
       </c>
       <c r="S24" s="25" t="inlineStr">
         <is>
-          <t>The title and test-case.md say the whole price ladder is recalculated. The code only checks that a won amount is visible and 다음 단계 is enabled; it does not compare prices before and after. Field labels differ by environment: dev uses 가로/세로 placeholders, while production uses 너비/높이 captions with an "예: 30" placeholder. test-case.md says the helper retries the click once; it now retries up to 5 times. The fractional per-unit price (e.g. 8.582원) is accepted behavior, not a defect (MS-V2-059 withdrawn).</t>
+          <t>The title and test-case.md say the whole price ladder is recalculated. The code only checks that a won amount is visible and 다음 단계 is enabled; it does not compare prices before and after. Field labels differ by environment: dev uses 가로/세로 placeholders, while production uses 너비/높이 captions with an "예: 30" placeholder. test-case.md says the helper retries the click once; it now retries up to 5 times. The fractional per-unit price (e.g. 8.582원) is accepted behavior, not a defect (MS-CFG-016 withdrawn).</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
@@ -5048,11 +5164,16 @@
       <c r="V24" s="15" t="n"/>
       <c r="W24" s="15" t="n"/>
       <c r="X24" s="15" t="n"/>
+      <c r="Y24" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-051</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-052</t>
+          <t>MS-CFG-009</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
@@ -5129,7 +5250,7 @@
       </c>
       <c r="P25" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-052 circle sheet sticker: bulk quantity tiers surface a bigger discount than smaller tiers</t>
+          <t>MS-CFG-009 circle sheet sticker: bulk quantity tiers surface a bigger discount than smaller tiers</t>
         </is>
       </c>
       <c r="Q25" s="25" t="inlineStr">
@@ -5142,7 +5263,7 @@
       </c>
       <c r="S25" s="25" t="inlineStr">
         <is>
-          <t>Changed by 2026-10-14: sheet stickers now show a discount on every tier (10시트 reads -4% against a 6,900원 list price), so the old check that small tiers show no badge no longer holds. Badge values vary with the price table, so only their order is asserted. The die-cut and roll equivalents (MS-V2-064, MS-V2-065) still show no badge at 10개 and are unchanged.</t>
+          <t>Changed by 2026-10-14: sheet stickers now show a discount on every tier (10시트 reads -4% against a 6,900원 list price), so the old check that small tiers show no badge no longer holds. Badge values vary with the price table, so only their order is asserted. The die-cut and roll equivalents (MS-CFG-021, MS-CFG-022) still show no badge at 10개 and are unchanged.</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
@@ -5154,11 +5275,16 @@
       <c r="V25" s="15" t="n"/>
       <c r="W25" s="15" t="n"/>
       <c r="X25" s="15" t="n"/>
+      <c r="Y25" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-052</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-053</t>
+          <t>MS-CFG-010</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
@@ -5214,7 +5340,7 @@
       </c>
       <c r="K26" s="25" t="inlineStr">
         <is>
-          <t>the 어떻게 주문하시겠어요? chooser appears with the three ways to order (see MS-V2-050); after choosing the file, the dropzone shows "sample-design.png"; after 파일로 주문하기 the 장바구니 미리보기 (cart preview) drawer opens and contains a line item named "원형 판스티커" showing "수량: 10"; 장바구니 보기 leads to /kr/cart, where the 원형 판스티커 row shows either "이미지 추가" or "이미지 변경".</t>
+          <t>the 어떻게 주문하시겠어요? chooser appears with the three ways to order (see MS-CFG-007); after choosing the file, the dropzone shows "sample-design.png"; after 파일로 주문하기 the 장바구니 미리보기 (cart preview) drawer opens and contains a line item named "원형 판스티커" showing "수량: 10"; 장바구니 보기 leads to /kr/cart, where the 원형 판스티커 row shows either "이미지 추가" or "이미지 변경".</t>
         </is>
       </c>
       <c r="L26" s="13" t="inlineStr">
@@ -5239,7 +5365,7 @@
       </c>
       <c r="P26" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-053 circle sheet sticker: design upload modal accepts an order note and a design file before adding to cart</t>
+          <t>MS-CFG-010 circle sheet sticker: design upload modal accepts an order note and a design file before adding to cart</t>
         </is>
       </c>
       <c r="Q26" s="25" t="inlineStr">
@@ -5264,11 +5390,16 @@
       <c r="V26" s="15" t="n"/>
       <c r="W26" s="15" t="n"/>
       <c r="X26" s="15" t="n"/>
+      <c r="Y26" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-053</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-054</t>
+          <t>MS-CFG-011</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
@@ -5348,7 +5479,7 @@
       </c>
       <c r="P27" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-054 circle sheet sticker: editing material from the cart preview drawer recalculates the line price</t>
+          <t>MS-CFG-011 circle sheet sticker: editing material from the cart preview drawer recalculates the line price</t>
         </is>
       </c>
       <c r="Q27" s="25" t="inlineStr">
@@ -5373,11 +5504,16 @@
       <c r="V27" s="15" t="n"/>
       <c r="W27" s="15" t="n"/>
       <c r="X27" s="15" t="n"/>
+      <c r="Y27" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-054</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-055</t>
+          <t>MS-CFG-012</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
@@ -5456,7 +5592,7 @@
       </c>
       <c r="P28" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-055 circle sheet sticker: cart preview drawer "장바구니 보기" hands off to the full cart page with the item intact</t>
+          <t>MS-CFG-012 circle sheet sticker: cart preview drawer "장바구니 보기" hands off to the full cart page with the item intact</t>
         </is>
       </c>
       <c r="Q28" s="25" t="inlineStr">
@@ -5481,11 +5617,16 @@
       <c r="V28" s="15" t="n"/>
       <c r="W28" s="15" t="n"/>
       <c r="X28" s="15" t="n"/>
+      <c r="Y28" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-055</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-056</t>
+          <t>MS-CFG-013</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
@@ -5566,7 +5707,7 @@
       </c>
       <c r="P29" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-056 circle sheet sticker: full cart page "사이즈 변경" dialog exposes material + size only (no quantity), and updates price</t>
+          <t>MS-CFG-013 circle sheet sticker: full cart page "사이즈 변경" dialog exposes material + size only (no quantity), and updates price</t>
         </is>
       </c>
       <c r="Q29" s="25" t="inlineStr">
@@ -5579,7 +5720,7 @@
       </c>
       <c r="S29" s="25" t="inlineStr">
         <is>
-          <t>Having no quantity field in this dialog is intended, not a defect: quantity is edited only through the row select (MS-V2-057). test-case.md says the dialog shows 소재 and 개별 사이즈; the code does not check those labels, only that 수량 is absent. The default sheet material 무광 화이트 was labelled PVC 매트 until early October 2026. Uses 10시트, the smallest tier since early October 2026: 5시트 was dropped, and until the selector was fixed on 2026-10-14 asking for 5 silently picked 50시트.</t>
+          <t>Having no quantity field in this dialog is intended, not a defect: quantity is edited only through the row select (MS-CFG-014). test-case.md says the dialog shows 소재 and 개별 사이즈; the code does not check those labels, only that 수량 is absent. The default sheet material 무광 화이트 was labelled PVC 매트 until early October 2026. Uses 10시트, the smallest tier since early October 2026: 5시트 was dropped, and until the selector was fixed on 2026-10-14 asking for 5 silently picked 50시트.</t>
         </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
@@ -5591,11 +5732,16 @@
       <c r="V29" s="15" t="n"/>
       <c r="W29" s="15" t="n"/>
       <c r="X29" s="15" t="n"/>
+      <c r="Y29" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-056</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-057</t>
+          <t>MS-CFG-014</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
@@ -5676,7 +5822,7 @@
       </c>
       <c r="P30" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-057 circle sheet sticker: full cart page row quantity select updates price without a separate confirm step</t>
+          <t>MS-CFG-014 circle sheet sticker: full cart page row quantity select updates price without a separate confirm step</t>
         </is>
       </c>
       <c r="Q30" s="25" t="inlineStr">
@@ -5701,11 +5847,16 @@
       <c r="V30" s="15" t="n"/>
       <c r="W30" s="15" t="n"/>
       <c r="X30" s="15" t="n"/>
+      <c r="Y30" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-057</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-058</t>
+          <t>MS-CFG-015</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
@@ -5782,7 +5933,7 @@
       </c>
       <c r="P31" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-058 원형 판스티커 size-guide illustrations have meaningful, localized alt text</t>
+          <t>MS-CFG-015 원형 판스티커 size-guide illustrations have meaningful, localized alt text</t>
         </is>
       </c>
       <c r="Q31" s="25" t="inlineStr">
@@ -5807,11 +5958,16 @@
       <c r="V31" s="15" t="n"/>
       <c r="W31" s="15" t="n"/>
       <c r="X31" s="15" t="n"/>
+      <c r="Y31" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-058</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>MS-V2-059</t>
+          <t>MS-CFG-016</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
@@ -5911,11 +6067,16 @@
       <c r="V32" s="15" t="n"/>
       <c r="W32" s="15" t="n"/>
       <c r="X32" s="15" t="n"/>
+      <c r="Y32" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-059</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-060</t>
+          <t>MS-CFG-017</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
@@ -5995,7 +6156,7 @@
       </c>
       <c r="P33" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-060 홀로그램 스티커 supports size and quantity selection through to cart</t>
+          <t>MS-CFG-017 홀로그램 스티커 supports size and quantity selection through to cart</t>
         </is>
       </c>
       <c r="Q33" s="25" t="inlineStr">
@@ -6020,11 +6181,16 @@
       <c r="V33" s="15" t="n"/>
       <c r="W33" s="15" t="n"/>
       <c r="X33" s="15" t="n"/>
+      <c r="Y33" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-060</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="150" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-061</t>
+          <t>MS-CFG-018</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
@@ -6104,7 +6270,7 @@
       </c>
       <c r="P34" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-061 투명 롤 스티커 supports size and quantity selection through to cart</t>
+          <t>MS-CFG-018 투명 롤 스티커 supports size and quantity selection through to cart</t>
         </is>
       </c>
       <c r="Q34" s="25" t="inlineStr">
@@ -6129,11 +6295,16 @@
       <c r="V34" s="15" t="n"/>
       <c r="W34" s="15" t="n"/>
       <c r="X34" s="15" t="n"/>
+      <c r="Y34" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-061</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-062</t>
+          <t>MS-CFG-019</t>
         </is>
       </c>
       <c r="B35" s="25" t="inlineStr">
@@ -6212,7 +6383,7 @@
       </c>
       <c r="P35" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-062 circle sticker: custom individual size recalculates the price</t>
+          <t>MS-CFG-019 circle sticker: custom individual size recalculates the price</t>
         </is>
       </c>
       <c r="Q35" s="25" t="inlineStr">
@@ -6237,11 +6408,16 @@
       <c r="V35" s="15" t="n"/>
       <c r="W35" s="15" t="n"/>
       <c r="X35" s="15" t="n"/>
+      <c r="Y35" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-062</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-063</t>
+          <t>MS-CFG-020</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
@@ -6320,7 +6496,7 @@
       </c>
       <c r="P36" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-063 circle roll sticker: custom individual size recalculates the price</t>
+          <t>MS-CFG-020 circle roll sticker: custom individual size recalculates the price</t>
         </is>
       </c>
       <c r="Q36" s="25" t="inlineStr">
@@ -6345,11 +6521,16 @@
       <c r="V36" s="15" t="n"/>
       <c r="W36" s="15" t="n"/>
       <c r="X36" s="15" t="n"/>
+      <c r="Y36" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-063</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-064</t>
+          <t>MS-CFG-021</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
@@ -6428,7 +6609,7 @@
       </c>
       <c r="P37" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-064 circle sticker: bulk quantity tiers surface a discount that smaller tiers do not</t>
+          <t>MS-CFG-021 circle sticker: bulk quantity tiers surface a discount that smaller tiers do not</t>
         </is>
       </c>
       <c r="Q37" s="25" t="inlineStr">
@@ -6453,11 +6634,16 @@
       <c r="V37" s="15" t="n"/>
       <c r="W37" s="15" t="n"/>
       <c r="X37" s="15" t="n"/>
+      <c r="Y37" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-064</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="150" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-065</t>
+          <t>MS-CFG-022</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
@@ -6536,7 +6722,7 @@
       </c>
       <c r="P38" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-065 circle roll sticker: bulk quantity tiers surface a discount that smaller tiers do not</t>
+          <t>MS-CFG-022 circle roll sticker: bulk quantity tiers surface a discount that smaller tiers do not</t>
         </is>
       </c>
       <c r="Q38" s="25" t="inlineStr">
@@ -6561,11 +6747,16 @@
       <c r="V38" s="15" t="n"/>
       <c r="W38" s="15" t="n"/>
       <c r="X38" s="15" t="n"/>
+      <c r="Y38" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-065</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-070</t>
+          <t>MS-CFG-023</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
@@ -6647,7 +6838,7 @@
       </c>
       <c r="P39" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-070 custom sheet sticker supports material, sheet size, and quantity selection through to cart</t>
+          <t>MS-CFG-023 custom sheet sticker supports material, sheet size, and quantity selection through to cart</t>
         </is>
       </c>
       <c r="Q39" s="25" t="inlineStr">
@@ -6672,11 +6863,16 @@
       <c r="V39" s="15" t="n"/>
       <c r="W39" s="15" t="n"/>
       <c r="X39" s="15" t="n"/>
+      <c r="Y39" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-070</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="150" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-071</t>
+          <t>MS-CFG-024</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
@@ -6757,7 +6953,7 @@
       </c>
       <c r="P40" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-071 lettering sticker supports color, custom text, and quantity selection through to cart</t>
+          <t>MS-CFG-024 lettering sticker supports color, custom text, and quantity selection through to cart</t>
         </is>
       </c>
       <c r="Q40" s="25" t="inlineStr">
@@ -6782,11 +6978,16 @@
       <c r="V40" s="15" t="n"/>
       <c r="W40" s="15" t="n"/>
       <c r="X40" s="15" t="n"/>
+      <c r="Y40" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-071</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="150" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-072</t>
+          <t>MS-CFG-025</t>
         </is>
       </c>
       <c r="B41" s="25" t="inlineStr">
@@ -6867,7 +7068,7 @@
       </c>
       <c r="P41" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-072 full-color lettering (transfer) sticker supports color, size, and quantity selection through to cart</t>
+          <t>MS-CFG-025 full-color lettering (transfer) sticker supports color, size, and quantity selection through to cart</t>
         </is>
       </c>
       <c r="Q41" s="25" t="inlineStr">
@@ -6892,11 +7093,16 @@
       <c r="V41" s="15" t="n"/>
       <c r="W41" s="15" t="n"/>
       <c r="X41" s="15" t="n"/>
+      <c r="Y41" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-072</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="150" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-073</t>
+          <t>MS-SHT-001</t>
         </is>
       </c>
       <c r="B42" s="25" t="inlineStr">
@@ -6976,7 +7182,7 @@
       </c>
       <c r="P42" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-073 원형 판스티커 rejects a custom size that fits only one sticker per sheet</t>
+          <t>MS-SHT-001 원형 판스티커 rejects a custom size that fits only one sticker per sheet</t>
         </is>
       </c>
       <c r="Q42" s="25" t="inlineStr">
@@ -7001,11 +7207,16 @@
       <c r="V42" s="15" t="n"/>
       <c r="W42" s="15" t="n"/>
       <c r="X42" s="15" t="n"/>
+      <c r="Y42" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-073</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-074</t>
+          <t>MS-SHT-002</t>
         </is>
       </c>
       <c r="B43" s="25" t="inlineStr">
@@ -7084,7 +7295,7 @@
       </c>
       <c r="P43" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-074 circle sheet sticker: the 138x97 gate is exact</t>
+          <t>MS-SHT-002 circle sheet sticker: the 138x97 gate is exact</t>
         </is>
       </c>
       <c r="Q43" s="25" t="inlineStr">
@@ -7109,11 +7320,16 @@
       <c r="V43" s="15" t="n"/>
       <c r="W43" s="15" t="n"/>
       <c r="X43" s="15" t="n"/>
+      <c r="Y43" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-074</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="150" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-075</t>
+          <t>MS-SHT-003</t>
         </is>
       </c>
       <c r="B44" s="25" t="inlineStr">
@@ -7192,7 +7408,7 @@
       </c>
       <c r="P44" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-075 원형 판스티커 preset sizes match the shape family table and all fit at least two per sheet</t>
+          <t>MS-SHT-003 원형 판스티커 preset sizes match the shape family table and all fit at least two per sheet</t>
         </is>
       </c>
       <c r="Q44" s="25" t="inlineStr">
@@ -7217,11 +7433,16 @@
       <c r="V44" s="15" t="n"/>
       <c r="W44" s="15" t="n"/>
       <c r="X44" s="15" t="n"/>
+      <c r="Y44" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-075</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="150" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-076</t>
+          <t>MS-SHT-004</t>
         </is>
       </c>
       <c r="B45" s="25" t="inlineStr">
@@ -7302,7 +7523,7 @@
       </c>
       <c r="P45" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-076 circle sheet sticker: both cart edit dialogs reject a one-per-sheet custom size</t>
+          <t>MS-SHT-004 circle sheet sticker: both cart edit dialogs reject a one-per-sheet custom size</t>
         </is>
       </c>
       <c r="Q45" s="25" t="inlineStr">
@@ -7327,11 +7548,16 @@
       <c r="V45" s="15" t="n"/>
       <c r="W45" s="15" t="n"/>
       <c r="X45" s="15" t="n"/>
+      <c r="Y45" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-076</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="150" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-077</t>
+          <t>MS-SHT-005</t>
         </is>
       </c>
       <c r="B46" s="25" t="inlineStr">
@@ -7410,7 +7636,7 @@
       </c>
       <c r="P46" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-077 circle sheet sticker: the A5 배치 가이드 modal rejects a one-per-sheet custom size</t>
+          <t>MS-SHT-005 circle sheet sticker: the A5 배치 가이드 modal rejects a one-per-sheet custom size</t>
         </is>
       </c>
       <c r="Q46" s="25" t="inlineStr">
@@ -7435,11 +7661,16 @@
       <c r="V46" s="15" t="n"/>
       <c r="W46" s="15" t="n"/>
       <c r="X46" s="15" t="n"/>
+      <c r="Y46" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-077</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="150" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-078</t>
+          <t>MS-SHT-006</t>
         </is>
       </c>
       <c r="B47" s="25" t="inlineStr">
@@ -7517,7 +7748,7 @@
       </c>
       <c r="P47" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-078 circle sheet sticker: 138x97 packs 2 per sheet and is orderable</t>
+          <t>MS-SHT-006 circle sheet sticker: 138x97 packs 2 per sheet and is orderable</t>
         </is>
       </c>
       <c r="Q47" s="25" t="inlineStr">
@@ -7530,7 +7761,7 @@
       </c>
       <c r="S47" s="25" t="inlineStr">
         <is>
-          <t>The minimum-two-per-sheet error is matched with the regex /한 시트에 최소 2개의 스티커/, the clause shared by both current wordings: the axis-specific line ("...들어가도록 세로 길이를 97mm 이하로 입력해 주세요.", on production since 2026-08-31, shown when only the height is over) and the original generic line ("더 작은 사이즈를 입력해 주세요. 한 시트에 최소 2개의 스티커가 들어가야 합니다.", shown when the width is over). test-case.md still quotes only the old generic literal. The old-literal assertions noted in memory have already been replaced in code by this shared-clause regex. Both gate axes are covered: width (138 vs 139) and height (97 vs 98). test-case.md says rejected sizes fall back to the last valid size (the default 소형); since 2026-08-31 the readout reports the rejected size itself (see MS-V2-073), but this test does not check counts for rejected sizes. test-case.md shows no @production tag for this ID, but the code has it.</t>
+          <t>The minimum-two-per-sheet error is matched with the regex /한 시트에 최소 2개의 스티커/, the clause shared by both current wordings: the axis-specific line ("...들어가도록 세로 길이를 97mm 이하로 입력해 주세요.", on production since 2026-08-31, shown when only the height is over) and the original generic line ("더 작은 사이즈를 입력해 주세요. 한 시트에 최소 2개의 스티커가 들어가야 합니다.", shown when the width is over). test-case.md still quotes only the old generic literal. The old-literal assertions noted in memory have already been replaced in code by this shared-clause regex. Both gate axes are covered: width (138 vs 139) and height (97 vs 98). test-case.md says rejected sizes fall back to the last valid size (the default 소형); since 2026-08-31 the readout reports the rejected size itself (see MS-SHT-001), but this test does not check counts for rejected sizes. test-case.md shows no @production tag for this ID, but the code has it.</t>
         </is>
       </c>
       <c r="T47" s="14" t="inlineStr">
@@ -7542,11 +7773,16 @@
       <c r="V47" s="15" t="n"/>
       <c r="W47" s="15" t="n"/>
       <c r="X47" s="15" t="n"/>
+      <c r="Y47" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-078</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="150" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-100</t>
+          <t>MS-CRT-001</t>
         </is>
       </c>
       <c r="B48" s="25" t="inlineStr">
@@ -7627,7 +7863,7 @@
       </c>
       <c r="P48" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-100 removing the only line item leaves an empty cart, not a broken one</t>
+          <t>MS-CRT-001 removing the only line item leaves an empty cart, not a broken one</t>
         </is>
       </c>
       <c r="Q48" s="25" t="inlineStr">
@@ -7652,11 +7888,16 @@
       <c r="V48" s="15" t="n"/>
       <c r="W48" s="15" t="n"/>
       <c r="X48" s="15" t="n"/>
+      <c r="Y48" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-100</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="150" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-101</t>
+          <t>MS-CRT-002</t>
         </is>
       </c>
       <c r="B49" s="25" t="inlineStr">
@@ -7736,7 +7977,7 @@
       </c>
       <c r="P49" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-101 two distinct products become two lines whose prices sum to the cart total</t>
+          <t>MS-CRT-002 two distinct products become two lines whose prices sum to the cart total</t>
         </is>
       </c>
       <c r="Q49" s="25" t="inlineStr">
@@ -7761,11 +8002,16 @@
       <c r="V49" s="15" t="n"/>
       <c r="W49" s="15" t="n"/>
       <c r="X49" s="15" t="n"/>
+      <c r="Y49" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-101</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="150" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-102</t>
+          <t>MS-CRT-003</t>
         </is>
       </c>
       <c r="B50" s="25" t="inlineStr">
@@ -7845,7 +8091,7 @@
       </c>
       <c r="P50" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-102 a guest cart survives a full page reload @smoke</t>
+          <t>MS-CRT-003 a guest cart survives a full page reload @smoke</t>
         </is>
       </c>
       <c r="Q50" s="25" t="inlineStr">
@@ -7870,11 +8116,16 @@
       <c r="V50" s="15" t="n"/>
       <c r="W50" s="15" t="n"/>
       <c r="X50" s="15" t="n"/>
+      <c r="Y50" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-102</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="150" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-103</t>
+          <t>MS-CRT-004</t>
         </is>
       </c>
       <c r="B51" s="25" t="inlineStr">
@@ -7954,7 +8205,7 @@
       </c>
       <c r="P51" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-103 the cart page confirms a removal before acting on it</t>
+          <t>MS-CRT-004 the cart page confirms a removal before acting on it</t>
         </is>
       </c>
       <c r="Q51" s="25" t="inlineStr">
@@ -7979,11 +8230,16 @@
       <c r="V51" s="15" t="n"/>
       <c r="W51" s="15" t="n"/>
       <c r="X51" s="15" t="n"/>
+      <c r="Y51" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-103</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-104</t>
+          <t>MS-CRT-005</t>
         </is>
       </c>
       <c r="B52" s="25" t="inlineStr">
@@ -8063,7 +8319,7 @@
       </c>
       <c r="P52" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-104 a guest cart is merged into the member cart on login</t>
+          <t>MS-CRT-005 a guest cart is merged into the member cart on login</t>
         </is>
       </c>
       <c r="Q52" s="25" t="inlineStr">
@@ -8088,11 +8344,16 @@
       <c r="V52" s="15" t="n"/>
       <c r="W52" s="15" t="n"/>
       <c r="X52" s="15" t="n"/>
+      <c r="Y52" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-104</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="150" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-105</t>
+          <t>MS-CRT-006</t>
         </is>
       </c>
       <c r="B53" s="25" t="inlineStr">
@@ -8170,7 +8431,7 @@
       </c>
       <c r="P53" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-105 an empty cart page offers a way back into the catalog</t>
+          <t>MS-CRT-006 an empty cart page offers a way back into the catalog</t>
         </is>
       </c>
       <c r="Q53" s="25" t="inlineStr">
@@ -8195,11 +8456,16 @@
       <c r="V53" s="15" t="n"/>
       <c r="W53" s="15" t="n"/>
       <c r="X53" s="15" t="n"/>
+      <c r="Y53" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-105</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="150" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-025</t>
+          <t>MS-CHK-001</t>
         </is>
       </c>
       <c r="B54" s="25" t="inlineStr">
@@ -8282,7 +8548,7 @@
       </c>
       <c r="P54" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-025 guest checkout completes via the KakaoPay sandbox and sends an order-confirmation email</t>
+          <t>MS-CHK-001 guest checkout completes via the KakaoPay sandbox and sends an order-confirmation email</t>
         </is>
       </c>
       <c r="Q54" s="25" t="inlineStr">
@@ -8307,11 +8573,16 @@
       <c r="V54" s="15" t="n"/>
       <c r="W54" s="15" t="n"/>
       <c r="X54" s="15" t="n"/>
+      <c r="Y54" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-025</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="150" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-041</t>
+          <t>MS-CHK-002</t>
         </is>
       </c>
       <c r="B55" s="25" t="inlineStr">
@@ -8389,7 +8660,7 @@
       </c>
       <c r="P55" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-041 checkout page renders shipping, payment, and order summary without submitting</t>
+          <t>MS-CHK-002 checkout page renders shipping, payment, and order summary without submitting</t>
         </is>
       </c>
       <c r="Q55" s="25" t="inlineStr">
@@ -8414,11 +8685,16 @@
       <c r="V55" s="15" t="n"/>
       <c r="W55" s="15" t="n"/>
       <c r="X55" s="15" t="n"/>
+      <c r="Y55" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-041</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="150" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-042</t>
+          <t>MS-CHK-003</t>
         </is>
       </c>
       <c r="B56" s="25" t="inlineStr">
@@ -8496,7 +8772,7 @@
       </c>
       <c r="P56" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-042 checkout blocks payment submission when required fields are blank</t>
+          <t>MS-CHK-003 checkout blocks payment submission when required fields are blank</t>
         </is>
       </c>
       <c r="Q56" s="25" t="inlineStr">
@@ -8521,11 +8797,16 @@
       <c r="V56" s="15" t="n"/>
       <c r="W56" s="15" t="n"/>
       <c r="X56" s="15" t="n"/>
+      <c r="Y56" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-042</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="150" customHeight="1">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-097</t>
+          <t>MS-CHK-004</t>
         </is>
       </c>
       <c r="B57" s="25" t="inlineStr">
@@ -8605,7 +8886,7 @@
       </c>
       <c r="P57" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-097 the quoted price survives product page, cart, and checkout unchanged</t>
+          <t>MS-CHK-004 the quoted price survives product page, cart, and checkout unchanged</t>
         </is>
       </c>
       <c r="Q57" s="25" t="inlineStr">
@@ -8630,11 +8911,16 @@
       <c r="V57" s="15" t="n"/>
       <c r="W57" s="15" t="n"/>
       <c r="X57" s="15" t="n"/>
+      <c r="Y57" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-097</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="150" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-098</t>
+          <t>MS-CHK-005</t>
         </is>
       </c>
       <c r="B58" s="25" t="inlineStr">
@@ -8713,7 +8999,7 @@
       </c>
       <c r="P58" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-098 an order below the free-shipping threshold is charged shipping</t>
+          <t>MS-CHK-005 an order below the free-shipping threshold is charged shipping</t>
         </is>
       </c>
       <c r="Q58" s="25" t="inlineStr">
@@ -8738,11 +9024,16 @@
       <c r="V58" s="15" t="n"/>
       <c r="W58" s="15" t="n"/>
       <c r="X58" s="15" t="n"/>
+      <c r="Y58" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-098</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="150" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-099</t>
+          <t>MS-CHK-006</t>
         </is>
       </c>
       <c r="B59" s="25" t="inlineStr">
@@ -8821,7 +9112,7 @@
       </c>
       <c r="P59" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-099 an order at or above the free-shipping threshold ships free</t>
+          <t>MS-CHK-006 an order at or above the free-shipping threshold ships free</t>
         </is>
       </c>
       <c r="Q59" s="25" t="inlineStr">
@@ -8846,6 +9137,11 @@
       <c r="V59" s="15" t="n"/>
       <c r="W59" s="15" t="n"/>
       <c r="X59" s="15" t="n"/>
+      <c r="Y59" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-099</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="150" customHeight="1">
       <c r="A60" s="12" t="inlineStr">
@@ -11910,7 +12206,7 @@
     <row r="88" ht="150" customHeight="1">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-026</t>
+          <t>MS-AUTH-001</t>
         </is>
       </c>
       <c r="B88" s="25" t="inlineStr">
@@ -11988,7 +12284,7 @@
       </c>
       <c r="P88" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-026 account navigation opens login</t>
+          <t>MS-AUTH-001 account navigation opens login</t>
         </is>
       </c>
       <c r="Q88" s="25" t="inlineStr">
@@ -12013,11 +12309,16 @@
       <c r="V88" s="15" t="n"/>
       <c r="W88" s="15" t="n"/>
       <c r="X88" s="15" t="n"/>
+      <c r="Y88" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-026</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="150" customHeight="1">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-027</t>
+          <t>MS-AUTH-002</t>
         </is>
       </c>
       <c r="B89" s="25" t="inlineStr">
@@ -12094,7 +12395,7 @@
       </c>
       <c r="P89" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-027 member login form exposes expected controls</t>
+          <t>MS-AUTH-002 member login form exposes expected controls</t>
         </is>
       </c>
       <c r="Q89" s="25" t="inlineStr">
@@ -12119,11 +12420,16 @@
       <c r="V89" s="15" t="n"/>
       <c r="W89" s="15" t="n"/>
       <c r="X89" s="15" t="n"/>
+      <c r="Y89" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-027</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="150" customHeight="1">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-028</t>
+          <t>MS-AUTH-003</t>
         </is>
       </c>
       <c r="B90" s="25" t="inlineStr">
@@ -12200,7 +12506,7 @@
       </c>
       <c r="P90" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-028 blank login is blocked before the auth endpoint is called @validation</t>
+          <t>MS-AUTH-003 blank login is blocked before the auth endpoint is called @validation</t>
         </is>
       </c>
       <c r="Q90" s="25" t="inlineStr">
@@ -12225,11 +12531,16 @@
       <c r="V90" s="15" t="n"/>
       <c r="W90" s="15" t="n"/>
       <c r="X90" s="15" t="n"/>
+      <c r="Y90" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-028</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="150" customHeight="1">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-029</t>
+          <t>MS-AUTH-004</t>
         </is>
       </c>
       <c r="B91" s="25" t="inlineStr">
@@ -12306,7 +12617,7 @@
       </c>
       <c r="P91" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-029 malformed email is rejected without starting an auth session @validation</t>
+          <t>MS-AUTH-004 malformed email is rejected without starting an auth session @validation</t>
         </is>
       </c>
       <c r="Q91" s="25" t="inlineStr">
@@ -12327,11 +12638,16 @@
       <c r="V91" s="15" t="n"/>
       <c r="W91" s="15" t="n"/>
       <c r="X91" s="15" t="n"/>
+      <c r="Y91" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-029</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="150" customHeight="1">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-030</t>
+          <t>MS-AUTH-005</t>
         </is>
       </c>
       <c r="B92" s="25" t="inlineStr">
@@ -12410,7 +12726,7 @@
       </c>
       <c r="P92" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-030 invalid credentials fail safely and keep the user anonymous @validation</t>
+          <t>MS-AUTH-005 invalid credentials fail safely and keep the user anonymous @validation</t>
         </is>
       </c>
       <c r="Q92" s="25" t="inlineStr">
@@ -12435,11 +12751,16 @@
       <c r="V92" s="15" t="n"/>
       <c r="W92" s="15" t="n"/>
       <c r="X92" s="15" t="n"/>
+      <c r="Y92" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-030</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="150" customHeight="1">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-031</t>
+          <t>MS-AUTH-006</t>
         </is>
       </c>
       <c r="B93" s="25" t="inlineStr">
@@ -12519,7 +12840,7 @@
       </c>
       <c r="P93" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-031 password visibility toggle masks and unmasks password</t>
+          <t>MS-AUTH-006 password visibility toggle masks and unmasks password</t>
         </is>
       </c>
       <c r="Q93" s="25" t="inlineStr">
@@ -12532,7 +12853,7 @@
       </c>
       <c r="S93" s="25" t="inlineStr">
         <is>
-          <t>Also covers MS-V2-044 (re-verification against production on 2026-08-11), which has no separate test; the 2026-08-10 toggle bug in test-case.md is no longer reproducible and the test is no longer fixme'd. Page load already round-trips the toggle once to detect hydration. test-case.md lists @regression; the spec does not carry it.</t>
+          <t>Also covers MS-AUTH-011 (re-verification against production on 2026-08-11), which has no separate test; the 2026-08-10 toggle bug in test-case.md is no longer reproducible and the test is no longer fixme'd. Page load already round-trips the toggle once to detect hydration. test-case.md lists @regression; the spec does not carry it.</t>
         </is>
       </c>
       <c r="T93" s="14" t="inlineStr">
@@ -12544,11 +12865,16 @@
       <c r="V93" s="15" t="n"/>
       <c r="W93" s="15" t="n"/>
       <c r="X93" s="15" t="n"/>
+      <c r="Y93" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-031</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="150" customHeight="1">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-032</t>
+          <t>MS-AUTH-007</t>
         </is>
       </c>
       <c r="B94" s="25" t="inlineStr">
@@ -12627,7 +12953,7 @@
       </c>
       <c r="P94" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-032 forgot-password recovery opens and validates its email input @validation</t>
+          <t>MS-AUTH-007 forgot-password recovery opens and validates its email input @validation</t>
         </is>
       </c>
       <c r="Q94" s="25" t="inlineStr">
@@ -12640,7 +12966,7 @@
       </c>
       <c r="S94" s="25" t="inlineStr">
         <is>
-          <t>Unlike MS-V2-028/029, the code does not watch the network, so the claim that no recovery request is sent is not actually verified. Never submit a real address in production.</t>
+          <t>Unlike MS-AUTH-003/MS-AUTH-004, the code does not watch the network, so the claim that no recovery request is sent is not actually verified. Never submit a real address in production.</t>
         </is>
       </c>
       <c r="T94" s="14" t="inlineStr">
@@ -12652,11 +12978,16 @@
       <c r="V94" s="15" t="n"/>
       <c r="W94" s="15" t="n"/>
       <c r="X94" s="15" t="n"/>
+      <c r="Y94" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-032</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="150" customHeight="1">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-033</t>
+          <t>MS-AUTH-008</t>
         </is>
       </c>
       <c r="B95" s="25" t="inlineStr">
@@ -12733,7 +13064,7 @@
       </c>
       <c r="P95" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-033 register entry is reachable from login</t>
+          <t>MS-AUTH-008 register entry is reachable from login</t>
         </is>
       </c>
       <c r="Q95" s="25" t="inlineStr">
@@ -12746,7 +13077,7 @@
       </c>
       <c r="S95" s="25" t="inlineStr">
         <is>
-          <t>test-case.md steps 4-6 (check registration fields, go back, login form restored) are not in this test; register controls are MS-V2-079 and the return trip is MS-V2-085. Nothing is submitted.</t>
+          <t>test-case.md steps 4-6 (check registration fields, go back, login form restored) are not in this test; register controls are MS-AUTH-012 and the return trip is MS-AUTH-018. Nothing is submitted.</t>
         </is>
       </c>
       <c r="T95" s="14" t="inlineStr">
@@ -12758,11 +13089,16 @@
       <c r="V95" s="15" t="n"/>
       <c r="W95" s="15" t="n"/>
       <c r="X95" s="15" t="n"/>
+      <c r="Y95" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-033</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="150" customHeight="1">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-034</t>
+          <t>MS-AUTH-009</t>
         </is>
       </c>
       <c r="B96" s="25" t="inlineStr">
@@ -12840,7 +13176,7 @@
       </c>
       <c r="P96" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-034 seeded member can log in @credentialed</t>
+          <t>MS-AUTH-009 seeded member can log in @credentialed</t>
         </is>
       </c>
       <c r="Q96" s="25" t="inlineStr">
@@ -12865,11 +13201,16 @@
       <c r="V96" s="15" t="n"/>
       <c r="W96" s="15" t="n"/>
       <c r="X96" s="15" t="n"/>
+      <c r="Y96" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-034</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="150" customHeight="1">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-035</t>
+          <t>MS-AUTH-010</t>
         </is>
       </c>
       <c r="B97" s="25" t="inlineStr">
@@ -12949,7 +13290,7 @@
       </c>
       <c r="P97" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-035 session persists across reload and navigation, and logout clears it @credentialed</t>
+          <t>MS-AUTH-010 session persists across reload and navigation, and logout clears it @credentialed</t>
         </is>
       </c>
       <c r="Q97" s="25" t="inlineStr">
@@ -12974,11 +13315,16 @@
       <c r="V97" s="15" t="n"/>
       <c r="W97" s="15" t="n"/>
       <c r="X97" s="15" t="n"/>
+      <c r="Y97" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-035</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="150" customHeight="1">
       <c r="A98" s="16" t="inlineStr">
         <is>
-          <t>MS-V2-044</t>
+          <t>MS-AUTH-011</t>
         </is>
       </c>
       <c r="B98" s="25" t="inlineStr">
@@ -12998,7 +13344,7 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>Withdrawn: re-verification of the MS-V2-031 password visibility toggle. Merged into MS-V2-031.</t>
+          <t>Withdrawn: re-verification of the MS-AUTH-006 password visibility toggle. Merged into MS-AUTH-006.</t>
         </is>
       </c>
       <c r="F98" s="13" t="inlineStr">
@@ -13066,7 +13412,7 @@
       </c>
       <c r="S98" s="25" t="inlineStr">
         <is>
-          <t>withdrawn 2026-08-11: the production toggle bug (rendered but did not unmask) no longer reproduced, so the re-verification was folded into MS-V2-031 (see the comment in tests/e2e/storefront/auth/login.spec.ts). Keep the ID; do not reuse it.</t>
+          <t>withdrawn 2026-08-11: the production toggle bug (rendered but did not unmask) no longer reproduced, so the re-verification was folded into MS-AUTH-006 (see the comment in tests/e2e/storefront/auth/login.spec.ts). Keep the ID; do not reuse it.</t>
         </is>
       </c>
       <c r="T98" s="14" t="inlineStr">
@@ -13078,11 +13424,16 @@
       <c r="V98" s="15" t="n"/>
       <c r="W98" s="15" t="n"/>
       <c r="X98" s="15" t="n"/>
+      <c r="Y98" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-044</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="150" customHeight="1">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-079</t>
+          <t>MS-AUTH-012</t>
         </is>
       </c>
       <c r="B99" s="25" t="inlineStr">
@@ -13160,7 +13511,7 @@
       </c>
       <c r="P99" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-079 register form exposes expected controls @smoke</t>
+          <t>MS-AUTH-012 register form exposes expected controls @smoke</t>
         </is>
       </c>
       <c r="Q99" s="25" t="inlineStr">
@@ -13185,11 +13536,16 @@
       <c r="V99" s="15" t="n"/>
       <c r="W99" s="15" t="n"/>
       <c r="X99" s="15" t="n"/>
+      <c r="Y99" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-079</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="150" customHeight="1">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-080</t>
+          <t>MS-AUTH-013</t>
         </is>
       </c>
       <c r="B100" s="25" t="inlineStr">
@@ -13266,7 +13622,7 @@
       </c>
       <c r="P100" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-080 blank register submit is blocked with required-field validation @validation</t>
+          <t>MS-AUTH-013 blank register submit is blocked with required-field validation @validation</t>
         </is>
       </c>
       <c r="Q100" s="25" t="inlineStr">
@@ -13291,11 +13647,16 @@
       <c r="V100" s="15" t="n"/>
       <c r="W100" s="15" t="n"/>
       <c r="X100" s="15" t="n"/>
+      <c r="Y100" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-080</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="150" customHeight="1">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-081</t>
+          <t>MS-AUTH-014</t>
         </is>
       </c>
       <c r="B101" s="25" t="inlineStr">
@@ -13372,7 +13733,7 @@
       </c>
       <c r="P101" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-081 malformed email is rejected before any account is requested @validation</t>
+          <t>MS-AUTH-014 malformed email is rejected before any account is requested @validation</t>
         </is>
       </c>
       <c r="Q101" s="25" t="inlineStr">
@@ -13385,7 +13746,7 @@
       </c>
       <c r="S101" s="25" t="inlineStr">
         <is>
-          <t>URL is not asserted here (unlike MS-V2-080).</t>
+          <t>URL is not asserted here (unlike MS-AUTH-013).</t>
         </is>
       </c>
       <c r="T101" s="14" t="inlineStr">
@@ -13397,11 +13758,16 @@
       <c r="V101" s="15" t="n"/>
       <c r="W101" s="15" t="n"/>
       <c r="X101" s="15" t="n"/>
+      <c r="Y101" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-081</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="150" customHeight="1">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-082</t>
+          <t>MS-AUTH-015</t>
         </is>
       </c>
       <c r="B102" s="25" t="inlineStr">
@@ -13478,7 +13844,7 @@
       </c>
       <c r="P102" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-082 password below the stated policy is rejected @validation</t>
+          <t>MS-AUTH-015 password below the stated policy is rejected @validation</t>
         </is>
       </c>
       <c r="Q102" s="25" t="inlineStr">
@@ -13503,11 +13869,16 @@
       <c r="V102" s="15" t="n"/>
       <c r="W102" s="15" t="n"/>
       <c r="X102" s="15" t="n"/>
+      <c r="Y102" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-082</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="150" customHeight="1">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-083</t>
+          <t>MS-AUTH-016</t>
         </is>
       </c>
       <c r="B103" s="25" t="inlineStr">
@@ -13585,7 +13956,7 @@
       </c>
       <c r="P103" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-083 registration is blocked until the terms checkbox is agreed @validation</t>
+          <t>MS-AUTH-016 registration is blocked until the terms checkbox is agreed @validation</t>
         </is>
       </c>
       <c r="Q103" s="25" t="inlineStr">
@@ -13610,11 +13981,16 @@
       <c r="V103" s="15" t="n"/>
       <c r="W103" s="15" t="n"/>
       <c r="X103" s="15" t="n"/>
+      <c r="Y103" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-083</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="150" customHeight="1">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-084</t>
+          <t>MS-AUTH-017</t>
         </is>
       </c>
       <c r="B104" s="25" t="inlineStr">
@@ -13692,7 +14068,7 @@
       </c>
       <c r="P104" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-084 register password visibility toggle masks and unmasks</t>
+          <t>MS-AUTH-017 register password visibility toggle masks and unmasks</t>
         </is>
       </c>
       <c r="Q104" s="25" t="inlineStr">
@@ -13717,11 +14093,16 @@
       <c r="V104" s="15" t="n"/>
       <c r="W104" s="15" t="n"/>
       <c r="X104" s="15" t="n"/>
+      <c r="Y104" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-084</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="150" customHeight="1">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-085</t>
+          <t>MS-AUTH-018</t>
         </is>
       </c>
       <c r="B105" s="25" t="inlineStr">
@@ -13798,7 +14179,7 @@
       </c>
       <c r="P105" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-085 login entry is reachable from register</t>
+          <t>MS-AUTH-018 login entry is reachable from register</t>
         </is>
       </c>
       <c r="Q105" s="25" t="inlineStr">
@@ -13823,11 +14204,16 @@
       <c r="V105" s="15" t="n"/>
       <c r="W105" s="15" t="n"/>
       <c r="X105" s="15" t="n"/>
+      <c r="Y105" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-085</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="150" customHeight="1">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-086</t>
+          <t>MS-AUTH-019</t>
         </is>
       </c>
       <c r="B106" s="25" t="inlineStr">
@@ -13905,7 +14291,7 @@
       </c>
       <c r="P106" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-086 registering an existing email offers sign-in instead of a duplicate account @credentialed</t>
+          <t>MS-AUTH-019 registering an existing email offers sign-in instead of a duplicate account @credentialed</t>
         </is>
       </c>
       <c r="Q106" s="25" t="inlineStr">
@@ -13930,11 +14316,16 @@
       <c r="V106" s="15" t="n"/>
       <c r="W106" s="15" t="n"/>
       <c r="X106" s="15" t="n"/>
+      <c r="Y106" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-086</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="150" customHeight="1">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-087</t>
+          <t>MS-AUTH-020</t>
         </is>
       </c>
       <c r="B107" s="25" t="inlineStr">
@@ -14013,7 +14404,7 @@
       </c>
       <c r="P107" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-087 a wrong verification code is rejected and creates no account</t>
+          <t>MS-AUTH-020 a wrong verification code is rejected and creates no account</t>
         </is>
       </c>
       <c r="Q107" s="25" t="inlineStr">
@@ -14038,11 +14429,16 @@
       <c r="V107" s="15" t="n"/>
       <c r="W107" s="15" t="n"/>
       <c r="X107" s="15" t="n"/>
+      <c r="Y107" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-087</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="150" customHeight="1">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-088</t>
+          <t>MS-AUTH-021</t>
         </is>
       </c>
       <c r="B108" s="25" t="inlineStr">
@@ -14122,7 +14518,7 @@
       </c>
       <c r="P108" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-088 a correct verification code creates the account and signs the new member in</t>
+          <t>MS-AUTH-021 a correct verification code creates the account and signs the new member in</t>
         </is>
       </c>
       <c r="Q108" s="25" t="inlineStr">
@@ -14135,7 +14531,7 @@
       </c>
       <c r="S108" s="25" t="inlineStr">
         <is>
-          <t>Discrepancy: test-case.md says the account needs no cleanup; the code records it (createdBy MS-V2-088) in .auth/created-accounts.jsonl, and global teardown deletes it only when TEST_DATA_USER_DELETE_ENDPOINT is set. Otherwise teardown warns and the real account stays on the dev server. Carries @production from its describe block but is gated and excluded from prod scripts by @destructive; do not run on production.</t>
+          <t>Discrepancy: test-case.md says the account needs no cleanup; the code records it (createdBy MS-AUTH-021) in .auth/created-accounts.jsonl, and global teardown deletes it only when TEST_DATA_USER_DELETE_ENDPOINT is set. Otherwise teardown warns and the real account stays on the dev server. Carries @production from its describe block but is gated and excluded from prod scripts by @destructive; do not run on production.</t>
         </is>
       </c>
       <c r="T108" s="14" t="inlineStr">
@@ -14147,11 +14543,16 @@
       <c r="V108" s="15" t="n"/>
       <c r="W108" s="15" t="n"/>
       <c r="X108" s="15" t="n"/>
+      <c r="Y108" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-088</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="150" customHeight="1">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-089</t>
+          <t>MS-AUTH-022</t>
         </is>
       </c>
       <c r="B109" s="25" t="inlineStr">
@@ -14229,7 +14630,7 @@
       </c>
       <c r="P109" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-089 account profile exposes the password change controls @smoke</t>
+          <t>MS-AUTH-022 account profile exposes the password change controls @smoke</t>
         </is>
       </c>
       <c r="Q109" s="25" t="inlineStr">
@@ -14254,11 +14655,16 @@
       <c r="V109" s="15" t="n"/>
       <c r="W109" s="15" t="n"/>
       <c r="X109" s="15" t="n"/>
+      <c r="Y109" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-089</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="150" customHeight="1">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-090</t>
+          <t>MS-AUTH-023</t>
         </is>
       </c>
       <c r="B110" s="25" t="inlineStr">
@@ -14337,7 +14743,7 @@
       </c>
       <c r="P110" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-090 change password stays disabled until every field is filled @validation</t>
+          <t>MS-AUTH-023 change password stays disabled until every field is filled @validation</t>
         </is>
       </c>
       <c r="Q110" s="25" t="inlineStr">
@@ -14362,11 +14768,16 @@
       <c r="V110" s="15" t="n"/>
       <c r="W110" s="15" t="n"/>
       <c r="X110" s="15" t="n"/>
+      <c r="Y110" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-090</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="150" customHeight="1">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-091</t>
+          <t>MS-AUTH-024</t>
         </is>
       </c>
       <c r="B111" s="25" t="inlineStr">
@@ -14444,7 +14855,7 @@
       </c>
       <c r="P111" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-091 a mismatched confirmation is rejected @validation</t>
+          <t>MS-AUTH-024 a mismatched confirmation is rejected @validation</t>
         </is>
       </c>
       <c r="Q111" s="25" t="inlineStr">
@@ -14469,11 +14880,16 @@
       <c r="V111" s="15" t="n"/>
       <c r="W111" s="15" t="n"/>
       <c r="X111" s="15" t="n"/>
+      <c r="Y111" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-091</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="150" customHeight="1">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-092</t>
+          <t>MS-AUTH-025</t>
         </is>
       </c>
       <c r="B112" s="25" t="inlineStr">
@@ -14551,7 +14967,7 @@
       </c>
       <c r="P112" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-092 a new password below the policy is rejected @validation</t>
+          <t>MS-AUTH-025 a new password below the policy is rejected @validation</t>
         </is>
       </c>
       <c r="Q112" s="25" t="inlineStr">
@@ -14576,11 +14992,16 @@
       <c r="V112" s="15" t="n"/>
       <c r="W112" s="15" t="n"/>
       <c r="X112" s="15" t="n"/>
+      <c r="Y112" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-092</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="150" customHeight="1">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-093</t>
+          <t>MS-AUTH-026</t>
         </is>
       </c>
       <c r="B113" s="25" t="inlineStr">
@@ -14658,7 +15079,7 @@
       </c>
       <c r="P113" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-093 a wrong current password is rejected @validation</t>
+          <t>MS-AUTH-026 a wrong current password is rejected @validation</t>
         </is>
       </c>
       <c r="Q113" s="25" t="inlineStr">
@@ -14683,11 +15104,16 @@
       <c r="V113" s="15" t="n"/>
       <c r="W113" s="15" t="n"/>
       <c r="X113" s="15" t="n"/>
+      <c r="Y113" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-093</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="150" customHeight="1">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-094</t>
+          <t>MS-AUTH-027</t>
         </is>
       </c>
       <c r="B114" s="25" t="inlineStr">
@@ -14767,7 +15193,7 @@
       </c>
       <c r="P114" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-094 changing a password rotates the credential end to end</t>
+          <t>MS-AUTH-027 changing a password rotates the credential end to end</t>
         </is>
       </c>
       <c r="Q114" s="25" t="inlineStr">
@@ -14780,7 +15206,7 @@
       </c>
       <c r="S114" s="25" t="inlineStr">
         <is>
-          <t>Creates a real member account. It is recorded (createdBy MS-V2-094) in .auth/created-accounts.jsonl; global teardown deletes it only when TEST_DATA_USER_DELETE_ENDPOINT is set, otherwise it just warns and the account stays on the server. Carries @production through its describe block but is skipped unless RUN_AUTH_DESTRUCTIVE_E2E=true and excluded from the prod scripts by @destructive; never run on production. Uses its own account so the seeded member's password is never touched.</t>
+          <t>Creates a real member account. It is recorded (createdBy MS-AUTH-027) in .auth/created-accounts.jsonl; global teardown deletes it only when TEST_DATA_USER_DELETE_ENDPOINT is set, otherwise it just warns and the account stays on the server. Carries @production through its describe block but is skipped unless RUN_AUTH_DESTRUCTIVE_E2E=true and excluded from the prod scripts by @destructive; never run on production. Uses its own account so the seeded member's password is never touched.</t>
         </is>
       </c>
       <c r="T114" s="14" t="inlineStr">
@@ -14792,11 +15218,16 @@
       <c r="V114" s="15" t="n"/>
       <c r="W114" s="15" t="n"/>
       <c r="X114" s="15" t="n"/>
+      <c r="Y114" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-094</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="150" customHeight="1">
       <c r="A115" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-095</t>
+          <t>MS-AUTH-028</t>
         </is>
       </c>
       <c r="B115" s="25" t="inlineStr">
@@ -14873,7 +15304,7 @@
       </c>
       <c r="P115" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-095 a member-only route is not reachable anonymously</t>
+          <t>MS-AUTH-028 a member-only route is not reachable anonymously</t>
         </is>
       </c>
       <c r="Q115" s="25" t="inlineStr">
@@ -14898,11 +15329,16 @@
       <c r="V115" s="15" t="n"/>
       <c r="W115" s="15" t="n"/>
       <c r="X115" s="15" t="n"/>
+      <c r="Y115" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-095</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="150" customHeight="1">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-096</t>
+          <t>MS-AUTH-029</t>
         </is>
       </c>
       <c r="B116" s="25" t="inlineStr">
@@ -14979,7 +15415,7 @@
       </c>
       <c r="P116" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-096 non-member mode swaps in the guest order-lookup form</t>
+          <t>MS-AUTH-029 non-member mode swaps in the guest order-lookup form</t>
         </is>
       </c>
       <c r="Q116" s="25" t="inlineStr">
@@ -14992,7 +15428,7 @@
       </c>
       <c r="S116" s="25" t="inlineStr">
         <is>
-          <t>Nothing is submitted; actual lookups are MS-V2-112 to MS-V2-114.</t>
+          <t>Nothing is submitted; actual lookups are MS-AUTH-030 to MS-AUTH-032.</t>
         </is>
       </c>
       <c r="T116" s="14" t="inlineStr">
@@ -15004,11 +15440,16 @@
       <c r="V116" s="15" t="n"/>
       <c r="W116" s="15" t="n"/>
       <c r="X116" s="15" t="n"/>
+      <c r="Y116" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-096</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="150" customHeight="1">
       <c r="A117" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-112</t>
+          <t>MS-AUTH-030</t>
         </is>
       </c>
       <c r="B117" s="25" t="inlineStr">
@@ -15086,7 +15527,7 @@
       </c>
       <c r="P117" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-112 an unknown order number is refused without signing anyone in</t>
+          <t>MS-AUTH-030 an unknown order number is refused without signing anyone in</t>
         </is>
       </c>
       <c r="Q117" s="25" t="inlineStr">
@@ -15111,11 +15552,16 @@
       <c r="V117" s="15" t="n"/>
       <c r="W117" s="15" t="n"/>
       <c r="X117" s="15" t="n"/>
+      <c r="Y117" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-112</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="150" customHeight="1">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-113</t>
+          <t>MS-AUTH-031</t>
         </is>
       </c>
       <c r="B118" s="25" t="inlineStr">
@@ -15192,7 +15638,7 @@
       </c>
       <c r="P118" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-113 blank guest lookup is blocked before the endpoint is called @validation</t>
+          <t>MS-AUTH-031 blank guest lookup is blocked before the endpoint is called @validation</t>
         </is>
       </c>
       <c r="Q118" s="25" t="inlineStr">
@@ -15217,11 +15663,16 @@
       <c r="V118" s="15" t="n"/>
       <c r="W118" s="15" t="n"/>
       <c r="X118" s="15" t="n"/>
+      <c r="Y118" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-113</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="150" customHeight="1">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-114</t>
+          <t>MS-AUTH-032</t>
         </is>
       </c>
       <c r="B119" s="25" t="inlineStr">
@@ -15299,7 +15750,7 @@
       </c>
       <c r="P119" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-114 the refusal does not reveal whether the email belongs to an account @credentialed</t>
+          <t>MS-AUTH-032 the refusal does not reveal whether the email belongs to an account @credentialed</t>
         </is>
       </c>
       <c r="Q119" s="25" t="inlineStr">
@@ -15324,11 +15775,16 @@
       <c r="V119" s="15" t="n"/>
       <c r="W119" s="15" t="n"/>
       <c r="X119" s="15" t="n"/>
+      <c r="Y119" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-114</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="150" customHeight="1">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-107</t>
+          <t>MS-ACC-001</t>
         </is>
       </c>
       <c r="B120" s="25" t="inlineStr">
@@ -15408,7 +15864,7 @@
       </c>
       <c r="P120" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-107 order history lists the member's orders with a number and a date each @smoke</t>
+          <t>MS-ACC-001 order history lists the member's orders with a number and a date each @smoke</t>
         </is>
       </c>
       <c r="Q120" s="25" t="inlineStr">
@@ -15433,11 +15889,16 @@
       <c r="V120" s="15" t="n"/>
       <c r="W120" s="15" t="n"/>
       <c r="X120" s="15" t="n"/>
+      <c r="Y120" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-107</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="150" customHeight="1">
       <c r="A121" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-108</t>
+          <t>MS-ACC-002</t>
         </is>
       </c>
       <c r="B121" s="25" t="inlineStr">
@@ -15516,7 +15977,7 @@
       </c>
       <c r="P121" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-108 selecting an order opens that order, not a placeholder</t>
+          <t>MS-ACC-002 selecting an order opens that order, not a placeholder</t>
         </is>
       </c>
       <c r="Q121" s="25" t="inlineStr">
@@ -15541,11 +16002,16 @@
       <c r="V121" s="15" t="n"/>
       <c r="W121" s="15" t="n"/>
       <c r="X121" s="15" t="n"/>
+      <c r="Y121" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-108</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="150" customHeight="1">
       <c r="A122" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-109</t>
+          <t>MS-ACC-003</t>
         </is>
       </c>
       <c r="B122" s="25" t="inlineStr">
@@ -15624,7 +16090,7 @@
       </c>
       <c r="P122" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-109 the 진행 중 / 이전 내역 control switches which orders are listed</t>
+          <t>MS-ACC-003 the 진행 중 / 이전 내역 control switches which orders are listed</t>
         </is>
       </c>
       <c r="Q122" s="25" t="inlineStr">
@@ -15649,11 +16115,16 @@
       <c r="V122" s="15" t="n"/>
       <c r="W122" s="15" t="n"/>
       <c r="X122" s="15" t="n"/>
+      <c r="Y122" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-109</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="150" customHeight="1">
       <c r="A123" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-110</t>
+          <t>MS-ACC-004</t>
         </is>
       </c>
       <c r="B123" s="25" t="inlineStr">
@@ -15732,7 +16203,7 @@
       </c>
       <c r="P123" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-110 order search narrows the list to the order that was searched for</t>
+          <t>MS-ACC-004 order search narrows the list to the order that was searched for</t>
         </is>
       </c>
       <c r="Q123" s="25" t="inlineStr">
@@ -15757,11 +16228,16 @@
       <c r="V123" s="15" t="n"/>
       <c r="W123" s="15" t="n"/>
       <c r="X123" s="15" t="n"/>
+      <c r="Y123" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-110</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="150" customHeight="1">
       <c r="A124" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-111</t>
+          <t>MS-ACC-005</t>
         </is>
       </c>
       <c r="B124" s="25" t="inlineStr">
@@ -15838,7 +16314,7 @@
       </c>
       <c r="P124" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-111 order history tools are present and named</t>
+          <t>MS-ACC-005 order history tools are present and named</t>
         </is>
       </c>
       <c r="Q124" s="25" t="inlineStr">
@@ -15863,11 +16339,16 @@
       <c r="V124" s="15" t="n"/>
       <c r="W124" s="15" t="n"/>
       <c r="X124" s="15" t="n"/>
+      <c r="Y124" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-111</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="150" customHeight="1">
       <c r="A125" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-017</t>
+          <t>MS-INQ-001</t>
         </is>
       </c>
       <c r="B125" s="25" t="inlineStr">
@@ -15945,7 +16426,7 @@
       </c>
       <c r="P125" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-017 inquiry form validates blank and invalid email submissions</t>
+          <t>MS-INQ-001 inquiry form validates blank and invalid email submissions</t>
         </is>
       </c>
       <c r="Q125" s="25" t="inlineStr">
@@ -15971,11 +16452,16 @@
       <c r="V125" s="15" t="n"/>
       <c r="W125" s="15" t="n"/>
       <c r="X125" s="15" t="n"/>
+      <c r="Y125" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-017</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="150" customHeight="1">
       <c r="A126" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-018</t>
+          <t>MS-INQ-002</t>
         </is>
       </c>
       <c r="B126" s="25" t="inlineStr">
@@ -16052,7 +16538,7 @@
       </c>
       <c r="P126" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-018 inquiry form documents supported attachment constraints</t>
+          <t>MS-INQ-002 inquiry form documents supported attachment constraints</t>
         </is>
       </c>
       <c r="Q126" s="25" t="inlineStr">
@@ -16078,11 +16564,16 @@
       <c r="V126" s="15" t="n"/>
       <c r="W126" s="15" t="n"/>
       <c r="X126" s="15" t="n"/>
+      <c r="Y126" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-018</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="150" customHeight="1">
       <c r="A127" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-019</t>
+          <t>MS-INQ-003</t>
         </is>
       </c>
       <c r="B127" s="25" t="inlineStr">
@@ -16159,7 +16650,7 @@
       </c>
       <c r="P127" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-019 external inquiry links point to Kakao and Naver destinations</t>
+          <t>MS-INQ-003 external inquiry links point to Kakao and Naver destinations</t>
         </is>
       </c>
       <c r="Q127" s="25" t="inlineStr">
@@ -16184,11 +16675,16 @@
       <c r="V127" s="15" t="n"/>
       <c r="W127" s="15" t="n"/>
       <c r="X127" s="15" t="n"/>
+      <c r="Y127" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-019</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="150" customHeight="1">
       <c r="A128" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-036</t>
+          <t>MS-API-001</t>
         </is>
       </c>
       <c r="B128" s="25" t="inlineStr">
@@ -16266,7 +16762,7 @@
       </c>
       <c r="P128" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-036 navigation categories API returns public category data</t>
+          <t>MS-API-001 navigation categories API returns public category data</t>
         </is>
       </c>
       <c r="Q128" s="25" t="inlineStr">
@@ -16291,11 +16787,16 @@
       <c r="V128" s="15" t="n"/>
       <c r="W128" s="15" t="n"/>
       <c r="X128" s="15" t="n"/>
+      <c r="Y128" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-036</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="150" customHeight="1">
       <c r="A129" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-037</t>
+          <t>MS-API-002</t>
         </is>
       </c>
       <c r="B129" s="25" t="inlineStr">
@@ -16373,7 +16874,7 @@
       </c>
       <c r="P129" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-037 inquiry types API returns selectable inquiry metadata</t>
+          <t>MS-API-002 inquiry types API returns selectable inquiry metadata</t>
         </is>
       </c>
       <c r="Q129" s="25" t="inlineStr">
@@ -16398,11 +16899,16 @@
       <c r="V129" s="15" t="n"/>
       <c r="W129" s="15" t="n"/>
       <c r="X129" s="15" t="n"/>
+      <c r="Y129" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-037</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="150" customHeight="1">
       <c r="A130" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-038</t>
+          <t>MS-API-003</t>
         </is>
       </c>
       <c r="B130" s="25" t="inlineStr">
@@ -16479,7 +16985,7 @@
       </c>
       <c r="P130" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-038 anonymous user session API rejects unauthenticated users safely</t>
+          <t>MS-API-003 anonymous user session API rejects unauthenticated users safely</t>
         </is>
       </c>
       <c r="Q130" s="25" t="inlineStr">
@@ -16504,11 +17010,16 @@
       <c r="V130" s="15" t="n"/>
       <c r="W130" s="15" t="n"/>
       <c r="X130" s="15" t="n"/>
+      <c r="Y130" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-038</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="150" customHeight="1">
       <c r="A131" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-023</t>
+          <t>MS-UX-001</t>
         </is>
       </c>
       <c r="B131" s="25" t="inlineStr">
@@ -16587,7 +17098,7 @@
       </c>
       <c r="P131" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-023 core controls are named and keyboard reachable</t>
+          <t>MS-UX-001 core controls are named and keyboard reachable</t>
         </is>
       </c>
       <c r="Q131" s="25" t="inlineStr">
@@ -16600,7 +17111,7 @@
       </c>
       <c r="S131" s="25" t="inlineStr">
         <is>
-          <t>Only one Tab press; focus is not checked to reach each control, and search is opened by mouse click, not Enter (test-case.md expects keyboard tabbing through all controls and Enter to open search). The header buttons are found by test id, so their accessible names are not verified here. The axe scan MS-V2-106 is the broader accessibility check.</t>
+          <t>Only one Tab press; focus is not checked to reach each control, and search is opened by mouse click, not Enter (test-case.md expects keyboard tabbing through all controls and Enter to open search). The header buttons are found by test id, so their accessible names are not verified here. The axe scan MS-UX-004 is the broader accessibility check.</t>
         </is>
       </c>
       <c r="T131" s="14" t="inlineStr">
@@ -16612,11 +17123,16 @@
       <c r="V131" s="15" t="n"/>
       <c r="W131" s="15" t="n"/>
       <c r="X131" s="15" t="n"/>
+      <c r="Y131" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-023</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="150" customHeight="1">
       <c r="A132" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-024</t>
+          <t>MS-UX-002</t>
         </is>
       </c>
       <c r="B132" s="25" t="inlineStr">
@@ -16695,7 +17211,7 @@
       </c>
       <c r="P132" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-024 home visual snapshot</t>
+          <t>MS-UX-002 home visual snapshot</t>
         </is>
       </c>
       <c r="Q132" s="25" t="inlineStr">
@@ -16720,11 +17236,16 @@
       <c r="V132" s="15" t="n"/>
       <c r="W132" s="15" t="n"/>
       <c r="X132" s="15" t="n"/>
+      <c r="Y132" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-024</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="150" customHeight="1">
       <c r="A133" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-043</t>
+          <t>MS-UX-003</t>
         </is>
       </c>
       <c r="B133" s="25" t="inlineStr">
@@ -16803,7 +17324,7 @@
       </c>
       <c r="P133" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-043 unknown route serves the 404 page with a working way back home</t>
+          <t>MS-UX-003 unknown route serves the 404 page with a working way back home</t>
         </is>
       </c>
       <c r="Q133" s="25" t="inlineStr">
@@ -16828,11 +17349,16 @@
       <c r="V133" s="15" t="n"/>
       <c r="W133" s="15" t="n"/>
       <c r="X133" s="15" t="n"/>
+      <c r="Y133" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-043</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="150" customHeight="1">
       <c r="A134" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-106</t>
+          <t>MS-UX-004</t>
         </is>
       </c>
       <c r="B134" s="25" t="inlineStr">
@@ -16911,7 +17437,7 @@
       </c>
       <c r="P134" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-106 home has no new WCAG AA violations</t>
+          <t>MS-UX-004 home has no new WCAG AA violations</t>
         </is>
       </c>
       <c r="Q134" s="25" t="inlineStr">
@@ -16936,6 +17462,11 @@
       <c r="V134" s="15" t="n"/>
       <c r="W134" s="15" t="n"/>
       <c r="X134" s="15" t="n"/>
+      <c r="Y134" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-106</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="150" customHeight="1">
       <c r="A135" s="12" t="inlineStr">
@@ -17679,7 +18210,7 @@
     <row r="142" ht="150" customHeight="1">
       <c r="A142" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-001</t>
+          <t>MS-ADMO-001</t>
         </is>
       </c>
       <c r="B142" s="25" t="inlineStr">
@@ -17765,7 +18296,7 @@
       </c>
       <c r="P142" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-001 artwork review, customer proof approval, production and delivery</t>
+          <t>MS-ADMO-001 artwork review, customer proof approval, production and delivery</t>
         </is>
       </c>
       <c r="Q142" s="25" t="inlineStr">
@@ -17802,11 +18333,16 @@
           <t>static-1. Every step has passed on the final code, but across two runs, not one uninterrupted run. Run 1 (AO-2609180003-dev) passed steps 1-7 and failed at step 8 on the redesigned approval dialog; with that fixed, the order was finished by a temporary script that found the other two flow changes (A-FPA label, no Move to Production). Run 2 (AO-2609090017-dev) with the updated spec passed steps 1-10 and failed at step 11 on the new no-results state of the order search; with that fixed, steps 11-12 passed against the same order. One seed order is left (AO-2609070006-dev) for a single clean run.</t>
         </is>
       </c>
+      <c r="Y142" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-001</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="150" customHeight="1">
       <c r="A143" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-007</t>
+          <t>MS-ADMO-002</t>
         </is>
       </c>
       <c r="B143" s="25" t="inlineStr">
@@ -17910,11 +18446,16 @@
       <c r="V143" s="15" t="n"/>
       <c r="W143" s="15" t="n"/>
       <c r="X143" s="15" t="n"/>
+      <c r="Y143" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-007</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="150" customHeight="1">
       <c r="A144" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-008</t>
+          <t>MS-ADMO-003</t>
         </is>
       </c>
       <c r="B144" s="25" t="inlineStr">
@@ -18017,11 +18558,16 @@
       <c r="V144" s="15" t="n"/>
       <c r="W144" s="15" t="n"/>
       <c r="X144" s="15" t="n"/>
+      <c r="Y144" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-008</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="150" customHeight="1">
       <c r="A145" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-009</t>
+          <t>MS-ADMO-004</t>
         </is>
       </c>
       <c r="B145" s="25" t="inlineStr">
@@ -18113,7 +18659,7 @@
       </c>
       <c r="S145" s="25" t="inlineStr">
         <is>
-          <t>Partly covered inside MS-ADM-001; this case isolates the rejection loop for quicker regression. Emails the member.</t>
+          <t>Partly covered inside MS-ADMO-001; this case isolates the rejection loop for quicker regression. Emails the member.</t>
         </is>
       </c>
       <c r="T145" s="14" t="inlineStr">
@@ -18125,11 +18671,16 @@
       <c r="V145" s="15" t="n"/>
       <c r="W145" s="15" t="n"/>
       <c r="X145" s="15" t="n"/>
+      <c r="Y145" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-009</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="150" customHeight="1">
       <c r="A146" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-010</t>
+          <t>MS-ADMO-005</t>
         </is>
       </c>
       <c r="B146" s="25" t="inlineStr">
@@ -18233,11 +18784,16 @@
       <c r="V146" s="15" t="n"/>
       <c r="W146" s="15" t="n"/>
       <c r="X146" s="15" t="n"/>
+      <c r="Y146" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-010</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="150" customHeight="1">
       <c r="A147" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-011</t>
+          <t>MS-ADMO-006</t>
         </is>
       </c>
       <c r="B147" s="25" t="inlineStr">
@@ -18340,11 +18896,16 @@
       <c r="V147" s="15" t="n"/>
       <c r="W147" s="15" t="n"/>
       <c r="X147" s="15" t="n"/>
+      <c r="Y147" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-011</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="150" customHeight="1">
       <c r="A148" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-012</t>
+          <t>MS-ADMO-007</t>
         </is>
       </c>
       <c r="B148" s="25" t="inlineStr">
@@ -18448,11 +19009,16 @@
       <c r="V148" s="15" t="n"/>
       <c r="W148" s="15" t="n"/>
       <c r="X148" s="15" t="n"/>
+      <c r="Y148" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-012</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="150" customHeight="1">
       <c r="A149" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-013</t>
+          <t>MS-ADMO-008</t>
         </is>
       </c>
       <c r="B149" s="25" t="inlineStr">
@@ -18555,11 +19121,16 @@
       <c r="V149" s="15" t="n"/>
       <c r="W149" s="15" t="n"/>
       <c r="X149" s="15" t="n"/>
+      <c r="Y149" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-013</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="150" customHeight="1">
       <c r="A150" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-014</t>
+          <t>MS-ADMO-009</t>
         </is>
       </c>
       <c r="B150" s="25" t="inlineStr">
@@ -18661,11 +19232,16 @@
       <c r="V150" s="15" t="n"/>
       <c r="W150" s="15" t="n"/>
       <c r="X150" s="15" t="n"/>
+      <c r="Y150" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-014</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="150" customHeight="1">
       <c r="A151" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-015</t>
+          <t>MS-ADMO-010</t>
         </is>
       </c>
       <c r="B151" s="25" t="inlineStr">
@@ -18756,7 +19332,7 @@
       </c>
       <c r="S151" s="25" t="inlineStr">
         <is>
-          <t>MUS-QA-004 fixed by 2026-10-14: the popup used to promise '제작 진행'; it now says 제작 대기, matching the behaviour. Covered end to end by MS-ADM-001 step 8. After approval the customer sees a cancellation notice citing a payment adjustment (MUS-QA-011).</t>
+          <t>MUS-QA-004 fixed by 2026-10-14: the popup used to promise '제작 진행'; it now says 제작 대기, matching the behaviour. Covered end to end by MS-ADMO-001 step 8. After approval the customer sees a cancellation notice citing a payment adjustment (MUS-QA-011).</t>
         </is>
       </c>
       <c r="T151" s="14" t="inlineStr">
@@ -18768,11 +19344,16 @@
       <c r="V151" s="15" t="n"/>
       <c r="W151" s="15" t="n"/>
       <c r="X151" s="15" t="n"/>
+      <c r="Y151" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-015</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="150" customHeight="1">
       <c r="A152" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-016</t>
+          <t>MS-ADMO-011</t>
         </is>
       </c>
       <c r="B152" s="25" t="inlineStr">
@@ -18863,7 +19444,7 @@
       </c>
       <c r="S152" s="25" t="inlineStr">
         <is>
-          <t>withdrawn 2026-10-14: Move to Production no longer exists on static-1. Mark as Printing (MS-ADM-017) is now the first staff action after approval and moves the order to 제작 진행 중 itself; the 주문 준비 중 (PO) stage is no longer reached. Keep the ID; do not reuse it.</t>
+          <t>withdrawn 2026-10-14: Move to Production no longer exists on static-1. Mark as Printing (MS-ADMO-012) is now the first staff action after approval and moves the order to 제작 진행 중 itself; the 주문 준비 중 (PO) stage is no longer reached. Keep the ID; do not reuse it.</t>
         </is>
       </c>
       <c r="T152" s="14" t="inlineStr">
@@ -18875,11 +19456,16 @@
       <c r="V152" s="15" t="n"/>
       <c r="W152" s="15" t="n"/>
       <c r="X152" s="15" t="n"/>
+      <c r="Y152" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-016</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="150" customHeight="1">
       <c r="A153" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-017</t>
+          <t>MS-ADMO-012</t>
         </is>
       </c>
       <c r="B153" s="25" t="inlineStr">
@@ -18982,11 +19568,16 @@
       <c r="V153" s="15" t="n"/>
       <c r="W153" s="15" t="n"/>
       <c r="X153" s="15" t="n"/>
+      <c r="Y153" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-017</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="150" customHeight="1">
       <c r="A154" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-018</t>
+          <t>MS-ADMO-013</t>
         </is>
       </c>
       <c r="B154" s="25" t="inlineStr">
@@ -19089,11 +19680,16 @@
       <c r="V154" s="15" t="n"/>
       <c r="W154" s="15" t="n"/>
       <c r="X154" s="15" t="n"/>
+      <c r="Y154" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-018</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="150" customHeight="1">
       <c r="A155" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-019</t>
+          <t>MS-ADMO-014</t>
         </is>
       </c>
       <c r="B155" s="25" t="inlineStr">
@@ -19195,11 +19791,16 @@
       <c r="V155" s="15" t="n"/>
       <c r="W155" s="15" t="n"/>
       <c r="X155" s="15" t="n"/>
+      <c r="Y155" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-019</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="150" customHeight="1">
       <c r="A156" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-020</t>
+          <t>MS-ADMO-015</t>
         </is>
       </c>
       <c r="B156" s="25" t="inlineStr">
@@ -19302,11 +19903,16 @@
       <c r="V156" s="15" t="n"/>
       <c r="W156" s="15" t="n"/>
       <c r="X156" s="15" t="n"/>
+      <c r="Y156" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-020</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="150" customHeight="1">
       <c r="A157" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-021</t>
+          <t>MS-ADMO-016</t>
         </is>
       </c>
       <c r="B157" s="25" t="inlineStr">
@@ -19407,11 +20013,16 @@
       <c r="V157" s="15" t="n"/>
       <c r="W157" s="15" t="n"/>
       <c r="X157" s="15" t="n"/>
+      <c r="Y157" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-021</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="150" customHeight="1">
       <c r="A158" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-025</t>
+          <t>MS-ADMO-017</t>
         </is>
       </c>
       <c r="B158" s="25" t="inlineStr">
@@ -19513,11 +20124,16 @@
       <c r="V158" s="15" t="n"/>
       <c r="W158" s="15" t="n"/>
       <c r="X158" s="15" t="n"/>
+      <c r="Y158" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-025</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="150" customHeight="1">
       <c r="A159" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-027</t>
+          <t>MS-ADMO-018</t>
         </is>
       </c>
       <c r="B159" s="25" t="inlineStr">
@@ -19619,11 +20235,16 @@
       <c r="V159" s="15" t="n"/>
       <c r="W159" s="15" t="n"/>
       <c r="X159" s="15" t="n"/>
+      <c r="Y159" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-027</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="150" customHeight="1">
       <c r="A160" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-002</t>
+          <t>MS-ADMA-001</t>
         </is>
       </c>
       <c r="B160" s="25" t="inlineStr">
@@ -19727,11 +20348,16 @@
       <c r="V160" s="15" t="n"/>
       <c r="W160" s="15" t="n"/>
       <c r="X160" s="15" t="n"/>
+      <c r="Y160" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-002</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="150" customHeight="1">
       <c r="A161" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-003</t>
+          <t>MS-ADMA-002</t>
         </is>
       </c>
       <c r="B161" s="25" t="inlineStr">
@@ -19836,11 +20462,16 @@
       <c r="V161" s="15" t="n"/>
       <c r="W161" s="15" t="n"/>
       <c r="X161" s="15" t="n"/>
+      <c r="Y161" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-003</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="150" customHeight="1">
       <c r="A162" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-004</t>
+          <t>MS-ADMA-003</t>
         </is>
       </c>
       <c r="B162" s="25" t="inlineStr">
@@ -19943,11 +20574,16 @@
       <c r="V162" s="15" t="n"/>
       <c r="W162" s="15" t="n"/>
       <c r="X162" s="15" t="n"/>
+      <c r="Y162" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-004</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="150" customHeight="1">
       <c r="A163" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-005</t>
+          <t>MS-ADMA-004</t>
         </is>
       </c>
       <c r="B163" s="25" t="inlineStr">
@@ -20052,11 +20688,16 @@
       <c r="V163" s="15" t="n"/>
       <c r="W163" s="15" t="n"/>
       <c r="X163" s="15" t="n"/>
+      <c r="Y163" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-005</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="150" customHeight="1">
       <c r="A164" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-006</t>
+          <t>MS-ADMA-005</t>
         </is>
       </c>
       <c r="B164" s="25" t="inlineStr">
@@ -20159,11 +20800,16 @@
       <c r="V164" s="15" t="n"/>
       <c r="W164" s="15" t="n"/>
       <c r="X164" s="15" t="n"/>
+      <c r="Y164" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-006</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="150" customHeight="1">
       <c r="A165" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-022</t>
+          <t>MS-ADMA-006</t>
         </is>
       </c>
       <c r="B165" s="25" t="inlineStr">
@@ -20198,7 +20844,7 @@
       </c>
       <c r="H165" s="25" t="inlineStr">
         <is>
-          <t>Admin panel static-1 (https://dev-static-1-admin-panel.musticker.com) signed in with a staff account. A test order taken through the lifecycle (e.g. after MS-ADM-001).</t>
+          <t>Admin panel static-1 (https://dev-static-1-admin-panel.musticker.com) signed in with a staff account. A test order taken through the lifecycle (e.g. after MS-ADMO-001).</t>
         </is>
       </c>
       <c r="I165" s="25" t="inlineStr">
@@ -20253,7 +20899,7 @@
       </c>
       <c r="S165" s="25" t="inlineStr">
         <is>
-          <t>Known defect 2026-09-25: the activity log records staff actions (Mark as Printing, tracking add/send/update; re-confirmed 2026-10-14) as the customer (user.is_admin=false). As of 2026-10-14 staff evaluation and proof entries (CA, FE, PE, NA) are correctly is_admin=true; printing and shipping entries (P, RS, OD, DE) are not. Audit-trail integrity issue; MS-ADM-001 deliberately asserts attribution only on customer steps until fixed.</t>
+          <t>Known defect 2026-09-25: the activity log records staff actions (Mark as Printing, tracking add/send/update; re-confirmed 2026-10-14) as the customer (user.is_admin=false). As of 2026-10-14 staff evaluation and proof entries (CA, FE, PE, NA) are correctly is_admin=true; printing and shipping entries (P, RS, OD, DE) are not. Audit-trail integrity issue; MS-ADMO-001 deliberately asserts attribution only on customer steps until fixed.</t>
         </is>
       </c>
       <c r="T165" s="14" t="inlineStr">
@@ -20265,11 +20911,16 @@
       <c r="V165" s="15" t="n"/>
       <c r="W165" s="15" t="n"/>
       <c r="X165" s="15" t="n"/>
+      <c r="Y165" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-022</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="150" customHeight="1">
       <c r="A166" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-023</t>
+          <t>MS-ADMA-007</t>
         </is>
       </c>
       <c r="B166" s="25" t="inlineStr">
@@ -20373,11 +21024,16 @@
       <c r="V166" s="15" t="n"/>
       <c r="W166" s="15" t="n"/>
       <c r="X166" s="15" t="n"/>
+      <c r="Y166" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-023</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="150" customHeight="1">
       <c r="A167" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-024</t>
+          <t>MS-ADMA-008</t>
         </is>
       </c>
       <c r="B167" s="25" t="inlineStr">
@@ -20479,11 +21135,16 @@
       <c r="V167" s="15" t="n"/>
       <c r="W167" s="15" t="n"/>
       <c r="X167" s="15" t="n"/>
+      <c r="Y167" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-024</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="150" customHeight="1">
       <c r="A168" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-026</t>
+          <t>MS-ADMA-009</t>
         </is>
       </c>
       <c r="B168" s="25" t="inlineStr">
@@ -20586,11 +21247,16 @@
       <c r="V168" s="15" t="n"/>
       <c r="W168" s="15" t="n"/>
       <c r="X168" s="15" t="n"/>
+      <c r="Y168" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-026</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="150" customHeight="1">
       <c r="A169" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-028</t>
+          <t>MS-ADMA-010</t>
         </is>
       </c>
       <c r="B169" s="25" t="inlineStr">
@@ -20688,11 +21354,16 @@
       <c r="V169" s="15" t="n"/>
       <c r="W169" s="15" t="n"/>
       <c r="X169" s="15" t="n"/>
+      <c r="Y169" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-028</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="150" customHeight="1">
       <c r="A170" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-029</t>
+          <t>MS-ADMA-011</t>
         </is>
       </c>
       <c r="B170" s="25" t="inlineStr">
@@ -20795,11 +21466,16 @@
       <c r="V170" s="15" t="n"/>
       <c r="W170" s="15" t="n"/>
       <c r="X170" s="15" t="n"/>
+      <c r="Y170" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-029</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="150" customHeight="1">
       <c r="A171" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-030</t>
+          <t>MS-ADMA-012</t>
         </is>
       </c>
       <c r="B171" s="25" t="inlineStr">
@@ -20901,11 +21577,16 @@
       <c r="V171" s="15" t="n"/>
       <c r="W171" s="15" t="n"/>
       <c r="X171" s="15" t="n"/>
+      <c r="Y171" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-030</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="150" customHeight="1">
       <c r="A172" s="12" t="inlineStr">
         <is>
-          <t>MS-ADM-031</t>
+          <t>MS-ADMA-013</t>
         </is>
       </c>
       <c r="B172" s="25" t="inlineStr">
@@ -20940,7 +21621,7 @@
       </c>
       <c r="H172" s="25" t="inlineStr">
         <is>
-          <t>Seeded member signed in on static-1 storefront; a test order at 주문 완료 (e.g. after MS-ADM-001).</t>
+          <t>Seeded member signed in on static-1 storefront; a test order at 주문 완료 (e.g. after MS-ADMO-001).</t>
         </is>
       </c>
       <c r="I172" s="25" t="inlineStr">
@@ -21007,11 +21688,16 @@
       <c r="V172" s="15" t="n"/>
       <c r="W172" s="15" t="n"/>
       <c r="X172" s="15" t="n"/>
+      <c r="Y172" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-ADM-031</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="150" customHeight="1">
       <c r="A173" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-115</t>
+          <t>MS-CFG-026</t>
         </is>
       </c>
       <c r="B173" s="25" t="inlineStr">
@@ -21088,7 +21774,7 @@
       </c>
       <c r="P173" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-115 다음 단계 offers three ways to order: with a file, in the studio, or file later</t>
+          <t>MS-CFG-026 다음 단계 offers three ways to order: with a file, in the studio, or file later</t>
         </is>
       </c>
       <c r="Q173" s="25" t="inlineStr">
@@ -21113,11 +21799,16 @@
       <c r="V173" s="15" t="n"/>
       <c r="W173" s="15" t="n"/>
       <c r="X173" s="15" t="n"/>
+      <c r="Y173" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-115</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="150" customHeight="1">
       <c r="A174" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-116</t>
+          <t>MS-CFG-027</t>
         </is>
       </c>
       <c r="B174" s="25" t="inlineStr">
@@ -21196,7 +21887,7 @@
       </c>
       <c r="P174" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-116 the studio keeps the configured size and quantity and prices every tier 5% below the configurator</t>
+          <t>MS-CFG-027 the studio keeps the configured size and quantity and prices every tier 5% below the configurator</t>
         </is>
       </c>
       <c r="Q174" s="25" t="inlineStr">
@@ -21221,11 +21912,16 @@
       <c r="V174" s="15" t="n"/>
       <c r="W174" s="15" t="n"/>
       <c r="X174" s="15" t="n"/>
+      <c r="Y174" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-116</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="150" customHeight="1">
       <c r="A175" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-117</t>
+          <t>MS-CFG-028</t>
         </is>
       </c>
       <c r="B175" s="25" t="inlineStr">
@@ -21270,7 +21966,7 @@
       </c>
       <c r="J175" s="25" t="inlineStr">
         <is>
-          <t>1. Open the studio for 자유형 조각스티커 at 중형 75x75 / 100개 (as MS-V2-116).
+          <t>1. Open the studio for 자유형 조각스티커 at 중형 75x75 / 100개 (as MS-CFG-027).
 2. Check 장바구니 담기 before attaching anything.
 3. Click 이미지 첨부하기 and choose qa-proof.png.
 4. Open a fresh studio the same way and attach studio-design.png.</t>
@@ -21303,7 +21999,7 @@
       </c>
       <c r="P175" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-117 the studio refuses a low-resolution design and accepts a print-quality one</t>
+          <t>MS-CFG-028 the studio refuses a low-resolution design and accepts a print-quality one</t>
         </is>
       </c>
       <c r="Q175" s="25" t="inlineStr">
@@ -21328,11 +22024,16 @@
       <c r="V175" s="15" t="n"/>
       <c r="W175" s="15" t="n"/>
       <c r="X175" s="15" t="n"/>
+      <c r="Y175" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-117</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="150" customHeight="1">
       <c r="A176" s="12" t="inlineStr">
         <is>
-          <t>MS-V2-118</t>
+          <t>MS-CFG-029</t>
         </is>
       </c>
       <c r="B176" s="25" t="inlineStr">
@@ -21377,7 +22078,7 @@
       </c>
       <c r="J176" s="25" t="inlineStr">
         <is>
-          <t>1. Open the studio with a print-quality design attached (MS-V2-117 step 4).
+          <t>1. Open the studio with a print-quality design attached (MS-CFG-028 step 4).
 2. Click 장바구니 담기.
 3. In 주문 준비 완료, wait for the preview, look through the 미리보기 대상 scenes, choose 재단 방식 (통재단 / 도무송).
 4. Tick 네, 확인했어요! and click 장바구니 담기.
@@ -21436,9 +22137,14 @@
       <c r="V176" s="15" t="n"/>
       <c r="W176" s="15" t="n"/>
       <c r="X176" s="15" t="n"/>
+      <c r="Y176" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MS-V2-118</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X176"/>
+  <autoFilter ref="A1:Y176"/>
   <dataValidations count="3">
     <dataValidation sqref="T2:T176" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Partial,N/A"</formula1>
@@ -21705,7 +22411,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>ADMIN SEED ORDERS (MS-ADM-001, static-1)</t>
+          <t>ADMIN SEED ORDERS (MS-ADMO-001, static-1)</t>
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
@@ -21769,12 +22475,12 @@
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>exploration 2026-09-25; MS-ADM-001 2026-10-14; other testers</t>
+          <t>exploration 2026-09-25; MS-ADMO-001 2026-10-14; other testers</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>AO-2609240008/2609250005: walked by hand 2026-09-25. AO-2609180003/2609090017: MS-ADM-001 runs 2026-10-14. AO-2609180004: found at 승인 대기 on 2026-10-14 (used by someone else). Not usable: AO-2609070004-dev and AO-2609070005-dev have two items each.</t>
+          <t>AO-2609240008/2609250005: walked by hand 2026-09-25. AO-2609180003/2609090017: MS-ADMO-001 runs 2026-10-14. AO-2609180004: found at 승인 대기 on 2026-10-14 (used by someone else). Not usable: AO-2609070004-dev and AO-2609070005-dev have two items each.</t>
         </is>
       </c>
     </row>
@@ -21828,7 +22534,7 @@
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-098 / 099.</t>
+          <t>MS-CHK-005 / MS-CHK-006.</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22713,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Verified by hand on static-1 (dev-static-1) on 2026-09-25 (AO-2609240008-dev, AO-2609250005-dev) and re-checked by MS-ADM-001 on 2026-10-14 (AO-2609180003-dev, AO-2609090017-dev). The reference when a case and the product disagree.</t>
+          <t>Verified by hand on static-1 (dev-static-1) on 2026-09-25 (AO-2609240008-dev, AO-2609250005-dev) and re-checked by MS-ADMO-001 on 2026-10-14 (AO-2609180003-dev, AO-2609090017-dev). The reference when a case and the product disagree.</t>
         </is>
       </c>
     </row>
@@ -24670,7 +25376,7 @@
       </c>
       <c r="C2" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-022</t>
+          <t>MS-ADMA-006</t>
         </is>
       </c>
       <c r="D2" s="25" t="inlineStr">
@@ -24755,7 +25461,7 @@
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-024</t>
+          <t>MS-ADMA-008</t>
         </is>
       </c>
       <c r="D3" s="25" t="inlineStr">
@@ -24840,7 +25546,7 @@
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-021</t>
+          <t>MS-ADMO-016</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
@@ -24925,7 +25631,7 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-015</t>
+          <t>MS-ADMO-010</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
@@ -25016,7 +25722,7 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-008</t>
+          <t>MS-ADMO-003</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
@@ -25102,7 +25808,7 @@
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-030</t>
+          <t>MS-ADMA-012</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
@@ -25187,7 +25893,7 @@
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-031</t>
+          <t>MS-ADMA-013</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
@@ -25276,7 +25982,7 @@
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-007</t>
+          <t>MS-ADMO-002</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
@@ -25361,7 +26067,7 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-109</t>
+          <t>MS-ACC-003</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
@@ -25446,7 +26152,7 @@
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-020</t>
+          <t>MS-ADMO-015</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
@@ -25502,7 +26208,7 @@
       </c>
       <c r="N11" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-001 run (automation)</t>
+          <t>MS-ADMO-001 run (automation)</t>
         </is>
       </c>
       <c r="O11" s="25" t="inlineStr">
@@ -25531,7 +26237,7 @@
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-015</t>
+          <t>MS-ADMO-010</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
@@ -25587,7 +26293,7 @@
       </c>
       <c r="N12" s="25" t="inlineStr">
         <is>
-          <t>MS-ADM-001 run (automation)</t>
+          <t>MS-ADMO-001 run (automation)</t>
         </is>
       </c>
       <c r="O12" s="25" t="inlineStr">
@@ -25616,7 +26322,7 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-003</t>
+          <t>MS-NAV-003</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
@@ -25701,7 +26407,7 @@
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-009</t>
+          <t>MS-CFG-001</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
@@ -25786,7 +26492,7 @@
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-009</t>
+          <t>MS-CFG-001</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
@@ -25871,7 +26577,7 @@
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-118</t>
+          <t>MS-CFG-029</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
@@ -25956,7 +26662,7 @@
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-002</t>
+          <t>MS-NAV-002</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
@@ -26041,7 +26747,7 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-009</t>
+          <t>MS-CFG-001</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
@@ -26126,7 +26832,7 @@
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-116</t>
+          <t>MS-CFG-027</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
@@ -26211,7 +26917,7 @@
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>MS-V2-106</t>
+          <t>MS-UX-004</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
@@ -26372,7 +27078,7 @@
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>MUS-QA-001 to 009 were found by exploratory testing on 2026-09-25 while building the admin suite, MUS-QA-010 and 011 by the MS-ADM-001 run on 2026-10-14, and MUS-QA-012 to 020 by storefront exploration the same day. Evidence gives order numbers and times so dev can find the records. Add new defects below; keep IDs sequential.</t>
+          <t>MUS-QA-001 to 009 were found by exploratory testing on 2026-09-25 while building the admin suite, MUS-QA-010 and 011 by the MS-ADMO-001 run on 2026-10-14, and MUS-QA-012 to 020 by storefront exploration the same day. Evidence gives order numbers and times so dev can find the records. Add new defects below; keep IDs sequential.</t>
         </is>
       </c>
     </row>
@@ -26402,7 +27108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -26426,299 +27132,298 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14 - workbook v1.1, MS-ADM-001 re-run, storefront explored</t>
+          <t xml:space="preserve">2026-10-14 - workbook v1.2, module-based TC IDs</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38.25" customHeight="1">
       <c r="A5" s="28" t="inlineStr">
         <is>
-          <t>MS-ADM-001</t>
+          <t xml:space="preserve">TC IDs</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Re-run on static-1 (AO-2609180003-dev, AO-2609090017-dev) and updated for four product changes: the proof-approval dialog needs an acknowledgement tick before 최종 시안 승인; A-FPA is labelled 최종 승인 완료; Move to Production is gone, so Mark as Printing moves the order to 제작 진행 중 and the item straight to 인쇄 진행 중 (no PO); completed orders moved to 이전 내역, and an order search with no match shows 주문을 찾을 수 없습니다. Every step passes on the updated code (see Tester Notes on the case).</t>
+          <t xml:space="preserve">MS-V2-### and MS-ADM-### are replaced by MS-&lt;MODULE&gt;-###, so an ID names its module (the Area): NAV, DSC, CFG, SHT, CRT, CHK, AUTH, ACC, INQ, API, UX, ADMO (admin order processing) and ADMA (admin access &amp; order management), numbered 001 upward in workbook order. MS-PRC-*, MS-SEC-* and MS-WAF-* are unchanged. 140 cases renamed.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38.25" customHeight="1">
       <c r="A6" s="28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Legacy ID</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New column Y keeps each renamed case's previous ID. Older entries in this changelog, past Allure history and defect evidence still use the old IDs; look them up in that column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38.25" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suite</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Playwright test titles, comments, fixtures and docs renamed to match (178 test titles; no test logic changed; still 2,473 tests). Defect Log TC IDs and the cross-references in the other tabs updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14 - workbook v1.1, MS-ADM-001 re-run, storefront explored</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38.25" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>MS-ADM-001</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Re-run on static-1 (AO-2609180003-dev, AO-2609090017-dev) and updated for four product changes: the proof-approval dialog needs an acknowledgement tick before 최종 시안 승인; A-FPA is labelled 최종 승인 완료; Move to Production is gone, so Mark as Printing moves the order to 제작 진행 중 and the item straight to 인쇄 진행 중 (no PO); completed orders moved to 이전 내역, and an order search with no match shows 주문을 찾을 수 없습니다. Every step passes on the updated code (see Tester Notes on the case).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38.25" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
           <t>Admin recording</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>A failed run showed that Playwright's failure screenshot and error context capture every open page, the admin panel included - the suite promised they did not. Admin specs now turn screenshots and traces off, and the adminPage fixture refuses to start otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25.5" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>Cases</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>MS-ADM-016 (Move to Production) withdrawn. MS-ADM-006, 013, 014, 015, 017, 020, 022, 030 and 031 updated to the new flow; Business Rules and Glossary likewise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>Defects</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>MUS-QA-004 and MUS-QA-007 retested as fixed. MUS-QA-001 still reproduces for the printing and shipping entries. New: MUS-QA-010 and MUS-QA-011 (Low, to confirm).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Environments</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Instructions, gating, the Test Plan, Test Data and pricing ids now use the current environment names (static-1..8; development-1..4 retired and development-static/-static-2 renamed on 2026-09-25), and the CI schedule no longer lists the removed nightly regression. Historical "verified on development-N" notes are kept as they were.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>Seed orders</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Re-checked on 2026-10-14: AO-2609180004-dev had been used elsewhere and AO-2609070004/0005-dev have two items, so one unused candidate is left (AO-2609070006-dev).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Admin login</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>dev-static-1 has a tester OTP endpoint that returns the admin verification code; noted under MS-ADM-002 as a way to run admin cases without a person. Not used by the suite yet.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1">
       <c r="A12" s="28" t="inlineStr">
         <is>
-          <t>Storefront run</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Production-safe storefront specs (pricing excluded) before the updates: production 132 passed / 27 failed / 5 flaky; static-1 131 / 28 / 5. After: production 162 passed, 2 failed and 3 flaky (a tier-price repaint race, fixed and then 32/32 twice; transient 502s), 5 skipped; static-1 165 passed, 0 failed, 2 flaky (a network blip; MS-V2-035's timeout, now 90 s and passing on both), 5 skipped. Pricing on production: 261 of 2,286 failed, all on the replaced lettering and transfer tables; after the re-export 272/272 for those two and the other 2,016 unchanged and passing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25.5" customHeight="1">
+          <t>MS-ADM-016 (Move to Production) withdrawn. MS-ADM-006, 013, 014, 015, 017, 020, 022, 030 and 031 updated to the new flow; Business Rules and Glossary likewise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="28" t="inlineStr">
         <is>
-          <t>Order chooser</t>
+          <t>Defects</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>다음 단계 now opens 어떻게 주문하시겠어요? (with a file / in the studio / file later), live on production. MS-V2-050 and 053 updated; new MS-V2-115.</t>
+          <t>MUS-QA-004 and MUS-QA-007 retested as fixed. MUS-QA-001 still reproduces for the printing and shipping entries. New: MUS-QA-010 and MUS-QA-011 (Low, to confirm).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="28" t="inlineStr">
         <is>
-          <t>Design studio</t>
+          <t>Environments</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>New web studio (?studio=1): carries size and quantity over, prices 5% lower, refuses low-resolution designs. New MS-V2-116 and 117 (automated, production-safe) and MS-V2-118 (planned: add-to-cart blocked by MUS-QA-015). New fixture studio-design.png.</t>
+          <t>Instructions, gating, the Test Plan, Test Data and pricing ids now use the current environment names (static-1..8; development-1..4 retired and development-static/-static-2 renamed on 2026-09-25), and the CI schedule no longer lists the removed nightly regression. Historical "verified on development-N" notes are kept as they were.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="28" t="inlineStr">
         <is>
-          <t>Header and footer</t>
+          <t>Seed orders</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Nav items open a product menu instead of the category page (MS-V2-002 rewritten, MS-V2-035 updated); the footer was redesigned (MS-V2-001, 020, 039).</t>
+          <t>Re-checked on 2026-10-14: AO-2609180004-dev had been used elsewhere and AO-2609070004/0005-dev have two items, so one unused candidate is left (AO-2609070006-dev).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="28" t="inlineStr">
         <is>
-          <t>Copy and options</t>
+          <t>Admin login</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>PVC 매트 is now 무광 화이트; sheet stickers show a discount on every tier (MS-V2-052 rewritten); rounded-roll, rounded-sheet and transfer H1s renamed back; production's category cards reverted to pre-rename names (MUS-QA-016).</t>
+          <t>dev-static-1 has a tester OTP endpoint that returns the admin verification code; noted under MS-ADM-002 as a way to run admin cases without a person. Not used by the suite yet.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
-          <t>Suite fixes</t>
+          <t>Storefront run</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>selectSize waits for the size re-quote (stale tier prices failed the money-path tests); quantity tiers match the whole number (5 had been picking 50시트); category menu and review carousel clicks wait for Nuxt hydration (new waitForNuxtHydration); addToCart handles both the chooser and the older upload dialog (풀 컬러 레터링); the unused-preload warning is benign on every first-party host; new allowStudioModelLoadNoise guard option.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+          <t>Production-safe storefront specs (pricing excluded) before the updates: production 132 passed / 27 failed / 5 flaky; static-1 131 / 28 / 5. After: production 162 passed, 2 failed and 3 flaky (a tier-price repaint race, fixed and then 32/32 twice; transient 502s), 5 skipped; static-1 165 passed, 0 failed, 2 flaky (a network blip; MS-V2-035's timeout, now 90 s and passing on both), 5 skipped. Pricing on production: 261 of 2,286 failed, all on the replaced lettering and transfer tables; after the re-export 272/272 for those two and the other 2,016 unchanged and passing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25.5" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>Order chooser</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Production replaced the vinyl-lettering and transfer-sticker tables on 2026-09-29 (ids 69 and 72; same rates on rungs 1-300, new rungs 500-5,000): CSVs re-exported, registry updated, now production-only baselines. The known interpolation overcharge checks are pinned to their quantities (the longer ladder had moved the sampled quantity off them and hidden that the overcharge is still live). Pricing now 2,288 tests.</t>
+          <t>다음 단계 now opens 어떻게 주문하시겠어요? (with a file / in the studio / file later), live on production. MS-V2-050 and 053 updated; new MS-V2-115.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="28" t="inlineStr">
         <is>
+          <t>Design studio</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>New web studio (?studio=1): carries size and quantity over, prices 5% lower, refuses low-resolution designs. New MS-V2-116 and 117 (automated, production-safe) and MS-V2-118 (planned: add-to-cart blocked by MUS-QA-015). New fixture studio-design.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Header and footer</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Nav items open a product menu instead of the category page (MS-V2-002 rewritten, MS-V2-035 updated); the footer was redesigned (MS-V2-001, 020, 039).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Copy and options</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>PVC 매트 is now 무광 화이트; sheet stickers show a discount on every tier (MS-V2-052 rewritten); rounded-roll, rounded-sheet and transfer H1s renamed back; production's category cards reverted to pre-rename names (MUS-QA-016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25.5" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Suite fixes</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>selectSize waits for the size re-quote (stale tier prices failed the money-path tests); quantity tiers match the whole number (5 had been picking 50시트); category menu and review carousel clicks wait for Nuxt hydration (new waitForNuxtHydration); addToCart handles both the chooser and the older upload dialog (풀 컬러 레터링); the unused-preload warning is benign on every first-party host; new allowStudioModelLoadNoise guard option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Production replaced the vinyl-lettering and transfer-sticker tables on 2026-09-29 (ids 69 and 72; same rates on rungs 1-300, new rungs 500-5,000): CSVs re-exported, registry updated, now production-only baselines. The known interpolation overcharge checks are pinned to their quantities (the longer ladder had moved the sampled quantity off them and hidden that the overcharge is still live). Pricing now 2,288 tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
           <t>Storefront defects</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>MUS-QA-012 to 020 logged (search button name, /dev/ assets on production, page weight, studio confirmation lock, pre-rename names, English FAQ on static-1, size-range mismatch, selection state not exposed, lettering 500-rung rate).</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>2026-09-25 - workbook v1, suite reorganised</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Workbook</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>This workbook replaces test-case.md as the test case source. Steps and expected results were re-derived from the spec code (the code is the source of truth); where test-case.md described more than the code checks, the case says so in Reference Notes, and three cases are marked Partial (MS-V2-012, 017, 018).</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Admin panel</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Added the admin panel to the suite: MS-ADM-001 (storefront-to-admin order processing: design upload, rejection and resubmission, pass, proof, customer approval, production, printing, shipping, delivery) plus planned admin cases (MS-ADM-002 onward).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Folders</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Specs moved to tests/e2e/storefront/&lt;area&gt;/ and tests/e2e/admin/&lt;area&gt;/; page objects to tests/pom/storefront/ and tests/pom/admin/. Same 2,468 tests before and after (verified by comparing the test lists).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>New docs/RUNNING.md, docs/ARCHITECTURE.md, docs/CONVENTIONS.md; README.md is now a short entry point.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Defects</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Nine defects/questions from exploratory testing logged (MUS-QA-001 to 009).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>KNOWN SUITE ISSUES (not product defects)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>dev-static-1 checkout</t>
+          <t>Folders</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare check before payment blocks automated browsers; guest checkout there shows no OTP popup on email blur. MS-V2-025 is verified on development-3 only.</t>
+          <t>Specs moved to tests/e2e/storefront/&lt;area&gt;/ and tests/e2e/admin/&lt;area&gt;/; page objects to tests/pom/storefront/ and tests/pom/admin/. Same 2,468 tests before and after (verified by comparing the test lists).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Upload dialog (dev-static-1)</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>The product upload dialog button is now 파일로 주문하기 and the file-type copy reads 'ai · psd · pdf · eps · tif · png · jpg'. ProductV2Page.expectDesignUploadModal and MS-V2-053 will fail when this reaches production - update storefront-data.ts then.</t>
+          <t>New docs/RUNNING.md, docs/ARCHITECTURE.md, docs/CONVENTIONS.md; README.md is now a short entry point.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>MS-V2-058</t>
+          <t>Defects</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Marked test.fixme (known alt-text defect on the size guide); skipped until fixed.</t>
+          <t>Nine defects/questions from exploratory testing logged (MUS-QA-001 to 009).</t>
         </is>
       </c>
     </row>
@@ -26726,17 +27431,61 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 - test-case.md v1</t>
+          <t>KNOWN SUITE ISSUES (not product defects)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>dev-static-1 checkout</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Cloudflare check before payment blocks automated browsers; guest checkout there shows no OTP popup on email blur. MS-V2-025 is verified on development-3 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Upload dialog (dev-static-1)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>The product upload dialog button is now 파일로 주문하기 and the file-type copy reads 'ai · psd · pdf · eps · tif · png · jpg'. ProductV2Page.expectDesignUploadModal and MS-V2-053 will fail when this reaches production - update storefront-data.ts then.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>MS-V2-058</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Marked test.fixme (known alt-text defect on the size guide); skipped until fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 - test-case.md v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Storefront v2 test case matrix (MS-V2-001 onward) and automation standards, now carried by this workbook and docs/CONVENTIONS.md.</t>
         </is>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -672,7 +672,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Storefront (www.musticker.com/kr) + Admin panel (admin-panel.musticker.com) | Playwright + TypeScript | Workbook v1.2 | 2026-10-14</t>
+          <t>Storefront (www.musticker.com/kr) + Admin panel (admin-panel.musticker.com) | Playwright + TypeScript | Workbook v1.3 | 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Filter the Test Cases tab by Area, Priority, App or Automation. Only the orange-headed columns (Result, Defect ID, Tester, Executed On, Tester Notes) are for you to fill in. The Legacy ID column (Y) shows the ID a case had before workbook v1.2 (MS-V2-### / MS-ADM-###); it is for reference only.</t>
+          <t>Filter the Test Cases tab by Area, Priority, App or Automation. Only the orange-headed columns (Result, Defect ID, Tester, Executed On, Tester Notes) are for you to fill in. The Legacy ID column (Y) shows the ID a case had before workbook v1.2 (MS-V2-### / MS-ADM-###); it is for reference only. Area is the module and Sub-Area is the suite: each suite is one Playwright spec file in that module's folder, and its test.describe title is the Sub-Area.</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Homepage critical content</t>
+          <t>Storefront smoke</t>
         </is>
       </c>
       <c r="E2" s="25" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="O2" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/smoke/storefront-smoke.spec.ts</t>
+          <t>tests/e2e/storefront/navigation/storefront-smoke.spec.ts</t>
         </is>
       </c>
       <c r="P2" s="25" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t>Category navigation</t>
+          <t>Storefront smoke</t>
         </is>
       </c>
       <c r="E3" s="25" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="O3" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/smoke/storefront-smoke.spec.ts</t>
+          <t>tests/e2e/storefront/navigation/storefront-smoke.spec.ts</t>
         </is>
       </c>
       <c r="P3" s="25" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Header search dialog</t>
+          <t>Storefront smoke</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="O4" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/smoke/storefront-smoke.spec.ts</t>
+          <t>tests/e2e/storefront/navigation/storefront-smoke.spec.ts</t>
         </is>
       </c>
       <c r="P4" s="25" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>Empty cart drawer</t>
+          <t>Storefront smoke</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="O5" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/smoke/storefront-smoke.spec.ts</t>
+          <t>tests/e2e/storefront/navigation/storefront-smoke.spec.ts</t>
         </is>
       </c>
       <c r="P5" s="25" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Anonymous account entry</t>
+          <t>Storefront smoke</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="O6" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/smoke/storefront-smoke.spec.ts</t>
+          <t>tests/e2e/storefront/navigation/storefront-smoke.spec.ts</t>
         </is>
       </c>
       <c r="P6" s="25" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>Footer legal and support links</t>
+          <t>Storefront smoke</t>
         </is>
       </c>
       <c r="E7" s="25" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="O7" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/smoke/storefront-smoke.spec.ts</t>
+          <t>tests/e2e/storefront/navigation/storefront-smoke.spec.ts</t>
         </is>
       </c>
       <c r="P7" s="25" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>Locale selector</t>
+          <t>Storefront smoke</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="O8" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/smoke/storefront-smoke.spec.ts</t>
+          <t>tests/e2e/storefront/navigation/storefront-smoke.spec.ts</t>
         </is>
       </c>
       <c r="P8" s="25" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="O9" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/smoke/mobile-critical.spec.ts</t>
+          <t>tests/e2e/storefront/navigation/mobile-critical.spec.ts</t>
         </is>
       </c>
       <c r="P9" s="25" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Sticker category listing</t>
+          <t>Category discovery</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>Roll sticker category listing</t>
+          <t>Category discovery</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Sheet sticker category listing</t>
+          <t>Category discovery</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>Topics and accordion</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>FAQ search</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>About page content</t>
+          <t>About page</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>Product page crawl</t>
+          <t>Catalog crawl</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>Die-cut sticker config</t>
+          <t>Product config</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="O17" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/product-config.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/product-config.spec.ts</t>
         </is>
       </c>
       <c r="P17" s="25" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>Die-cut roll config</t>
+          <t>Product config</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="O18" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/product-config.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/product-config.spec.ts</t>
         </is>
       </c>
       <c r="P18" s="25" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>Die-cut sheet config</t>
+          <t>Product config</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="O19" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/product-config.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/product-config.spec.ts</t>
         </is>
       </c>
       <c r="P19" s="25" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>Custom size/quantity entry</t>
+          <t>Product config</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="O20" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/product-config.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/product-config.spec.ts</t>
         </is>
       </c>
       <c r="P20" s="25" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t>Delivery &amp; trust copy</t>
+          <t>Product config</t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="O21" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/product-config.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/product-config.spec.ts</t>
         </is>
       </c>
       <c r="P21" s="25" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t>Review carousel</t>
+          <t>Product config</t>
         </is>
       </c>
       <c r="E22" s="25" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="O22" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/product-config.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/product-config.spec.ts</t>
         </is>
       </c>
       <c r="P22" s="25" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D23" s="25" t="inlineStr">
         <is>
-          <t>Shaped sheet configurator</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E23" s="25" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="O23" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sheet-sticker-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P23" s="25" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>Shaped sheet custom size</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O24" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sheet-sticker-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P24" s="25" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
-          <t>Bulk discount badge</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O25" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sheet-sticker-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P25" s="25" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>Design upload modal</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E26" s="25" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="O26" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sheet-sticker-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P26" s="25" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>Drawer material edit</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E27" s="25" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="O27" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sheet-sticker-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P27" s="25" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>Drawer to cart handoff</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E28" s="25" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="O28" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sheet-sticker-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P28" s="25" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="D29" s="25" t="inlineStr">
         <is>
-          <t>Cart page size-change dialog</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E29" s="25" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="O29" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sheet-sticker-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P29" s="25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="D30" s="25" t="inlineStr">
         <is>
-          <t>Cart row quantity select</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E30" s="25" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="O30" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sheet-sticker-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P30" s="25" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>Size-guide image alt text</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E31" s="25" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="O31" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sheet-sticker-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P31" s="25" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="D32" s="25" t="inlineStr">
         <is>
-          <t>Per-unit price</t>
+          <t>Sheet sticker configurator</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D33" s="25" t="inlineStr">
         <is>
-          <t>Die-cut shape catalog</t>
+          <t>Sticker catalog configurator</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="O33" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sticker-catalog-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sticker-catalog-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P33" s="25" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>Die-cut roll catalog</t>
+          <t>Sticker catalog configurator</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="O34" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sticker-catalog-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sticker-catalog-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P34" s="25" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="D35" s="25" t="inlineStr">
         <is>
-          <t>Die-cut custom size</t>
+          <t>Sticker catalog configurator</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="O35" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sticker-catalog-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sticker-catalog-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P35" s="25" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t>Roll custom size</t>
+          <t>Sticker catalog configurator</t>
         </is>
       </c>
       <c r="E36" s="25" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="O36" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sticker-catalog-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sticker-catalog-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P36" s="25" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="D37" s="25" t="inlineStr">
         <is>
-          <t>Bulk discount badge</t>
+          <t>Sticker catalog configurator</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="O37" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sticker-catalog-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sticker-catalog-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P37" s="25" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>Bulk discount badge</t>
+          <t>Sticker catalog configurator</t>
         </is>
       </c>
       <c r="E38" s="25" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O38" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sticker-catalog-configurator.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sticker-catalog-configurator.spec.ts</t>
         </is>
       </c>
       <c r="P38" s="25" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>Custom sheet sticker</t>
+          <t>Sticker sheet and lettering</t>
         </is>
       </c>
       <c r="E39" s="25" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O39" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sticker-sheet-and-lettering.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sticker-sheet-and-lettering.spec.ts</t>
         </is>
       </c>
       <c r="P39" s="25" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>Vinyl lettering</t>
+          <t>Sticker sheet and lettering</t>
         </is>
       </c>
       <c r="E40" s="25" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O40" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sticker-sheet-and-lettering.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sticker-sheet-and-lettering.spec.ts</t>
         </is>
       </c>
       <c r="P40" s="25" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>Full-colour transfer lettering</t>
+          <t>Sticker sheet and lettering</t>
         </is>
       </c>
       <c r="E41" s="25" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O41" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sticker-sheet-and-lettering.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/sticker-sheet-and-lettering.spec.ts</t>
         </is>
       </c>
       <c r="P41" s="25" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>Sheet size rule (min 2/sheet)</t>
+          <t>Sheet sticker size rules</t>
         </is>
       </c>
       <c r="E42" s="25" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="O42" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-size-rules.spec.ts</t>
+          <t>tests/e2e/storefront/sheet-size-rules/sheet-sticker-size-rules.spec.ts</t>
         </is>
       </c>
       <c r="P42" s="25" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>Sheet size rule gate</t>
+          <t>Sheet sticker size rules</t>
         </is>
       </c>
       <c r="E43" s="25" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="O43" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-size-rules.spec.ts</t>
+          <t>tests/e2e/storefront/sheet-size-rules/sheet-sticker-size-rules.spec.ts</t>
         </is>
       </c>
       <c r="P43" s="25" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="D44" s="25" t="inlineStr">
         <is>
-          <t>Sheet size presets</t>
+          <t>Sheet sticker size rules</t>
         </is>
       </c>
       <c r="E44" s="25" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="O44" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-size-rules.spec.ts</t>
+          <t>tests/e2e/storefront/sheet-size-rules/sheet-sticker-size-rules.spec.ts</t>
         </is>
       </c>
       <c r="P44" s="25" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="D45" s="25" t="inlineStr">
         <is>
-          <t>Cart edit dialog size rule</t>
+          <t>Sheet sticker size rules</t>
         </is>
       </c>
       <c r="E45" s="25" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="O45" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-size-rules.spec.ts</t>
+          <t>tests/e2e/storefront/sheet-size-rules/sheet-sticker-size-rules.spec.ts</t>
         </is>
       </c>
       <c r="P45" s="25" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>Size guide modal rule</t>
+          <t>Sheet sticker size rules</t>
         </is>
       </c>
       <c r="E46" s="25" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="O46" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-size-rules.spec.ts</t>
+          <t>tests/e2e/storefront/sheet-size-rules/sheet-sticker-size-rules.spec.ts</t>
         </is>
       </c>
       <c r="P46" s="25" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="D47" s="25" t="inlineStr">
         <is>
-          <t>A5 layout formula boundary</t>
+          <t>Sheet sticker size rules</t>
         </is>
       </c>
       <c r="E47" s="25" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="O47" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/sheet-sticker-size-rules.spec.ts</t>
+          <t>tests/e2e/storefront/sheet-size-rules/sheet-sticker-size-rules.spec.ts</t>
         </is>
       </c>
       <c r="P47" s="25" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>Line item removal</t>
+          <t>Cart lifecycle</t>
         </is>
       </c>
       <c r="E48" s="25" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="O48" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/cart-lifecycle.spec.ts</t>
+          <t>tests/e2e/storefront/cart/cart-lifecycle.spec.ts</t>
         </is>
       </c>
       <c r="P48" s="25" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>Multi-line totals</t>
+          <t>Cart lifecycle</t>
         </is>
       </c>
       <c r="E49" s="25" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="O49" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/cart-lifecycle.spec.ts</t>
+          <t>tests/e2e/storefront/cart/cart-lifecycle.spec.ts</t>
         </is>
       </c>
       <c r="P49" s="25" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>Guest cart persistence</t>
+          <t>Cart lifecycle</t>
         </is>
       </c>
       <c r="E50" s="25" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O50" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/cart-lifecycle.spec.ts</t>
+          <t>tests/e2e/storefront/cart/cart-lifecycle.spec.ts</t>
         </is>
       </c>
       <c r="P50" s="25" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>Removal confirmation</t>
+          <t>Cart lifecycle</t>
         </is>
       </c>
       <c r="E51" s="25" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="O51" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/cart-lifecycle.spec.ts</t>
+          <t>tests/e2e/storefront/cart/cart-lifecycle.spec.ts</t>
         </is>
       </c>
       <c r="P51" s="25" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="D52" s="25" t="inlineStr">
         <is>
-          <t>Guest-to-member merge</t>
+          <t>Guest cart merge</t>
         </is>
       </c>
       <c r="E52" s="25" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="O52" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/cart-lifecycle.spec.ts</t>
+          <t>tests/e2e/storefront/cart/guest-cart-merge.spec.ts</t>
         </is>
       </c>
       <c r="P52" s="25" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="D53" s="25" t="inlineStr">
         <is>
-          <t>Empty cart state</t>
+          <t>Cart lifecycle</t>
         </is>
       </c>
       <c r="E53" s="25" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="O53" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/cart-lifecycle.spec.ts</t>
+          <t>tests/e2e/storefront/cart/cart-lifecycle.spec.ts</t>
         </is>
       </c>
       <c r="P53" s="25" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="O54" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/checkout-destructive.spec.ts</t>
+          <t>tests/e2e/storefront/checkout/guest-checkout-payment.spec.ts</t>
         </is>
       </c>
       <c r="P54" s="25" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>Checkout page render</t>
+          <t>Checkout page</t>
         </is>
       </c>
       <c r="E55" s="25" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="O55" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/checkout-page.spec.ts</t>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
         </is>
       </c>
       <c r="P55" s="25" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>Blank submission</t>
+          <t>Checkout page</t>
         </is>
       </c>
       <c r="E56" s="25" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="O56" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/checkout-page.spec.ts</t>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
         </is>
       </c>
       <c r="P56" s="25" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>Price hand-off reconciliation</t>
+          <t>Money path</t>
         </is>
       </c>
       <c r="E57" s="25" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="O57" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/money-path.spec.ts</t>
+          <t>tests/e2e/storefront/checkout/money-path.spec.ts</t>
         </is>
       </c>
       <c r="P57" s="25" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>Paid shipping threshold</t>
+          <t>Money path</t>
         </is>
       </c>
       <c r="E58" s="25" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="O58" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/money-path.spec.ts</t>
+          <t>tests/e2e/storefront/checkout/money-path.spec.ts</t>
         </is>
       </c>
       <c r="P58" s="25" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
-          <t>Free shipping threshold</t>
+          <t>Money path</t>
         </is>
       </c>
       <c r="E59" s="25" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="O59" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/money-path.spec.ts</t>
+          <t>tests/e2e/storefront/checkout/money-path.spec.ts</t>
         </is>
       </c>
       <c r="P59" s="25" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>Interpolation - Area between two grid rows</t>
+          <t>Price interpolation</t>
         </is>
       </c>
       <c r="E60" s="25" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>Interpolation - Highest grid row</t>
+          <t>Price interpolation</t>
         </is>
       </c>
       <c r="E61" s="25" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>Interpolation - Lowest grid row</t>
+          <t>Price interpolation</t>
         </is>
       </c>
       <c r="E62" s="25" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="D63" s="25" t="inlineStr">
         <is>
-          <t>Interpolation - Quantity between ladder rungs</t>
+          <t>Price interpolation</t>
         </is>
       </c>
       <c r="E63" s="25" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="D64" s="25" t="inlineStr">
         <is>
-          <t>Interpolation - Equal area, different dimensions</t>
+          <t>Price interpolation</t>
         </is>
       </c>
       <c r="E64" s="25" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="D65" s="25" t="inlineStr">
         <is>
-          <t>Product-table mapping - Product served by pricing table N</t>
+          <t>Product table mapping</t>
         </is>
       </c>
       <c r="E65" s="25" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="D66" s="25" t="inlineStr">
         <is>
-          <t>Product-table mapping - CSVs for a shared table agree</t>
+          <t>Product table mapping</t>
         </is>
       </c>
       <c r="E66" s="25" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="D67" s="25" t="inlineStr">
         <is>
-          <t>Product-table mapping - Table identical across products</t>
+          <t>Product table mapping</t>
         </is>
       </c>
       <c r="E67" s="25" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="D68" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/roll-stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E68" s="25" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D69" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E69" s="25" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="D70" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/roll-stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E70" s="25" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D71" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E71" s="25" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D72" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/roll-stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E72" s="25" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="D73" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E73" s="25" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D74" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E74" s="25" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="D75" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E75" s="25" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="D76" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/roll-stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E76" s="25" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D77" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E77" s="25" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="D78" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/roll-stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E78" s="25" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="D79" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/roll-stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E79" s="25" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="D80" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E80" s="25" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="D81" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/roll-stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E81" s="25" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="D82" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E82" s="25" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="D83" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/roll-stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E83" s="25" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="D84" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E84" s="25" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="D85" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E85" s="25" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="D86" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E86" s="25" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="D87" s="25" t="inlineStr">
         <is>
-          <t>Price table cells - /kr/stickers</t>
+          <t>Price table</t>
         </is>
       </c>
       <c r="E87" s="25" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="D88" s="25" t="inlineStr">
         <is>
-          <t>Login entry</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E88" s="25" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="D89" s="25" t="inlineStr">
         <is>
-          <t>Login form</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E89" s="25" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="D90" s="25" t="inlineStr">
         <is>
-          <t>Login validation</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E90" s="25" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>Login validation</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E91" s="25" t="inlineStr">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>Invalid credentials</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E92" s="25" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>Password masking</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E93" s="25" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>Forgot password</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E94" s="25" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>Login to register</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E95" s="25" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>Member login</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E96" s="25" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="D97" s="25" t="inlineStr">
         <is>
-          <t>Session lifecycle</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E97" s="25" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="D98" s="25" t="inlineStr">
         <is>
-          <t>Password visibility</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="D99" s="25" t="inlineStr">
         <is>
-          <t>Registration form</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E99" s="25" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="D100" s="25" t="inlineStr">
         <is>
-          <t>Registration validation</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E100" s="25" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="D101" s="25" t="inlineStr">
         <is>
-          <t>Registration validation</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E101" s="25" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="D102" s="25" t="inlineStr">
         <is>
-          <t>Registration validation</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E102" s="25" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="D103" s="25" t="inlineStr">
         <is>
-          <t>Registration validation</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E103" s="25" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="D104" s="25" t="inlineStr">
         <is>
-          <t>Password masking</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E104" s="25" t="inlineStr">
@@ -14117,7 +14117,7 @@
       </c>
       <c r="D105" s="25" t="inlineStr">
         <is>
-          <t>Register to login</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E105" s="25" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="D106" s="25" t="inlineStr">
         <is>
-          <t>Duplicate registration</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E106" s="25" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="D107" s="25" t="inlineStr">
         <is>
-          <t>Email verification</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E107" s="25" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="D108" s="25" t="inlineStr">
         <is>
-          <t>Email verification</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="E108" s="25" t="inlineStr">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="D109" s="25" t="inlineStr">
         <is>
-          <t>Change password form</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="E109" s="25" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="D110" s="25" t="inlineStr">
         <is>
-          <t>Change password form</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="E110" s="25" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="D111" s="25" t="inlineStr">
         <is>
-          <t>Change password validation</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="E111" s="25" t="inlineStr">
@@ -14904,7 +14904,7 @@
       </c>
       <c r="D112" s="25" t="inlineStr">
         <is>
-          <t>Change password validation</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="E112" s="25" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="D113" s="25" t="inlineStr">
         <is>
-          <t>Change password validation</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="E113" s="25" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="D114" s="25" t="inlineStr">
         <is>
-          <t>Password rotation</t>
+          <t>Change password</t>
         </is>
       </c>
       <c r="E114" s="25" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="D115" s="25" t="inlineStr">
         <is>
-          <t>Route protection</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="E115" s="25" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="O116" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/auth/login.spec.ts</t>
+          <t>tests/e2e/storefront/auth/guest-order-lookup.spec.ts</t>
         </is>
       </c>
       <c r="P116" s="25" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="D119" s="25" t="inlineStr">
         <is>
-          <t>Account enumeration</t>
+          <t>Guest order lookup</t>
         </is>
       </c>
       <c r="E119" s="25" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="D120" s="25" t="inlineStr">
         <is>
-          <t>Order list</t>
+          <t>Order history</t>
         </is>
       </c>
       <c r="E120" s="25" t="inlineStr">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="D121" s="25" t="inlineStr">
         <is>
-          <t>Order detail</t>
+          <t>Order history</t>
         </is>
       </c>
       <c r="E121" s="25" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="D122" s="25" t="inlineStr">
         <is>
-          <t>Segment filter</t>
+          <t>Order history</t>
         </is>
       </c>
       <c r="E122" s="25" t="inlineStr">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="D123" s="25" t="inlineStr">
         <is>
-          <t>Order search</t>
+          <t>Order history</t>
         </is>
       </c>
       <c r="E123" s="25" t="inlineStr">
@@ -16252,7 +16252,7 @@
       </c>
       <c r="D124" s="25" t="inlineStr">
         <is>
-          <t>History toolbar</t>
+          <t>Order history</t>
         </is>
       </c>
       <c r="E124" s="25" t="inlineStr">
@@ -16363,7 +16363,7 @@
       </c>
       <c r="D125" s="25" t="inlineStr">
         <is>
-          <t>Inquiry form fields</t>
+          <t>Inquiry validation</t>
         </is>
       </c>
       <c r="E125" s="25" t="inlineStr">
@@ -16421,7 +16421,7 @@
       </c>
       <c r="O125" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/validation/inquiry-validation.spec.ts</t>
+          <t>tests/e2e/storefront/inquiry/inquiry-validation.spec.ts</t>
         </is>
       </c>
       <c r="P125" s="25" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="D126" s="25" t="inlineStr">
         <is>
-          <t>Attachment guidance</t>
+          <t>Inquiry validation</t>
         </is>
       </c>
       <c r="E126" s="25" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="O126" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/validation/inquiry-validation.spec.ts</t>
+          <t>tests/e2e/storefront/inquiry/inquiry-validation.spec.ts</t>
         </is>
       </c>
       <c r="P126" s="25" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="D127" s="25" t="inlineStr">
         <is>
-          <t>Kakao and Naver inquiry</t>
+          <t>Inquiry validation</t>
         </is>
       </c>
       <c r="E127" s="25" t="inlineStr">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="O127" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/validation/inquiry-validation.spec.ts</t>
+          <t>tests/e2e/storefront/inquiry/inquiry-validation.spec.ts</t>
         </is>
       </c>
       <c r="P127" s="25" t="inlineStr">
@@ -16699,7 +16699,7 @@
       </c>
       <c r="D128" s="25" t="inlineStr">
         <is>
-          <t>Navigation categories API</t>
+          <t>Public API</t>
         </is>
       </c>
       <c r="E128" s="25" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="D129" s="25" t="inlineStr">
         <is>
-          <t>Inquiry types API</t>
+          <t>Public API</t>
         </is>
       </c>
       <c r="E129" s="25" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="D130" s="25" t="inlineStr">
         <is>
-          <t>Anonymous session boundary</t>
+          <t>Public API</t>
         </is>
       </c>
       <c r="E130" s="25" t="inlineStr">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="D131" s="25" t="inlineStr">
         <is>
-          <t>Keyboard and named controls</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="E131" s="25" t="inlineStr">
@@ -17093,7 +17093,7 @@
       </c>
       <c r="O131" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/regression/accessibility.spec.ts</t>
+          <t>tests/e2e/storefront/ux/accessibility.spec.ts</t>
         </is>
       </c>
       <c r="P131" s="25" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="D132" s="25" t="inlineStr">
         <is>
-          <t>Full-page visual snapshots</t>
+          <t>Visual</t>
         </is>
       </c>
       <c r="E132" s="25" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="O132" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/regression/visual.spec.ts</t>
+          <t>tests/e2e/storefront/ux/visual.spec.ts</t>
         </is>
       </c>
       <c r="P132" s="25" t="inlineStr">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="D133" s="25" t="inlineStr">
         <is>
-          <t>404 not-found page</t>
+          <t>Error pages</t>
         </is>
       </c>
       <c r="E133" s="25" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="O133" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/regression/error-pages.spec.ts</t>
+          <t>tests/e2e/storefront/ux/error-pages.spec.ts</t>
         </is>
       </c>
       <c r="P133" s="25" t="inlineStr">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="D134" s="25" t="inlineStr">
         <is>
-          <t>WCAG 2.1 AA axe scan</t>
+          <t>Axe accessibility</t>
         </is>
       </c>
       <c r="E134" s="25" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="O134" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/regression/axe-accessibility.spec.ts</t>
+          <t>tests/e2e/storefront/ux/axe-accessibility.spec.ts</t>
         </is>
       </c>
       <c r="P134" s="25" t="inlineStr">
@@ -17486,7 +17486,7 @@
       </c>
       <c r="D135" s="25" t="inlineStr">
         <is>
-          <t>Internal-origin header scope</t>
+          <t>Internal origin scope</t>
         </is>
       </c>
       <c r="E135" s="25" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="D136" s="25" t="inlineStr">
         <is>
-          <t>Internal-origin header scope</t>
+          <t>Internal origin scope</t>
         </is>
       </c>
       <c r="E136" s="25" t="inlineStr">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="D137" s="25" t="inlineStr">
         <is>
-          <t>Per-environment key mapping</t>
+          <t>Internal origin scope</t>
         </is>
       </c>
       <c r="E137" s="25" t="inlineStr">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="D138" s="25" t="inlineStr">
         <is>
-          <t>Per-environment key mapping</t>
+          <t>Internal origin scope</t>
         </is>
       </c>
       <c r="E138" s="25" t="inlineStr">
@@ -17906,7 +17906,7 @@
       </c>
       <c r="D139" s="25" t="inlineStr">
         <is>
-          <t>WAF throttle detection</t>
+          <t>Throttle detection</t>
         </is>
       </c>
       <c r="E139" s="25" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="D140" s="25" t="inlineStr">
         <is>
-          <t>WAF throttle detection</t>
+          <t>Throttle detection</t>
         </is>
       </c>
       <c r="E140" s="25" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="D141" s="25" t="inlineStr">
         <is>
-          <t>WAF throttle detection</t>
+          <t>Throttle detection</t>
         </is>
       </c>
       <c r="E141" s="25" t="inlineStr">
@@ -18225,7 +18225,7 @@
       </c>
       <c r="D142" s="25" t="inlineStr">
         <is>
-          <t>End-to-end order lifecycle (storefront + admin panel)</t>
+          <t>Order processing</t>
         </is>
       </c>
       <c r="E142" s="25" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="D143" s="25" t="inlineStr">
         <is>
-          <t>Make Evaluation</t>
+          <t>Artwork evaluation</t>
         </is>
       </c>
       <c r="E143" s="25" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="D144" s="25" t="inlineStr">
         <is>
-          <t>Evaluation validation</t>
+          <t>Artwork evaluation</t>
         </is>
       </c>
       <c r="E144" s="25" t="inlineStr">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="D145" s="25" t="inlineStr">
         <is>
-          <t>Rejection and resubmission</t>
+          <t>Artwork evaluation</t>
         </is>
       </c>
       <c r="E145" s="25" t="inlineStr">
@@ -18695,7 +18695,7 @@
       </c>
       <c r="D146" s="25" t="inlineStr">
         <is>
-          <t>Send Final Proof validation</t>
+          <t>Final proof</t>
         </is>
       </c>
       <c r="E146" s="25" t="inlineStr">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="D147" s="25" t="inlineStr">
         <is>
-          <t>Customer proof review</t>
+          <t>Final proof</t>
         </is>
       </c>
       <c r="E147" s="25" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="D148" s="25" t="inlineStr">
         <is>
-          <t>Proof menu actions</t>
+          <t>Final proof</t>
         </is>
       </c>
       <c r="E148" s="25" t="inlineStr">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="D149" s="25" t="inlineStr">
         <is>
-          <t>Approve on customer's behalf</t>
+          <t>Final proof</t>
         </is>
       </c>
       <c r="E149" s="25" t="inlineStr">
@@ -19145,7 +19145,7 @@
       </c>
       <c r="D150" s="25" t="inlineStr">
         <is>
-          <t>Undo Approval</t>
+          <t>Final proof</t>
         </is>
       </c>
       <c r="E150" s="25" t="inlineStr">
@@ -19256,7 +19256,7 @@
       </c>
       <c r="D151" s="25" t="inlineStr">
         <is>
-          <t>Customer approval</t>
+          <t>Final proof</t>
         </is>
       </c>
       <c r="E151" s="25" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="D152" s="25" t="inlineStr">
         <is>
-          <t>Move to Production</t>
+          <t>Production and shipping</t>
         </is>
       </c>
       <c r="E152" s="25" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="D153" s="25" t="inlineStr">
         <is>
-          <t>Mark as Printing</t>
+          <t>Production and shipping</t>
         </is>
       </c>
       <c r="E153" s="25" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="D154" s="25" t="inlineStr">
         <is>
-          <t>Add Tracking Number</t>
+          <t>Production and shipping</t>
         </is>
       </c>
       <c r="E154" s="25" t="inlineStr">
@@ -19704,7 +19704,7 @@
       </c>
       <c r="D155" s="25" t="inlineStr">
         <is>
-          <t>Send tracking</t>
+          <t>Production and shipping</t>
         </is>
       </c>
       <c r="E155" s="25" t="inlineStr">
@@ -19815,7 +19815,7 @@
       </c>
       <c r="D156" s="25" t="inlineStr">
         <is>
-          <t>Mark delivered</t>
+          <t>Production and shipping</t>
         </is>
       </c>
       <c r="E156" s="25" t="inlineStr">
@@ -19927,7 +19927,7 @@
       </c>
       <c r="D157" s="25" t="inlineStr">
         <is>
-          <t>Track link</t>
+          <t>Production and shipping</t>
         </is>
       </c>
       <c r="E157" s="25" t="inlineStr">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="D158" s="25" t="inlineStr">
         <is>
-          <t>Production note</t>
+          <t>Order adjustments</t>
         </is>
       </c>
       <c r="E158" s="25" t="inlineStr">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="D159" s="25" t="inlineStr">
         <is>
-          <t>Waive Shipping Fee</t>
+          <t>Order adjustments</t>
         </is>
       </c>
       <c r="E159" s="25" t="inlineStr">
@@ -20259,7 +20259,7 @@
       </c>
       <c r="D160" s="25" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Admin sign-in</t>
         </is>
       </c>
       <c r="E160" s="25" t="inlineStr">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="D161" s="25" t="inlineStr">
         <is>
-          <t>Single active session</t>
+          <t>Admin sign-in</t>
         </is>
       </c>
       <c r="E161" s="25" t="inlineStr">
@@ -20486,7 +20486,7 @@
       </c>
       <c r="D162" s="25" t="inlineStr">
         <is>
-          <t>Orders list tabs</t>
+          <t>Orders list</t>
         </is>
       </c>
       <c r="E162" s="25" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="D163" s="25" t="inlineStr">
         <is>
-          <t>Search and export</t>
+          <t>Orders list</t>
         </is>
       </c>
       <c r="E163" s="25" t="inlineStr">
@@ -20712,7 +20712,7 @@
       </c>
       <c r="D164" s="25" t="inlineStr">
         <is>
-          <t>Header status dropdown</t>
+          <t>Orders list</t>
         </is>
       </c>
       <c r="E164" s="25" t="inlineStr">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="D165" s="25" t="inlineStr">
         <is>
-          <t>Activity log attribution</t>
+          <t>Order detail</t>
         </is>
       </c>
       <c r="E165" s="25" t="inlineStr">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="D166" s="25" t="inlineStr">
         <is>
-          <t>Edit Item</t>
+          <t>Order detail</t>
         </is>
       </c>
       <c r="E166" s="25" t="inlineStr">
@@ -21048,7 +21048,7 @@
       </c>
       <c r="D167" s="25" t="inlineStr">
         <is>
-          <t>Add Item</t>
+          <t>Order detail</t>
         </is>
       </c>
       <c r="E167" s="25" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="D168" s="25" t="inlineStr">
         <is>
-          <t>More Actions</t>
+          <t>Order detail</t>
         </is>
       </c>
       <c r="E168" s="25" t="inlineStr">
@@ -21271,7 +21271,7 @@
       </c>
       <c r="D169" s="25" t="inlineStr">
         <is>
-          <t>Verify Payment</t>
+          <t>Payments and completion</t>
         </is>
       </c>
       <c r="E169" s="25" t="inlineStr">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="D170" s="25" t="inlineStr">
         <is>
-          <t>Refund after item reduction</t>
+          <t>Payments and completion</t>
         </is>
       </c>
       <c r="E170" s="25" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="D171" s="25" t="inlineStr">
         <is>
-          <t>Pending refund blocks progress</t>
+          <t>Payments and completion</t>
         </is>
       </c>
       <c r="E171" s="25" t="inlineStr">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="D172" s="25" t="inlineStr">
         <is>
-          <t>Storefront completed order</t>
+          <t>Payments and completion</t>
         </is>
       </c>
       <c r="E172" s="25" t="inlineStr">
@@ -21712,7 +21712,7 @@
       </c>
       <c r="D173" s="25" t="inlineStr">
         <is>
-          <t>Order chooser</t>
+          <t>Design studio</t>
         </is>
       </c>
       <c r="E173" s="25" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="O173" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/design-studio.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/design-studio.spec.ts</t>
         </is>
       </c>
       <c r="P173" s="25" t="inlineStr">
@@ -21882,7 +21882,7 @@
       </c>
       <c r="O174" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/design-studio.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/design-studio.spec.ts</t>
         </is>
       </c>
       <c r="P174" s="25" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="O175" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/storefront/purchasing/design-studio.spec.ts</t>
+          <t>tests/e2e/storefront/configuration/design-studio.spec.ts</t>
         </is>
       </c>
       <c r="P175" s="25" t="inlineStr">
@@ -27108,7 +27108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -27132,360 +27132,391 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-10-15 - workbook v1.3, suites</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="51" customHeight="1">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sub-Area</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sub-Area now names the suite a case belongs to (for example Registration, Change password, Guest order lookup), instead of a short label per case: 175 cases in 42 suites. Each automated suite is one Playwright spec file, and the suite name is that file's test.describe title. Planned admin cases are grouped into the suites their specs will use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="51" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Playwright Spec</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spec files moved into one folder per module: navigation, configuration, sheet-size-rules, cart, checkout, inquiry and ux replace smoke, purchasing, validation and regression. checkout-destructive.spec.ts is now guest-checkout-payment.spec.ts. MS-AUTH-029 moved to the Guest order lookup suite and MS-CRT-005 to the new Guest cart merge suite. Test titles, tags and test logic are unchanged; still 2,473 tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-14 - workbook v1.2, module-based TC IDs</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="38.25" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+    <row r="9" ht="38.25" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">TC IDs</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">MS-V2-### and MS-ADM-### are replaced by MS-&lt;MODULE&gt;-###, so an ID names its module (the Area): NAV, DSC, CFG, SHT, CRT, CHK, AUTH, ACC, INQ, API, UX, ADMO (admin order processing) and ADMA (admin access &amp; order management), numbered 001 upward in workbook order. MS-PRC-*, MS-SEC-* and MS-WAF-* are unchanged. 140 cases renamed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38.25" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Legacy ID</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New column Y keeps each renamed case's previous ID. Older entries in this changelog, past Allure history and defect evidence still use the old IDs; look them up in that column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38.25" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suite</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Playwright test titles, comments, fixtures and docs renamed to match (178 test titles; no test logic changed; still 2,473 tests). Defect Log TC IDs and the cross-references in the other tabs updated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14 - workbook v1.1, MS-ADM-001 re-run, storefront explored</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38.25" customHeight="1">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>MS-ADM-001</t>
+          <t xml:space="preserve">Legacy ID</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Re-run on static-1 (AO-2609180003-dev, AO-2609090017-dev) and updated for four product changes: the proof-approval dialog needs an acknowledgement tick before 최종 시안 승인; A-FPA is labelled 최종 승인 완료; Move to Production is gone, so Mark as Printing moves the order to 제작 진행 중 and the item straight to 인쇄 진행 중 (no PO); completed orders moved to 이전 내역, and an order search with no match shows 주문을 찾을 수 없습니다. Every step passes on the updated code (see Tester Notes on the case).</t>
+          <t xml:space="preserve">New column Y keeps each renamed case's previous ID. Older entries in this changelog, past Allure history and defect evidence still use the old IDs; look them up in that column.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38.25" customHeight="1">
       <c r="A11" s="28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Suite</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Playwright test titles, comments, fixtures and docs renamed to match (178 test titles; no test logic changed; still 2,473 tests). Defect Log TC IDs and the cross-references in the other tabs updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14 - workbook v1.1, MS-ADM-001 re-run, storefront explored</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38.25" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>MS-ADM-001</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Re-run on static-1 (AO-2609180003-dev, AO-2609090017-dev) and updated for four product changes: the proof-approval dialog needs an acknowledgement tick before 최종 시안 승인; A-FPA is labelled 최종 승인 완료; Move to Production is gone, so Mark as Printing moves the order to 제작 진행 중 and the item straight to 인쇄 진행 중 (no PO); completed orders moved to 이전 내역, and an order search with no match shows 주문을 찾을 수 없습니다. Every step passes on the updated code (see Tester Notes on the case).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38.25" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
           <t>Admin recording</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>A failed run showed that Playwright's failure screenshot and error context capture every open page, the admin panel included - the suite promised they did not. Admin specs now turn screenshots and traces off, and the adminPage fixture refuses to start otherwise.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="25.5" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+    <row r="16" ht="25.5" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>MS-ADM-016 (Move to Production) withdrawn. MS-ADM-006, 013, 014, 015, 017, 020, 022, 030 and 031 updated to the new flow; Business Rules and Glossary likewise.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Defects</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>MUS-QA-004 and MUS-QA-007 retested as fixed. MUS-QA-001 still reproduces for the printing and shipping entries. New: MUS-QA-010 and MUS-QA-011 (Low, to confirm).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Environments</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Instructions, gating, the Test Plan, Test Data and pricing ids now use the current environment names (static-1..8; development-1..4 retired and development-static/-static-2 renamed on 2026-09-25), and the CI schedule no longer lists the removed nightly regression. Historical "verified on development-N" notes are kept as they were.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Seed orders</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Re-checked on 2026-10-14: AO-2609180004-dev had been used elsewhere and AO-2609070004/0005-dev have two items, so one unused candidate is left (AO-2609070006-dev).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Admin login</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>dev-static-1 has a tester OTP endpoint that returns the admin verification code; noted under MS-ADM-002 as a way to run admin cases without a person. Not used by the suite yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25.5" customHeight="1">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>Storefront run</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Production-safe storefront specs (pricing excluded) before the updates: production 132 passed / 27 failed / 5 flaky; static-1 131 / 28 / 5. After: production 162 passed, 2 failed and 3 flaky (a tier-price repaint race, fixed and then 32/32 twice; transient 502s), 5 skipped; static-1 165 passed, 0 failed, 2 flaky (a network blip; MS-V2-035's timeout, now 90 s and passing on both), 5 skipped. Pricing on production: 261 of 2,286 failed, all on the replaced lettering and transfer tables; after the re-export 272/272 for those two and the other 2,016 unchanged and passing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25.5" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>Order chooser</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>다음 단계 now opens 어떻게 주문하시겠어요? (with a file / in the studio / file later), live on production. MS-V2-050 and 053 updated; new MS-V2-115.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>Design studio</t>
+          <t>Seed orders</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>New web studio (?studio=1): carries size and quantity over, prices 5% lower, refuses low-resolution designs. New MS-V2-116 and 117 (automated, production-safe) and MS-V2-118 (planned: add-to-cart blocked by MUS-QA-015). New fixture studio-design.png.</t>
+          <t>Re-checked on 2026-10-14: AO-2609180004-dev had been used elsewhere and AO-2609070004/0005-dev have two items, so one unused candidate is left (AO-2609070006-dev).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="28" t="inlineStr">
         <is>
-          <t>Header and footer</t>
+          <t>Admin login</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Nav items open a product menu instead of the category page (MS-V2-002 rewritten, MS-V2-035 updated); the footer was redesigned (MS-V2-001, 020, 039).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>dev-static-1 has a tester OTP endpoint that returns the admin verification code; noted under MS-ADM-002 as a way to run admin cases without a person. Not used by the suite yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25.5" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>Copy and options</t>
+          <t>Storefront run</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>PVC 매트 is now 무광 화이트; sheet stickers show a discount on every tier (MS-V2-052 rewritten); rounded-roll, rounded-sheet and transfer H1s renamed back; production's category cards reverted to pre-rename names (MUS-QA-016).</t>
+          <t>Production-safe storefront specs (pricing excluded) before the updates: production 132 passed / 27 failed / 5 flaky; static-1 131 / 28 / 5. After: production 162 passed, 2 failed and 3 flaky (a tier-price repaint race, fixed and then 32/32 twice; transient 502s), 5 skipped; static-1 165 passed, 0 failed, 2 flaky (a network blip; MS-V2-035's timeout, now 90 s and passing on both), 5 skipped. Pricing on production: 261 of 2,286 failed, all on the replaced lettering and transfer tables; after the re-export 272/272 for those two and the other 2,016 unchanged and passing.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>Suite fixes</t>
+          <t>Order chooser</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>selectSize waits for the size re-quote (stale tier prices failed the money-path tests); quantity tiers match the whole number (5 had been picking 50시트); category menu and review carousel clicks wait for Nuxt hydration (new waitForNuxtHydration); addToCart handles both the chooser and the older upload dialog (풀 컬러 레터링); the unused-preload warning is benign on every first-party host; new allowStudioModelLoadNoise guard option.</t>
+          <t>다음 단계 now opens 어떻게 주문하시겠어요? (with a file / in the studio / file later), live on production. MS-V2-050 and 053 updated; new MS-V2-115.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>Design studio</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Production replaced the vinyl-lettering and transfer-sticker tables on 2026-09-29 (ids 69 and 72; same rates on rungs 1-300, new rungs 500-5,000): CSVs re-exported, registry updated, now production-only baselines. The known interpolation overcharge checks are pinned to their quantities (the longer ladder had moved the sampled quantity off them and hidden that the overcharge is still live). Pricing now 2,288 tests.</t>
+          <t>New web studio (?studio=1): carries size and quantity over, prices 5% lower, refuses low-resolution designs. New MS-V2-116 and 117 (automated, production-safe) and MS-V2-118 (planned: add-to-cart blocked by MUS-QA-015). New fixture studio-design.png.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
         <is>
+          <t>Header and footer</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Nav items open a product menu instead of the category page (MS-V2-002 rewritten, MS-V2-035 updated); the footer was redesigned (MS-V2-001, 020, 039).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>Copy and options</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>PVC 매트 is now 무광 화이트; sheet stickers show a discount on every tier (MS-V2-052 rewritten); rounded-roll, rounded-sheet and transfer H1s renamed back; production's category cards reverted to pre-rename names (MUS-QA-016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25.5" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>Suite fixes</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>selectSize waits for the size re-quote (stale tier prices failed the money-path tests); quantity tiers match the whole number (5 had been picking 50시트); category menu and review carousel clicks wait for Nuxt hydration (new waitForNuxtHydration); addToCart handles both the chooser and the older upload dialog (풀 컬러 레터링); the unused-preload warning is benign on every first-party host; new allowStudioModelLoadNoise guard option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Production replaced the vinyl-lettering and transfer-sticker tables on 2026-09-29 (ids 69 and 72; same rates on rungs 1-300, new rungs 500-5,000): CSVs re-exported, registry updated, now production-only baselines. The known interpolation overcharge checks are pinned to their quantities (the longer ladder had moved the sampled quantity off them and hidden that the overcharge is still live). Pricing now 2,288 tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
           <t>Storefront defects</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>MUS-QA-012 to 020 logged (search button name, /dev/ assets on production, page weight, studio confirmation lock, pre-rename names, English FAQ on static-1, size-range mismatch, selection state not exposed, lettering 500-rung rate).</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>2026-09-25 - workbook v1, suite reorganised</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Workbook</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>This workbook replaces test-case.md as the test case source. Steps and expected results were re-derived from the spec code (the code is the source of truth); where test-case.md described more than the code checks, the case says so in Reference Notes, and three cases are marked Partial (MS-V2-012, 017, 018).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Admin panel</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Added the admin panel to the suite: MS-ADM-001 (storefront-to-admin order processing: design upload, rejection and resubmission, pass, proof, customer approval, production, printing, shipping, delivery) plus planned admin cases (MS-ADM-002 onward).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Folders</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Specs moved to tests/e2e/storefront/&lt;area&gt;/ and tests/e2e/admin/&lt;area&gt;/; page objects to tests/pom/storefront/ and tests/pom/admin/. Same 2,468 tests before and after (verified by comparing the test lists).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>New docs/RUNNING.md, docs/ARCHITECTURE.md, docs/CONVENTIONS.md; README.md is now a short entry point.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Defects</t>
+          <t>Workbook</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Nine defects/questions from exploratory testing logged (MUS-QA-001 to 009).</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
+          <t>This workbook replaces test-case.md as the test case source. Steps and expected results were re-derived from the spec code (the code is the source of truth); where test-case.md described more than the code checks, the case says so in Reference Notes, and three cases are marked Partial (MS-V2-012, 017, 018).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Admin panel</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Added the admin panel to the suite: MS-ADM-001 (storefront-to-admin order processing: design upload, rejection and resubmission, pass, proof, customer approval, production, printing, shipping, delivery) plus planned admin cases (MS-ADM-002 onward).</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>KNOWN SUITE ISSUES (not product defects)</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Folders</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Specs moved to tests/e2e/storefront/&lt;area&gt;/ and tests/e2e/admin/&lt;area&gt;/; page objects to tests/pom/storefront/ and tests/pom/admin/. Same 2,468 tests before and after (verified by comparing the test lists).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>dev-static-1 checkout</t>
+          <t>Docs</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare check before payment blocks automated browsers; guest checkout there shows no OTP popup on email blur. MS-V2-025 is verified on development-3 only.</t>
+          <t>New docs/RUNNING.md, docs/ARCHITECTURE.md, docs/CONVENTIONS.md; README.md is now a short entry point.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Upload dialog (dev-static-1)</t>
+          <t>Defects</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>The product upload dialog button is now 파일로 주문하기 and the file-type copy reads 'ai · psd · pdf · eps · tif · png · jpg'. ProductV2Page.expectDesignUploadModal and MS-V2-053 will fail when this reaches production - update storefront-data.ts then.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>MS-V2-058</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Marked test.fixme (known alt-text defect on the size guide); skipped until fixed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
+          <t>Nine defects/questions from exploratory testing logged (MUS-QA-001 to 009).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>KNOWN SUITE ISSUES (not product defects)</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10 - test-case.md v1</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>dev-static-1 checkout</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Cloudflare check before payment blocks automated browsers; guest checkout there shows no OTP popup on email blur. MS-V2-025 is verified on development-3 only.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
+          <t>Upload dialog (dev-static-1)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>The product upload dialog button is now 파일로 주문하기 and the file-type copy reads 'ai · psd · pdf · eps · tif · png · jpg'. ProductV2Page.expectDesignUploadModal and MS-V2-053 will fail when this reaches production - update storefront-data.ts then.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>MS-V2-058</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Marked test.fixme (known alt-text defect on the size guide); skipped until fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 - test-case.md v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Storefront v2 test case matrix (MS-V2-001 onward) and automation standards, now carried by this workbook and docs/CONVENTIONS.md.</t>
         </is>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Test Cases'!$A$1:$Y$192</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Defect Log'!$A$1:$R$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Defect Log'!$A$1:$R$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Testing tiers'!$A$1:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Dev-2 Audit 2026-10-23'!$A$9:$H$204</definedName>
   </definedNames>
@@ -37289,7 +37289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -39461,8 +39461,94 @@
         </is>
       </c>
     </row>
+    <row r="28" ht="110" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>MUS-QA-025</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>MS-ADMO-019</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>Artwork reminder email after checkout fails with HTTP 500</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="inlineStr">
+        <is>
+          <t>Storefront + API</t>
+        </is>
+      </c>
+      <c r="H28" s="25" t="inlineStr">
+        <is>
+          <t>dev-1 / Chromium desktop</t>
+        </is>
+      </c>
+      <c r="I28" s="25" t="inlineStr">
+        <is>
+          <t>Newly registered member with a mail.tm inbox; one 자유형 조각스티커 (75x75mm, 100개) in the cart; KakaoPay sandbox (PayApp Local Mock).</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="inlineStr">
+        <is>
+          <t>1. Sign in as a member and add one sticker to the cart.
+2. Check out with KakaoPay and complete the PayApp mock card payment.
+3. On the order confirmation page, watch the network and console.</t>
+        </is>
+      </c>
+      <c r="K28" s="25" t="inlineStr">
+        <is>
+          <t>POST /sys/kr/orders/checkout/complete/send/artwork/&lt;order id&gt; succeeds and the customer receives an artwork reminder email.</t>
+        </is>
+      </c>
+      <c r="L28" s="25" t="inlineStr">
+        <is>
+          <t>The request answers HTTP 500. The page logs "Critical Server Error. Please contact support." and "Order artwork reminder email failed: FetchError ... 500". No reminder email arrives; only the [주문 안내] order email does.</t>
+        </is>
+      </c>
+      <c r="M28" s="25" t="inlineStr">
+        <is>
+          <t>MS-ADMO-019 runs on dev-1, 2026-10-28: AO-2610280007-dev (order id 2633) and order id 2630. Spec: tests/e2e/admin/orders/order-emails.spec.ts</t>
+        </is>
+      </c>
+      <c r="N28" s="25" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="O28" s="25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P28" s="25" t="n"/>
+      <c r="Q28" s="25" t="n"/>
+      <c r="R28" s="25" t="inlineStr">
+        <is>
+          <t>Not Retested</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R27"/>
+  <autoFilter ref="A1:R28"/>
   <dataValidations count="4">
     <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -20,7 +20,7 @@
     <sheet name="Dev-2 Audit 2026-10-23" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Test Cases'!$A$1:$Y$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Test Cases'!$A$1:$Y$208</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Defect Log'!$A$1:$R$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Testing tiers'!$A$1:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Dev-2 Audit 2026-10-23'!$A$9:$H$204</definedName>
@@ -767,6 +767,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -782,6 +783,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -897,6 +899,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -964,6 +967,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
@@ -979,6 +983,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -994,6 +999,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
@@ -1037,6 +1043,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -1169,6 +1176,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -2165,6 +2173,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
@@ -9828,6 +9837,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="25.5" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -9864,6 +9874,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="51" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
@@ -9912,6 +9923,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="38.25" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
@@ -9948,6 +9960,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="51" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
@@ -10006,6 +10019,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -11209,7 +11223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y192"/>
+  <dimension ref="A1:Y208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -18220,13 +18234,25 @@
       </c>
       <c r="T56" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="U56" s="15" t="n"/>
-      <c r="V56" s="15" t="n"/>
-      <c r="W56" s="15" t="n"/>
-      <c r="X56" s="15" t="n"/>
+      <c r="V56" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W56" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X56" s="15" t="inlineStr">
+        <is>
+          <t>dev-1 3/3; retries=0. Login step now waits for the client-side guest-cart merge (POST /cart/create) before opening the cart.</t>
+        </is>
+      </c>
       <c r="Y56" s="25" t="inlineStr">
         <is>
           <t>MS-V2-104</t>
@@ -18461,13 +18487,25 @@
       </c>
       <c r="T58" s="14" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="U58" s="15" t="n"/>
-      <c r="V58" s="15" t="n"/>
-      <c r="W58" s="15" t="n"/>
-      <c r="X58" s="15" t="n"/>
+      <c r="V58" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W58" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X58" s="15" t="inlineStr">
+        <is>
+          <t>dev-1: guest checkout now runs a Cloudflare Turnstile check (live site key) on 결제하기 that never clears in automation; no OTP on email blur any more. test.fixme until dev uses the Turnstile test key or a QA bypass.</t>
+        </is>
+      </c>
       <c r="Y58" s="25" t="inlineStr">
         <is>
           <t>MS-V2-025</t>
@@ -18530,7 +18568,7 @@
       </c>
       <c r="K59" s="25" t="inlineStr">
         <is>
-          <t>Visible fields: email (placeholder 이메일 주소를 입력해 주세요.), name (성함을 입력하세요), postal code (우편번호를 입력하세요). Payment buttons 카카오페이 and 신용카드 are visible. The page contains the text 쿠폰. The 결제하기 button is visible. Suite guard: no unexpected console errors or HTTP 4xx/5xx (guest checkout bootstrap 401s allowed).</t>
+          <t>Visible fields: email (placeholder 이메일 주소를 입력해 주세요.), name (성함을 입력하세요), a disabled 우편번호 field with its 주소 찾기 (address search) button. Payment buttons 카카오페이 and 신용카드 are visible. The page contains the text 쿠폰. The 결제하기 button is visible. Suite guard: no unexpected console errors or HTTP 4xx/5xx (guest checkout bootstrap 401s allowed).</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
@@ -18579,17 +18617,17 @@
       <c r="U59" s="15" t="n"/>
       <c r="V59" s="15" t="inlineStr">
         <is>
-          <t>Codex / Playwright</t>
+          <t>Claude / Playwright</t>
         </is>
       </c>
       <c r="W59" s="15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="X59" s="15" t="inlineStr">
         <is>
-          <t>dev-2; retries=0. Full desktop: 1 passed, 0 failed, 0 skipped. See Dev-2 Audit 2026-10-23.</t>
+          <t>dev-1 3/3 and production 1/1; retries=0. Checkout redesign: postal code and road address now come from the Kakao postcode search.</t>
         </is>
       </c>
       <c r="Y59" s="25" t="inlineStr">
@@ -32874,17 +32912,17 @@
       <c r="U181" s="15" t="n"/>
       <c r="V181" s="15" t="inlineStr">
         <is>
-          <t>Codex / Playwright</t>
+          <t>Claude / Playwright</t>
         </is>
       </c>
       <c r="W181" s="15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="X181" s="15" t="inlineStr">
         <is>
-          <t>dev-2; retries=0. Full desktop: 1 passed, 0 failed, 0 skipped. See Dev-2 Audit 2026-10-23.</t>
+          <t>dev-1 4/4 and production 1/1. Section found by title: hydration renumbers section ids (#terms-section-N).</t>
         </is>
       </c>
       <c r="Y181" s="25" t="n"/>
@@ -32994,17 +33032,17 @@
       <c r="U182" s="15" t="n"/>
       <c r="V182" s="15" t="inlineStr">
         <is>
-          <t>Codex / Playwright</t>
+          <t>Claude / Playwright</t>
         </is>
       </c>
       <c r="W182" s="15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="X182" s="15" t="inlineStr">
         <is>
-          <t>dev-2; retries=0. Full desktop: 1 passed, 0 failed, 0 skipped. See Dev-2 Audit 2026-10-23.</t>
+          <t>dev-1 4/4 and production 1/1. Section found by title: hydration renumbers section ids (#privacy-section-N).</t>
         </is>
       </c>
       <c r="Y182" s="25" t="n"/>
@@ -33113,17 +33151,17 @@
       <c r="U183" s="15" t="n"/>
       <c r="V183" s="15" t="inlineStr">
         <is>
-          <t>Codex / Playwright</t>
+          <t>Claude / Playwright</t>
         </is>
       </c>
       <c r="W183" s="15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="X183" s="15" t="inlineStr">
         <is>
-          <t>dev-2; retries=0. Full desktop: 1 passed, 0 failed, 0 skipped. See Dev-2 Audit 2026-10-23.</t>
+          <t>dev-1 and production. Footer label is now 오픈소스고지 (no space).</t>
         </is>
       </c>
       <c r="Y183" s="25" t="n"/>
@@ -34189,16 +34227,1928 @@
       </c>
       <c r="Y192" s="25" t="n"/>
     </row>
+    <row r="193" ht="150" customHeight="1">
+      <c r="A193" s="12" t="inlineStr">
+        <is>
+          <t>MS-NAV-012</t>
+        </is>
+      </c>
+      <c r="B193" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C193" s="25" t="inlineStr">
+        <is>
+          <t>1. Smoke &amp; core navigation</t>
+        </is>
+      </c>
+      <c r="D193" s="25" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="E193" s="25" t="inlineStr">
+        <is>
+          <t>footer columns list their links in order, and new-tab links open without an opener</t>
+        </is>
+      </c>
+      <c r="F193" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G193" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H193" s="25" t="inlineStr">
+        <is>
+          <t>Fresh anonymous browser context; production read-only.</t>
+        </is>
+      </c>
+      <c r="I193" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/footer-data.ts</t>
+        </is>
+      </c>
+      <c r="J193" s="25" t="inlineStr">
+        <is>
+          <t>1. Open /kr.
+2. For each footer column (제품, 주문 안내, 혜택·지원, 회사) read its links in order.
+3. Check each link's href and, for new-tab links, target and rel.
+4. Check the legal row (이용약관, 개인정보처리방침, 오픈소스고지).</t>
+        </is>
+      </c>
+      <c r="K193" s="25" t="inlineStr">
+        <is>
+          <t>Each column lists exactly the expected links in order with the expected /kr hrefs. In-tab links have no target=_blank; new-tab links (학교·공공기관 주문, 대량주문·기업 견적, 제휴·파트너십 문의, 브랜드 소개, 인재채용 and the three legal links) have target=_blank and rel="noopener noreferrer".</t>
+        </is>
+      </c>
+      <c r="L193" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M193" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N193" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O193" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/navigation/footer.spec.ts</t>
+        </is>
+      </c>
+      <c r="P193" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-012 footer columns list their links in order, and new-tab links open without an opener</t>
+        </is>
+      </c>
+      <c r="Q193" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production @discovery</t>
+        </is>
+      </c>
+      <c r="R193" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S193" s="25" t="inlineStr">
+        <is>
+          <t>Explored read-only on production on 2026-10-30; dev-1 matched. No orders, accounts, messages or admin data are created.</t>
+        </is>
+      </c>
+      <c r="T193" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U193" s="15" t="n"/>
+      <c r="V193" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W193" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X193" s="15" t="inlineStr">
+        <is>
+          <t>production 3/3 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y193" s="25" t="n"/>
+    </row>
+    <row r="194" ht="150" customHeight="1">
+      <c r="A194" s="12" t="inlineStr">
+        <is>
+          <t>MS-NAV-013</t>
+        </is>
+      </c>
+      <c r="B194" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C194" s="25" t="inlineStr">
+        <is>
+          <t>1. Smoke &amp; core navigation</t>
+        </is>
+      </c>
+      <c r="D194" s="25" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="E194" s="25" t="inlineStr">
+        <is>
+          <t>footer product links open their category and product pages, each keeping the footer</t>
+        </is>
+      </c>
+      <c r="F194" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G194" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H194" s="25" t="inlineStr">
+        <is>
+          <t>Fresh anonymous browser context; production read-only.</t>
+        </is>
+      </c>
+      <c r="I194" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/footer-data.ts</t>
+        </is>
+      </c>
+      <c r="J194" s="25" t="inlineStr">
+        <is>
+          <t>1. Open /kr.
+2. Click 스티커 in the footer.
+3. From the page that opens, click the next 제품 link in its footer (롤스티커, 판스티커, 홀로그램 스티커, 글자 커팅 스티커).</t>
+        </is>
+      </c>
+      <c r="K194" s="25" t="inlineStr">
+        <is>
+          <t>Each link opens in the same tab at its /kr path with the matching level-1 heading, and each category and product page renders the footer.</t>
+        </is>
+      </c>
+      <c r="L194" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M194" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N194" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O194" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/navigation/footer.spec.ts</t>
+        </is>
+      </c>
+      <c r="P194" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-013 footer product links open their category and product pages, each keeping the footer</t>
+        </is>
+      </c>
+      <c r="Q194" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production @discovery</t>
+        </is>
+      </c>
+      <c r="R194" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S194" s="25" t="inlineStr">
+        <is>
+          <t>Explored read-only on production on 2026-10-30; dev-1 matched. No orders, accounts, messages or admin data are created.</t>
+        </is>
+      </c>
+      <c r="T194" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U194" s="15" t="n"/>
+      <c r="V194" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W194" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X194" s="15" t="inlineStr">
+        <is>
+          <t>production 3/3 and dev-1 3/3; retries=0. Client-side navigation to a cold product page took over 10s once on production, so the URL check allows 30s.</t>
+        </is>
+      </c>
+      <c r="Y194" s="25" t="n"/>
+    </row>
+    <row r="195" ht="150" customHeight="1">
+      <c r="A195" s="12" t="inlineStr">
+        <is>
+          <t>MS-NAV-014</t>
+        </is>
+      </c>
+      <c r="B195" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C195" s="25" t="inlineStr">
+        <is>
+          <t>1. Smoke &amp; core navigation</t>
+        </is>
+      </c>
+      <c r="D195" s="25" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="E195" s="25" t="inlineStr">
+        <is>
+          <t>footer support and company links open their pages in a new tab</t>
+        </is>
+      </c>
+      <c r="F195" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G195" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H195" s="25" t="inlineStr">
+        <is>
+          <t>Fresh anonymous browser context; production read-only.</t>
+        </is>
+      </c>
+      <c r="I195" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/footer-data.ts</t>
+        </is>
+      </c>
+      <c r="J195" s="25" t="inlineStr">
+        <is>
+          <t>1. Open /kr.
+2. Click each new-tab footer link: 학교·공공기관 주문, 대량주문·기업 견적, 제휴·파트너십 문의, 브랜드 소개, 인재채용.
+3. Check the new tab, then close it.</t>
+        </is>
+      </c>
+      <c r="K195" s="25" t="inlineStr">
+        <is>
+          <t>Each link opens a new tab at its /kr path showing the page's level-1 heading; the storefront tab stays on /kr.</t>
+        </is>
+      </c>
+      <c r="L195" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M195" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N195" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O195" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/navigation/footer.spec.ts</t>
+        </is>
+      </c>
+      <c r="P195" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-014 footer support and company links open their pages in a new tab</t>
+        </is>
+      </c>
+      <c r="Q195" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production @discovery</t>
+        </is>
+      </c>
+      <c r="R195" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S195" s="25" t="inlineStr">
+        <is>
+          <t>Explored read-only on production on 2026-10-30; dev-1 matched. No orders, accounts, messages or admin data are created.</t>
+        </is>
+      </c>
+      <c r="T195" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U195" s="15" t="n"/>
+      <c r="V195" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W195" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X195" s="15" t="inlineStr">
+        <is>
+          <t>production 3/3 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y195" s="25" t="n"/>
+    </row>
+    <row r="196" ht="150" customHeight="1">
+      <c r="A196" s="12" t="inlineStr">
+        <is>
+          <t>MS-NAV-015</t>
+        </is>
+      </c>
+      <c r="B196" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C196" s="25" t="inlineStr">
+        <is>
+          <t>1. Smoke &amp; core navigation</t>
+        </is>
+      </c>
+      <c r="D196" s="25" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="E196" s="25" t="inlineStr">
+        <is>
+          <t>footer 고객리뷰 takes the shopper to the home page reviews from another page</t>
+        </is>
+      </c>
+      <c r="F196" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G196" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H196" s="25" t="inlineStr">
+        <is>
+          <t>Fresh anonymous browser context; production read-only.</t>
+        </is>
+      </c>
+      <c r="I196" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/footer-data.ts</t>
+        </is>
+      </c>
+      <c r="J196" s="25" t="inlineStr">
+        <is>
+          <t>1. Open /kr/faq.
+2. Click the 고객리뷰 button in the footer.</t>
+        </is>
+      </c>
+      <c r="K196" s="25" t="inlineStr">
+        <is>
+          <t>The browser lands on /kr#reviews with the 사진 후기 N개, 만족도는 이미 증명됐어요 heading in the viewport.</t>
+        </is>
+      </c>
+      <c r="L196" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M196" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N196" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O196" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/navigation/footer.spec.ts</t>
+        </is>
+      </c>
+      <c r="P196" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-015 footer 고객리뷰 takes the shopper to the home page reviews from another page</t>
+        </is>
+      </c>
+      <c r="Q196" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production @discovery</t>
+        </is>
+      </c>
+      <c r="R196" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S196" s="25" t="inlineStr">
+        <is>
+          <t>Explored read-only on production on 2026-10-30; dev-1 matched. No orders, accounts, messages or admin data are created.</t>
+        </is>
+      </c>
+      <c r="T196" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U196" s="15" t="n"/>
+      <c r="V196" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W196" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X196" s="15" t="inlineStr">
+        <is>
+          <t>production 3/3 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y196" s="25" t="n"/>
+    </row>
+    <row r="197" ht="150" customHeight="1">
+      <c r="A197" s="12" t="inlineStr">
+        <is>
+          <t>MS-NAV-016</t>
+        </is>
+      </c>
+      <c r="B197" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C197" s="25" t="inlineStr">
+        <is>
+          <t>1. Smoke &amp; core navigation</t>
+        </is>
+      </c>
+      <c r="D197" s="25" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="E197" s="25" t="inlineStr">
+        <is>
+          <t>footer shows contact, social and business registration details</t>
+        </is>
+      </c>
+      <c r="F197" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G197" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H197" s="25" t="inlineStr">
+        <is>
+          <t>Fresh anonymous browser context; production read-only.</t>
+        </is>
+      </c>
+      <c r="I197" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/footer-data.ts</t>
+        </is>
+      </c>
+      <c r="J197" s="25" t="inlineStr">
+        <is>
+          <t>1. Open /kr.
+2. Read the footer contact block, social links, business details and copyright.</t>
+        </is>
+      </c>
+      <c r="K197" s="25" t="inlineStr">
+        <is>
+          <t>고객센터 phone links to tel:1899-5529 with hours 평일 09:00 – 18:00 · 토·일·공휴일 휴무; 구매 문의 links to mailto:sales@musticker.com. Instagram and KakaoTalk Channel links open in a new tab with rel="noopener noreferrer". Company, representative, 사업자번호 877-88-03313, 통신판매업신고 number, address and the © GLOPHICS copyright are shown.</t>
+        </is>
+      </c>
+      <c r="L197" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M197" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N197" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O197" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/navigation/footer.spec.ts</t>
+        </is>
+      </c>
+      <c r="P197" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-016 footer shows contact, social and business registration details</t>
+        </is>
+      </c>
+      <c r="Q197" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production @discovery</t>
+        </is>
+      </c>
+      <c r="R197" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S197" s="25" t="inlineStr">
+        <is>
+          <t>Explored read-only on production on 2026-10-30; dev-1 matched. No orders, accounts, messages or admin data are created.</t>
+        </is>
+      </c>
+      <c r="T197" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U197" s="15" t="n"/>
+      <c r="V197" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W197" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X197" s="15" t="inlineStr">
+        <is>
+          <t>production 3/3 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y197" s="25" t="n"/>
+    </row>
+    <row r="198" ht="150" customHeight="1">
+      <c r="A198" s="12" t="inlineStr">
+        <is>
+          <t>MS-NAV-017</t>
+        </is>
+      </c>
+      <c r="B198" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C198" s="25" t="inlineStr">
+        <is>
+          <t>1. Smoke &amp; core navigation</t>
+        </is>
+      </c>
+      <c r="D198" s="25" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="E198" s="25" t="inlineStr">
+        <is>
+          <t>footer 사업자정보확인 opens the FTC lookup for the registration number it shows</t>
+        </is>
+      </c>
+      <c r="F198" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G198" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H198" s="25" t="inlineStr">
+        <is>
+          <t>Fresh anonymous browser context; production read-only.</t>
+        </is>
+      </c>
+      <c r="I198" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/footer-data.ts</t>
+        </is>
+      </c>
+      <c r="J198" s="25" t="inlineStr">
+        <is>
+          <t>1. Open /kr.
+2. Click the 사업자정보확인 button (the FTC page is stubbed by the test).</t>
+        </is>
+      </c>
+      <c r="K198" s="25" t="inlineStr">
+        <is>
+          <t>A new tab opens https://www.ftc.go.kr/bizCommPop.do with wrkr_no=8778803313, the same number as the footer's 사업자번호.</t>
+        </is>
+      </c>
+      <c r="L198" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M198" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N198" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O198" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/navigation/footer.spec.ts</t>
+        </is>
+      </c>
+      <c r="P198" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-017 footer 사업자정보확인 opens the FTC lookup for the registration number it shows</t>
+        </is>
+      </c>
+      <c r="Q198" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production @discovery</t>
+        </is>
+      </c>
+      <c r="R198" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S198" s="25" t="inlineStr">
+        <is>
+          <t>Explored read-only on production on 2026-10-30; dev-1 matched. No orders, accounts, messages or admin data are created.</t>
+        </is>
+      </c>
+      <c r="T198" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U198" s="15" t="n"/>
+      <c r="V198" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W198" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X198" s="15" t="inlineStr">
+        <is>
+          <t>production 3/3 and dev-1 3/3; retries=0. Note: the button shares data-testid category-footer-link-business with the 대량주문·기업 견적 link.</t>
+        </is>
+      </c>
+      <c r="Y198" s="25" t="n"/>
+    </row>
+    <row r="199" ht="150" customHeight="1">
+      <c r="A199" s="12" t="inlineStr">
+        <is>
+          <t>MS-NAV-018</t>
+        </is>
+      </c>
+      <c r="B199" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C199" s="25" t="inlineStr">
+        <is>
+          <t>1. Smoke &amp; core navigation</t>
+        </is>
+      </c>
+      <c r="D199" s="25" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="E199" s="25" t="inlineStr">
+        <is>
+          <t>home footer CTAs open the die-cut sticker product and an inquiry form that 취소 closes</t>
+        </is>
+      </c>
+      <c r="F199" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G199" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H199" s="25" t="inlineStr">
+        <is>
+          <t>Fresh anonymous browser context; production read-only.</t>
+        </is>
+      </c>
+      <c r="I199" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/footer-data.ts</t>
+        </is>
+      </c>
+      <c r="J199" s="25" t="inlineStr">
+        <is>
+          <t>1. Open /kr and check the footer CTA band (처음 주문해도 걱정할 필요 없어요).
+2. Click 제작 문의하기, check the inquiry form, click 취소.
+3. Click 바로 주문하기.</t>
+        </is>
+      </c>
+      <c r="K199" s="25" t="inlineStr">
+        <is>
+          <t>The inquiry form opens with its 문의 heading and 취소 closes it. 바로 주문하기 opens /kr/stickers/die-cut-sticker (자유형 조각스티커), whose footer has no CTA band (home-only).</t>
+        </is>
+      </c>
+      <c r="L199" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M199" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N199" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O199" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/navigation/footer.spec.ts</t>
+        </is>
+      </c>
+      <c r="P199" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-018 home footer CTAs open the die-cut sticker product and an inquiry form that 취소 closes</t>
+        </is>
+      </c>
+      <c r="Q199" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production @discovery</t>
+        </is>
+      </c>
+      <c r="R199" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S199" s="25" t="inlineStr">
+        <is>
+          <t>Explored read-only on production on 2026-10-30; dev-1 matched. No orders, accounts, messages or admin data are created.</t>
+        </is>
+      </c>
+      <c r="T199" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U199" s="15" t="n"/>
+      <c r="V199" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W199" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X199" s="15" t="inlineStr">
+        <is>
+          <t>production 3/3 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y199" s="25" t="n"/>
+    </row>
+    <row r="200" ht="150" customHeight="1">
+      <c r="A200" s="12" t="inlineStr">
+        <is>
+          <t>MS-NAV-019</t>
+        </is>
+      </c>
+      <c r="B200" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C200" s="25" t="inlineStr">
+        <is>
+          <t>1. Smoke &amp; core navigation</t>
+        </is>
+      </c>
+      <c r="D200" s="25" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="E200" s="25" t="inlineStr">
+        <is>
+          <t>footer inquiry form is announced as a dialog, takes focus and closes on Escape</t>
+        </is>
+      </c>
+      <c r="F200" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G200" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H200" s="25" t="inlineStr">
+        <is>
+          <t>Fresh anonymous browser context; production read-only.</t>
+        </is>
+      </c>
+      <c r="I200" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/footer-data.ts</t>
+        </is>
+      </c>
+      <c r="J200" s="25" t="inlineStr">
+        <is>
+          <t>1. Open /kr.
+2. Click 제작 문의하기 in the footer.
+3. Check the form's role and focus, press Escape.</t>
+        </is>
+      </c>
+      <c r="K200" s="25" t="inlineStr">
+        <is>
+          <t>The form is a dialog named 문의, focus moves into it, Escape closes it and focus returns to 제작 문의하기.</t>
+        </is>
+      </c>
+      <c r="L200" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M200" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N200" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O200" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/navigation/footer.spec.ts</t>
+        </is>
+      </c>
+      <c r="P200" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-019 footer inquiry form is announced as a dialog, takes focus and closes on Escape</t>
+        </is>
+      </c>
+      <c r="Q200" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production @discovery</t>
+        </is>
+      </c>
+      <c r="R200" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S200" s="25" t="inlineStr">
+        <is>
+          <t>Explored read-only on production on 2026-10-30; dev-1 matched. No orders, accounts, messages or admin data are created.</t>
+        </is>
+      </c>
+      <c r="T200" s="14" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="U200" s="15" t="inlineStr">
+        <is>
+          <t>MUS-QA-026</t>
+        </is>
+      </c>
+      <c r="V200" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W200" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X200" s="15" t="inlineStr">
+        <is>
+          <t>production 3/3 and dev-1 3/3; retries=0. Marked test.fail for MUS-QA-026: no dialog role or name, focus stays on the trigger, Escape does nothing, 취소 drops focus to &lt;body&gt;.</t>
+        </is>
+      </c>
+      <c r="Y200" s="25" t="n"/>
+    </row>
+    <row r="201" ht="150" customHeight="1">
+      <c r="A201" s="12" t="inlineStr">
+        <is>
+          <t>MS-CHK-007</t>
+        </is>
+      </c>
+      <c r="B201" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C201" s="25" t="inlineStr">
+        <is>
+          <t>6. Checkout &amp; money path</t>
+        </is>
+      </c>
+      <c r="D201" s="25" t="inlineStr">
+        <is>
+          <t>Checkout page</t>
+        </is>
+      </c>
+      <c r="E201" s="25" t="inlineStr">
+        <is>
+          <t>payment options are a single choice that starts on Npay</t>
+        </is>
+      </c>
+      <c r="F201" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G201" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H201" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item; nothing is submitted or paid.</t>
+        </is>
+      </c>
+      <c r="I201" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/checkout-data.ts</t>
+        </is>
+      </c>
+      <c r="J201" s="25" t="inlineStr">
+        <is>
+          <t>1. As a guest, add 자유형 조각스티커 75x75 x100 to the cart and open /kr/checkout.
+2. Read the 결제 수단 options.
+3. Select each option in turn, then Npay again.</t>
+        </is>
+      </c>
+      <c r="K201" s="25" t="inlineStr">
+        <is>
+          <t>Eight options in order: Npay, 카카오페이, 토스페이, 페이코 (간편결제); 신용카드, 실시간 계좌이체, 가상계좌, 무통장 입금 (기타 결제). Npay is pressed on arrival; selecting any option makes it the only pressed one.</t>
+        </is>
+      </c>
+      <c r="L201" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M201" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N201" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O201" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
+        </is>
+      </c>
+      <c r="P201" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-007 payment options are a single choice that starts on Npay</t>
+        </is>
+      </c>
+      <c r="Q201" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production</t>
+        </is>
+      </c>
+      <c r="R201" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S201" s="25" t="inlineStr">
+        <is>
+          <t>Checkout redesign, explored read-only on production on 2026-10-30 with a guest cart; dev-1 matched apart from two payment labels (Naver Pay, 무통장 입), which the test self-heals by position.</t>
+        </is>
+      </c>
+      <c r="T201" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U201" s="15" t="n"/>
+      <c r="V201" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W201" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X201" s="15" t="inlineStr">
+        <is>
+          <t>production 2/2 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y201" s="25" t="n"/>
+    </row>
+    <row r="202" ht="150" customHeight="1">
+      <c r="A202" s="12" t="inlineStr">
+        <is>
+          <t>MS-CHK-008</t>
+        </is>
+      </c>
+      <c r="B202" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C202" s="25" t="inlineStr">
+        <is>
+          <t>6. Checkout &amp; money path</t>
+        </is>
+      </c>
+      <c r="D202" s="25" t="inlineStr">
+        <is>
+          <t>Checkout page</t>
+        </is>
+      </c>
+      <c r="E202" s="25" t="inlineStr">
+        <is>
+          <t>무통장 입금 asks for the depositor name only while it is selected</t>
+        </is>
+      </c>
+      <c r="F202" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G202" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H202" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item; nothing is submitted or paid.</t>
+        </is>
+      </c>
+      <c r="I202" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/checkout-data.ts</t>
+        </is>
+      </c>
+      <c r="J202" s="25" t="inlineStr">
+        <is>
+          <t>1. As a guest, add 자유형 조각스티커 75x75 x100 to the cart and open /kr/checkout.
+2. Check there is no 입금자명 field.
+3. Select 무통장 입금.
+4. Select 신용카드.</t>
+        </is>
+      </c>
+      <c r="K202" s="25" t="inlineStr">
+        <is>
+          <t>Selecting 무통장 입금 shows the 입금자명 field, the 영업일 기준 1~2일 processing note and the 하나은행 account; switching to 신용카드 removes the field.</t>
+        </is>
+      </c>
+      <c r="L202" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M202" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N202" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O202" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
+        </is>
+      </c>
+      <c r="P202" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-008 무통장 입금 asks for the depositor name only while it is selected</t>
+        </is>
+      </c>
+      <c r="Q202" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production</t>
+        </is>
+      </c>
+      <c r="R202" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S202" s="25" t="inlineStr">
+        <is>
+          <t>Checkout redesign, explored read-only on production on 2026-10-30 with a guest cart; dev-1 matched apart from two payment labels (Naver Pay, 무통장 입), which the test self-heals by position.</t>
+        </is>
+      </c>
+      <c r="T202" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U202" s="15" t="n"/>
+      <c r="V202" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W202" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X202" s="15" t="inlineStr">
+        <is>
+          <t>production 2/2 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y202" s="25" t="n"/>
+    </row>
+    <row r="203" ht="150" customHeight="1">
+      <c r="A203" s="12" t="inlineStr">
+        <is>
+          <t>MS-CHK-009</t>
+        </is>
+      </c>
+      <c r="B203" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C203" s="25" t="inlineStr">
+        <is>
+          <t>6. Checkout &amp; money path</t>
+        </is>
+      </c>
+      <c r="D203" s="25" t="inlineStr">
+        <is>
+          <t>Checkout page</t>
+        </is>
+      </c>
+      <c r="E203" s="25" t="inlineStr">
+        <is>
+          <t>the address search fills the postal code and road address, which stay read-only</t>
+        </is>
+      </c>
+      <c r="F203" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G203" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H203" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item; nothing is submitted or paid.</t>
+        </is>
+      </c>
+      <c r="I203" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/checkout-data.ts</t>
+        </is>
+      </c>
+      <c r="J203" s="25" t="inlineStr">
+        <is>
+          <t>1. As a guest, add 자유형 조각스티커 75x75 x100 to the cart and open /kr/checkout.
+2. Check 우편번호 and 도로명 주소 are disabled and 상세 주소 is editable.
+3. Click 주소 찾기, search 테헤란로 152 in the Kakao postcode search and pick the road address.</t>
+        </is>
+      </c>
+      <c r="K203" s="25" t="inlineStr">
+        <is>
+          <t>우편번호 becomes 06236 and 도로명 주소 starts with 서울 강남구 테헤란로 152; both stay disabled and 상세 주소 stays editable.</t>
+        </is>
+      </c>
+      <c r="L203" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M203" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N203" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O203" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
+        </is>
+      </c>
+      <c r="P203" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-009 the address search fills the postal code and road address, which stay read-only</t>
+        </is>
+      </c>
+      <c r="Q203" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production</t>
+        </is>
+      </c>
+      <c r="R203" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S203" s="25" t="inlineStr">
+        <is>
+          <t>Checkout redesign, explored read-only on production on 2026-10-30 with a guest cart; dev-1 matched apart from two payment labels (Naver Pay, 무통장 입), which the test self-heals by position.</t>
+        </is>
+      </c>
+      <c r="T203" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U203" s="15" t="n"/>
+      <c r="V203" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W203" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X203" s="15" t="inlineStr">
+        <is>
+          <t>production 2/2 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y203" s="25" t="n"/>
+    </row>
+    <row r="204" ht="150" customHeight="1">
+      <c r="A204" s="12" t="inlineStr">
+        <is>
+          <t>MS-CHK-010</t>
+        </is>
+      </c>
+      <c r="B204" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C204" s="25" t="inlineStr">
+        <is>
+          <t>6. Checkout &amp; money path</t>
+        </is>
+      </c>
+      <c r="D204" s="25" t="inlineStr">
+        <is>
+          <t>Checkout page</t>
+        </is>
+      </c>
+      <c r="E204" s="25" t="inlineStr">
+        <is>
+          <t>일반 배송 promises a delivery window after today and charges the fee the summary shows</t>
+        </is>
+      </c>
+      <c r="F204" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G204" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H204" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item; nothing is submitted or paid.</t>
+        </is>
+      </c>
+      <c r="I204" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/checkout-data.ts</t>
+        </is>
+      </c>
+      <c r="J204" s="25" t="inlineStr">
+        <is>
+          <t>1. As a guest, add 자유형 조각스티커 75x75 x100 to the cart and open /kr/checkout.
+2. Read the 일반 배송 option (예상 배송일 and fee) and the order summary.</t>
+        </is>
+      </c>
+      <c r="K204" s="25" t="inlineStr">
+        <is>
+          <t>The 오늘 주문 확정 시 도착 예정일 note is shown. The window starts after today (Seoul), ends on or after its start, within 7 days of today, and the option fee equals the summary 배송비.</t>
+        </is>
+      </c>
+      <c r="L204" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M204" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N204" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O204" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
+        </is>
+      </c>
+      <c r="P204" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-010 일반 배송 promises a delivery window after today and charges the fee the summary shows</t>
+        </is>
+      </c>
+      <c r="Q204" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production</t>
+        </is>
+      </c>
+      <c r="R204" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S204" s="25" t="inlineStr">
+        <is>
+          <t>Checkout redesign, explored read-only on production on 2026-10-30 with a guest cart; dev-1 matched apart from two payment labels (Naver Pay, 무통장 입), which the test self-heals by position.</t>
+        </is>
+      </c>
+      <c r="T204" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U204" s="15" t="n"/>
+      <c r="V204" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W204" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X204" s="15" t="inlineStr">
+        <is>
+          <t>production 2/2 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y204" s="25" t="n"/>
+    </row>
+    <row r="205" ht="150" customHeight="1">
+      <c r="A205" s="12" t="inlineStr">
+        <is>
+          <t>MS-CHK-011</t>
+        </is>
+      </c>
+      <c r="B205" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C205" s="25" t="inlineStr">
+        <is>
+          <t>6. Checkout &amp; money path</t>
+        </is>
+      </c>
+      <c r="D205" s="25" t="inlineStr">
+        <is>
+          <t>Checkout page</t>
+        </is>
+      </c>
+      <c r="E205" s="25" t="inlineStr">
+        <is>
+          <t>위탁배송 adds a sender name and company block that unticking removes</t>
+        </is>
+      </c>
+      <c r="F205" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G205" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H205" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item; nothing is submitted or paid.</t>
+        </is>
+      </c>
+      <c r="I205" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/checkout-data.ts</t>
+        </is>
+      </c>
+      <c r="J205" s="25" t="inlineStr">
+        <is>
+          <t>1. As a guest, add 자유형 조각스티커 75x75 x100 to the cart and open /kr/checkout.
+2. Tick 위탁배송 이용하기.
+3. Untick it.</t>
+        </is>
+      </c>
+      <c r="K205" s="25" t="inlineStr">
+        <is>
+          <t>Ticking adds a second 성함 and 회사명 (선택사항) field with the note 주소 저장은 회원만 이용할 수 있습니다.; unticking removes them.</t>
+        </is>
+      </c>
+      <c r="L205" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M205" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N205" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O205" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
+        </is>
+      </c>
+      <c r="P205" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-011 위탁배송 adds a sender name and company block that unticking removes</t>
+        </is>
+      </c>
+      <c r="Q205" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production</t>
+        </is>
+      </c>
+      <c r="R205" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S205" s="25" t="inlineStr">
+        <is>
+          <t>Checkout redesign, explored read-only on production on 2026-10-30 with a guest cart; dev-1 matched apart from two payment labels (Naver Pay, 무통장 입), which the test self-heals by position.</t>
+        </is>
+      </c>
+      <c r="T205" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U205" s="15" t="inlineStr">
+        <is>
+          <t>MUS-QA-027</t>
+        </is>
+      </c>
+      <c r="V205" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W205" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X205" s="15" t="inlineStr">
+        <is>
+          <t>production 2/2 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y205" s="25" t="n"/>
+    </row>
+    <row r="206" ht="150" customHeight="1">
+      <c r="A206" s="12" t="inlineStr">
+        <is>
+          <t>MS-CHK-012</t>
+        </is>
+      </c>
+      <c r="B206" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C206" s="25" t="inlineStr">
+        <is>
+          <t>6. Checkout &amp; money path</t>
+        </is>
+      </c>
+      <c r="D206" s="25" t="inlineStr">
+        <is>
+          <t>Checkout page</t>
+        </is>
+      </c>
+      <c r="E206" s="25" t="inlineStr">
+        <is>
+          <t>checkout info tips explain email, address, 위탁배송 and the shipping fee</t>
+        </is>
+      </c>
+      <c r="F206" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G206" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H206" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item; nothing is submitted or paid.</t>
+        </is>
+      </c>
+      <c r="I206" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/checkout-data.ts</t>
+        </is>
+      </c>
+      <c r="J206" s="25" t="inlineStr">
+        <is>
+          <t>1. As a guest, add 자유형 조각스티커 75x75 x100 to the cart and open /kr/checkout.
+2. Open each info icon in turn: email, 도로명 주소, 위탁배송, 배송비 정보 보기.</t>
+        </is>
+      </c>
+      <c r="K206" s="25" t="inlineStr">
+        <is>
+          <t>Each shows its explanation: 이메일 인증 및 업데이트; 도로명 주소 (use 주소 찾기); 위탁배송 이용하기 (머스티커가 제작, 포장, 배송까지 대신 진행); 배송비 (5만원 이상 주문 시 무료배송).</t>
+        </is>
+      </c>
+      <c r="L206" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M206" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N206" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O206" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
+        </is>
+      </c>
+      <c r="P206" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-012 checkout info tips explain email, address, 위탁배송 and the shipping fee</t>
+        </is>
+      </c>
+      <c r="Q206" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production</t>
+        </is>
+      </c>
+      <c r="R206" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S206" s="25" t="inlineStr">
+        <is>
+          <t>Checkout redesign, explored read-only on production on 2026-10-30 with a guest cart; dev-1 matched apart from two payment labels (Naver Pay, 무통장 입), which the test self-heals by position.</t>
+        </is>
+      </c>
+      <c r="T206" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U206" s="15" t="n"/>
+      <c r="V206" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W206" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X206" s="15" t="inlineStr">
+        <is>
+          <t>production 2/2 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y206" s="25" t="n"/>
+    </row>
+    <row r="207" ht="150" customHeight="1">
+      <c r="A207" s="12" t="inlineStr">
+        <is>
+          <t>MS-CHK-013</t>
+        </is>
+      </c>
+      <c r="B207" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C207" s="25" t="inlineStr">
+        <is>
+          <t>6. Checkout &amp; money path</t>
+        </is>
+      </c>
+      <c r="D207" s="25" t="inlineStr">
+        <is>
+          <t>Checkout page</t>
+        </is>
+      </c>
+      <c r="E207" s="25" t="inlineStr">
+        <is>
+          <t>로그인 opens sign-in over the checkout, and 주문 요약 수정 returns to the cart</t>
+        </is>
+      </c>
+      <c r="F207" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G207" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H207" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item; nothing is submitted or paid.</t>
+        </is>
+      </c>
+      <c r="I207" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/checkout-data.ts</t>
+        </is>
+      </c>
+      <c r="J207" s="25" t="inlineStr">
+        <is>
+          <t>1. As a guest, add 자유형 조각스티커 75x75 x100 to the cart and open /kr/checkout.
+2. Click 로그인 in 연락처 정보.
+3. Reopen /kr/checkout and click 주문 요약 수정.</t>
+        </is>
+      </c>
+      <c r="K207" s="25" t="inlineStr">
+        <is>
+          <t>A sign-in dialog with 회원 and 비회원 tabs opens while the URL stays /kr/checkout; 주문 요약 수정 opens /kr/cart.</t>
+        </is>
+      </c>
+      <c r="L207" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M207" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N207" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O207" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
+        </is>
+      </c>
+      <c r="P207" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-013 로그인 opens sign-in over the checkout, and 주문 요약 수정 returns to the cart</t>
+        </is>
+      </c>
+      <c r="Q207" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production</t>
+        </is>
+      </c>
+      <c r="R207" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S207" s="25" t="inlineStr">
+        <is>
+          <t>Checkout redesign, explored read-only on production on 2026-10-30 with a guest cart; dev-1 matched apart from two payment labels (Naver Pay, 무통장 입), which the test self-heals by position.</t>
+        </is>
+      </c>
+      <c r="T207" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="U207" s="15" t="n"/>
+      <c r="V207" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W207" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X207" s="15" t="inlineStr">
+        <is>
+          <t>production 2/2 and dev-1 3/3; retries=0.</t>
+        </is>
+      </c>
+      <c r="Y207" s="25" t="n"/>
+    </row>
+    <row r="208" ht="150" customHeight="1">
+      <c r="A208" s="12" t="inlineStr">
+        <is>
+          <t>MS-CHK-014</t>
+        </is>
+      </c>
+      <c r="B208" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="C208" s="25" t="inlineStr">
+        <is>
+          <t>6. Checkout &amp; money path</t>
+        </is>
+      </c>
+      <c r="D208" s="25" t="inlineStr">
+        <is>
+          <t>Checkout page</t>
+        </is>
+      </c>
+      <c r="E208" s="25" t="inlineStr">
+        <is>
+          <t>checkout info icons have accessible names</t>
+        </is>
+      </c>
+      <c r="F208" s="13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G208" s="25" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H208" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item; nothing is submitted or paid.</t>
+        </is>
+      </c>
+      <c r="I208" s="25" t="inlineStr">
+        <is>
+          <t>tests/fixtures/checkout-data.ts</t>
+        </is>
+      </c>
+      <c r="J208" s="25" t="inlineStr">
+        <is>
+          <t>1. As a guest, add 자유형 조각스티커 75x75 x100 to the cart and open /kr/checkout.
+2. Read the accessible name of every info icon.</t>
+        </is>
+      </c>
+      <c r="K208" s="25" t="inlineStr">
+        <is>
+          <t>Every info icon button has an accessible name (as 배송비 정보 보기 does).</t>
+        </is>
+      </c>
+      <c r="L208" s="13" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="M208" s="25" t="inlineStr">
+        <is>
+          <t>Production-safe</t>
+        </is>
+      </c>
+      <c r="N208" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O208" s="25" t="inlineStr">
+        <is>
+          <t>tests/e2e/storefront/checkout/checkout-page.spec.ts</t>
+        </is>
+      </c>
+      <c r="P208" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-014 checkout info icons have accessible names</t>
+        </is>
+      </c>
+      <c r="Q208" s="25" t="inlineStr">
+        <is>
+          <t>@regression @production</t>
+        </is>
+      </c>
+      <c r="R208" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S208" s="25" t="inlineStr">
+        <is>
+          <t>Checkout redesign, explored read-only on production on 2026-10-30 with a guest cart; dev-1 matched apart from two payment labels (Naver Pay, 무통장 입), which the test self-heals by position.</t>
+        </is>
+      </c>
+      <c r="T208" s="14" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="U208" s="15" t="inlineStr">
+        <is>
+          <t>MUS-QA-027</t>
+        </is>
+      </c>
+      <c r="V208" s="15" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="W208" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="X208" s="15" t="inlineStr">
+        <is>
+          <t>production 2/2 and dev-1 3/3; retries=0. Marked test.fail for MUS-QA-027.</t>
+        </is>
+      </c>
+      <c r="Y208" s="25" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y192"/>
+  <autoFilter ref="A1:Y208"/>
   <dataValidations count="3">
-    <dataValidation sqref="T2:T192" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="T2:T208" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Partial,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L192" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="L2:L208" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Automated,Partial,Planned,Manual,Withdrawn"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F192" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F2:F208" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
@@ -34763,6 +36713,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -35249,6 +37200,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
@@ -35395,6 +37347,7 @@
       <c r="F24" s="25" t="n"/>
       <c r="G24" s="25" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
@@ -35527,6 +37480,7 @@
       <c r="F33" s="26" t="n"/>
       <c r="G33" s="27" t="n"/>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
@@ -35663,6 +37617,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="25.5" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -35737,31 +37692,31 @@
         </is>
       </c>
       <c r="B5" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A5)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A5,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A5,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A5,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A5,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A5,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A5,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F5" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A5,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A5,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G5" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A5,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A5,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H5" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A5,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A5,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I5" s="19">
@@ -35773,15 +37728,15 @@
         <v/>
       </c>
       <c r="K5" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A5,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A5,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A5,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A5,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L5" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A5,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A5,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M5" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A5)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A5)</f>
         <v/>
       </c>
     </row>
@@ -35792,31 +37747,31 @@
         </is>
       </c>
       <c r="B6" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A6)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A6,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A6,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A6,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A6,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A6,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A6,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F6" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A6,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A6,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G6" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A6,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A6,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H6" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A6,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A6,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I6" s="19">
@@ -35828,15 +37783,15 @@
         <v/>
       </c>
       <c r="K6" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A6,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A6,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A6,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A6,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L6" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A6,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A6,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M6" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A6)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A6)</f>
         <v/>
       </c>
     </row>
@@ -35847,31 +37802,31 @@
         </is>
       </c>
       <c r="B7" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A7)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A7,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A7,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A7,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A7,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A7,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A7,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F7" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A7,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A7,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G7" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A7,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A7,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H7" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A7,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A7,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I7" s="19">
@@ -35883,15 +37838,15 @@
         <v/>
       </c>
       <c r="K7" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A7,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A7,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A7,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A7,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L7" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A7,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A7,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M7" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A7)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A7)</f>
         <v/>
       </c>
     </row>
@@ -35902,31 +37857,31 @@
         </is>
       </c>
       <c r="B8" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A8)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A8,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A8,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A8,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A8,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A8,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A8,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A8,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A8,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A8,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A8,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A8,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A8,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I8" s="19">
@@ -35938,15 +37893,15 @@
         <v/>
       </c>
       <c r="K8" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A8,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A8,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A8,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A8,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L8" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A8,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A8,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M8" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A8)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A8)</f>
         <v/>
       </c>
     </row>
@@ -35957,31 +37912,31 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A9)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A9,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A9,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A9,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A9,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A9,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A9,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A9,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A9,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G9" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A9,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A9,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A9,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A9,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I9" s="19">
@@ -35993,15 +37948,15 @@
         <v/>
       </c>
       <c r="K9" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A9,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A9,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A9,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A9,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L9" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A9,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A9,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M9" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A9)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A9)</f>
         <v/>
       </c>
     </row>
@@ -36012,31 +37967,31 @@
         </is>
       </c>
       <c r="B10" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A10)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A10,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A10,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A10,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A10,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A10,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A10,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A10,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A10,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A10,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A10,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H10" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A10,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A10,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I10" s="19">
@@ -36048,15 +38003,15 @@
         <v/>
       </c>
       <c r="K10" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A10,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A10,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A10,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A10,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L10" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A10,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A10,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M10" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A10)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A10)</f>
         <v/>
       </c>
     </row>
@@ -36067,31 +38022,31 @@
         </is>
       </c>
       <c r="B11" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A11)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A11,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A11,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A11,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A11,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A11,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A11,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A11,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A11,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A11,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A11,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A11,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A11,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I11" s="19">
@@ -36103,15 +38058,15 @@
         <v/>
       </c>
       <c r="K11" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A11,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A11,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A11,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A11,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L11" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A11,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A11,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M11" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A11)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A11)</f>
         <v/>
       </c>
     </row>
@@ -36122,31 +38077,31 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A12)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A12,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A12,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A12,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A12,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A12,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A12,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F12" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A12,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A12,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G12" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A12,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A12,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H12" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A12,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A12,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I12" s="19">
@@ -36158,15 +38113,15 @@
         <v/>
       </c>
       <c r="K12" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A12,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A12,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A12,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A12,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L12" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A12,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A12,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M12" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A12)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A12)</f>
         <v/>
       </c>
     </row>
@@ -36177,31 +38132,31 @@
         </is>
       </c>
       <c r="B13" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A13)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A13,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A13,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D13" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A13,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A13,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A13,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A13,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F13" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A13,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A13,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G13" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A13,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A13,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H13" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A13,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A13,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I13" s="19">
@@ -36213,15 +38168,15 @@
         <v/>
       </c>
       <c r="K13" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A13,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A13,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A13,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A13,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L13" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A13,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A13,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M13" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A13)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A13)</f>
         <v/>
       </c>
     </row>
@@ -36232,31 +38187,31 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A14)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A14,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A14,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A14,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A14,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A14,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A14,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F14" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A14,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A14,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G14" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A14,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A14,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H14" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A14,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A14,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I14" s="19">
@@ -36268,15 +38223,15 @@
         <v/>
       </c>
       <c r="K14" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A14,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A14,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A14,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A14,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L14" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A14,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A14,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M14" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A14)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A14)</f>
         <v/>
       </c>
     </row>
@@ -36287,31 +38242,31 @@
         </is>
       </c>
       <c r="B15" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A15)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A15,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A15,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D15" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A15,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A15,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A15,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A15,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F15" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A15,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A15,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G15" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A15,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A15,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H15" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A15,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A15,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I15" s="19">
@@ -36323,15 +38278,15 @@
         <v/>
       </c>
       <c r="K15" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A15,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A15,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A15,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A15,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L15" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A15,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A15,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M15" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A15)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A15)</f>
         <v/>
       </c>
     </row>
@@ -36342,31 +38297,31 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A16)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A16,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A16,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A16,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A16,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A16,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A16,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F16" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A16,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A16,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G16" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A16,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A16,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H16" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A16,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A16,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I16" s="19">
@@ -36378,15 +38333,15 @@
         <v/>
       </c>
       <c r="K16" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A16,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A16,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A16,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A16,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L16" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A16,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A16,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M16" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A16)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A16)</f>
         <v/>
       </c>
     </row>
@@ -36397,31 +38352,31 @@
         </is>
       </c>
       <c r="B17" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A17)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A17)</f>
         <v/>
       </c>
       <c r="C17" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A17,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A17,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A17,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A17,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A17,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A17,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A17,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A17,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G17" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A17,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A17,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H17" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A17,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A17,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I17" s="19">
@@ -36433,15 +38388,15 @@
         <v/>
       </c>
       <c r="K17" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A17,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A17,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A17,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A17,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L17" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A17,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A17,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M17" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A17)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A17)</f>
         <v/>
       </c>
     </row>
@@ -36452,31 +38407,31 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A18)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A18,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A18,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A18,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A18,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A18,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A18,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F18" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A18,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A18,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G18" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A18,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A18,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H18" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A18,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A18,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I18" s="19">
@@ -36488,15 +38443,15 @@
         <v/>
       </c>
       <c r="K18" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A18,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A18,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A18,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A18,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L18" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A18,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A18,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M18" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A18)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A18)</f>
         <v/>
       </c>
     </row>
@@ -36507,31 +38462,31 @@
         </is>
       </c>
       <c r="B19" s="13">
-        <f>COUNTIF('Test Cases'!$C$2:$C$192,$A19)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$208,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A19,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A19,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D19" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A19,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A19,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A19,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A19,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F19" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A19,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A19,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G19" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A19,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A19,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H19" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A19,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A19,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I19" s="19">
@@ -36543,15 +38498,15 @@
         <v/>
       </c>
       <c r="K19" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A19,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$192,$A19,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A19,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$C$2:$C$208,$A19,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L19" s="13">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$192,$A19,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$208,$A19,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M19" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$C$2:$C$192,$A19)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$C$2:$C$208,$A19)</f>
         <v/>
       </c>
     </row>
@@ -36610,6 +38565,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
@@ -36703,31 +38659,31 @@
         </is>
       </c>
       <c r="B24" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$192,$A24)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$208,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A24,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A24,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A24,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A24,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A24,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A24,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F24" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A24,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A24,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G24" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A24,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A24,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H24" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A24,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A24,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I24" s="19">
@@ -36739,15 +38695,15 @@
         <v/>
       </c>
       <c r="K24" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A24,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$B$2:$B$192,$A24,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A24,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$B$2:$B$208,$A24,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L24" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A24,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A24,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M24" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$B$2:$B$192,$A24)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$B$2:$B$208,$A24)</f>
         <v/>
       </c>
     </row>
@@ -36758,31 +38714,31 @@
         </is>
       </c>
       <c r="B25" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$192,$A25)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$208,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A25,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A25,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A25,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A25,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E25" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A25,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A25,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F25" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A25,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A25,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G25" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A25,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A25,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H25" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A25,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A25,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I25" s="19">
@@ -36794,15 +38750,15 @@
         <v/>
       </c>
       <c r="K25" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A25,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$B$2:$B$192,$A25,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A25,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$B$2:$B$208,$A25,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L25" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A25,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A25,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M25" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$B$2:$B$192,$A25)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$B$2:$B$208,$A25)</f>
         <v/>
       </c>
     </row>
@@ -36813,31 +38769,31 @@
         </is>
       </c>
       <c r="B26" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$192,$A26)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$208,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A26,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A26,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A26,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A26,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E26" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A26,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A26,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F26" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A26,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A26,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G26" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A26,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A26,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H26" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A26,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A26,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I26" s="19">
@@ -36849,15 +38805,15 @@
         <v/>
       </c>
       <c r="K26" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A26,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$B$2:$B$192,$A26,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A26,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$B$2:$B$208,$A26,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L26" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A26,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A26,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M26" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$B$2:$B$192,$A26)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$B$2:$B$208,$A26)</f>
         <v/>
       </c>
     </row>
@@ -36868,31 +38824,31 @@
         </is>
       </c>
       <c r="B27" s="13">
-        <f>COUNTIF('Test Cases'!$B$2:$B$192,$A27)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$208,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A27,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A27,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A27,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A27,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E27" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A27,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A27,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F27" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A27,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A27,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G27" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A27,'Test Cases'!$T$2:$T$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A27,'Test Cases'!$T$2:$T$208,"Partial")</f>
         <v/>
       </c>
       <c r="H27" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A27,'Test Cases'!$T$2:$T$192,"N/A")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A27,'Test Cases'!$T$2:$T$208,"N/A")</f>
         <v/>
       </c>
       <c r="I27" s="19">
@@ -36904,18 +38860,19 @@
         <v/>
       </c>
       <c r="K27" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A27,'Test Cases'!$L$2:$L$192,"Automated")+COUNTIFS('Test Cases'!$B$2:$B$192,$A27,'Test Cases'!$L$2:$L$192,"Partial")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A27,'Test Cases'!$L$2:$L$208,"Automated")+COUNTIFS('Test Cases'!$B$2:$B$208,$A27,'Test Cases'!$L$2:$L$208,"Partial")</f>
         <v/>
       </c>
       <c r="L27" s="13">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$192,$A27,'Test Cases'!$L$2:$L$192,"Planned")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$208,$A27,'Test Cases'!$L$2:$L$208,"Planned")</f>
         <v/>
       </c>
       <c r="M27" s="20">
-        <f>SUMIFS('Test Cases'!$R$2:$R$192,'Test Cases'!$B$2:$B$192,$A27)</f>
+        <f>SUMIFS('Test Cases'!$R$2:$R$208,'Test Cases'!$B$2:$B$208,$A27)</f>
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
@@ -36984,27 +38941,27 @@
         </is>
       </c>
       <c r="B31" s="13">
-        <f>COUNTIF('Test Cases'!$F$2:$F$192,$A31)</f>
+        <f>COUNTIF('Test Cases'!$F$2:$F$208,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A31,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A31,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D31" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A31,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A31,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E31" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A31,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A31,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F31" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A31,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A31,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G31" s="19">
-        <f>IFERROR(($B31-$C31-COUNTIFS('Test Cases'!$F$2:$F$192,$A31,'Test Cases'!$T$2:$T$192,"N/A"))/($B31-COUNTIFS('Test Cases'!$F$2:$F$192,$A31,'Test Cases'!$T$2:$T$192,"N/A")),0)</f>
+        <f>IFERROR(($B31-$C31-COUNTIFS('Test Cases'!$F$2:$F$208,$A31,'Test Cases'!$T$2:$T$208,"N/A"))/($B31-COUNTIFS('Test Cases'!$F$2:$F$208,$A31,'Test Cases'!$T$2:$T$208,"N/A")),0)</f>
         <v/>
       </c>
       <c r="H31" s="25" t="inlineStr">
@@ -37025,27 +38982,27 @@
         </is>
       </c>
       <c r="B32" s="13">
-        <f>COUNTIF('Test Cases'!$F$2:$F$192,$A32)</f>
+        <f>COUNTIF('Test Cases'!$F$2:$F$208,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A32,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A32,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D32" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A32,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A32,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E32" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A32,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A32,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F32" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A32,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A32,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G32" s="19">
-        <f>IFERROR(($B32-$C32-COUNTIFS('Test Cases'!$F$2:$F$192,$A32,'Test Cases'!$T$2:$T$192,"N/A"))/($B32-COUNTIFS('Test Cases'!$F$2:$F$192,$A32,'Test Cases'!$T$2:$T$192,"N/A")),0)</f>
+        <f>IFERROR(($B32-$C32-COUNTIFS('Test Cases'!$F$2:$F$208,$A32,'Test Cases'!$T$2:$T$208,"N/A"))/($B32-COUNTIFS('Test Cases'!$F$2:$F$208,$A32,'Test Cases'!$T$2:$T$208,"N/A")),0)</f>
         <v/>
       </c>
       <c r="H32" s="25" t="inlineStr">
@@ -37066,27 +39023,27 @@
         </is>
       </c>
       <c r="B33" s="13">
-        <f>COUNTIF('Test Cases'!$F$2:$F$192,$A33)</f>
+        <f>COUNTIF('Test Cases'!$F$2:$F$208,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A33,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A33,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D33" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A33,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A33,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E33" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A33,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A33,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F33" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A33,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A33,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G33" s="19">
-        <f>IFERROR(($B33-$C33-COUNTIFS('Test Cases'!$F$2:$F$192,$A33,'Test Cases'!$T$2:$T$192,"N/A"))/($B33-COUNTIFS('Test Cases'!$F$2:$F$192,$A33,'Test Cases'!$T$2:$T$192,"N/A")),0)</f>
+        <f>IFERROR(($B33-$C33-COUNTIFS('Test Cases'!$F$2:$F$208,$A33,'Test Cases'!$T$2:$T$208,"N/A"))/($B33-COUNTIFS('Test Cases'!$F$2:$F$208,$A33,'Test Cases'!$T$2:$T$208,"N/A")),0)</f>
         <v/>
       </c>
       <c r="H33" s="25" t="inlineStr">
@@ -37107,27 +39064,27 @@
         </is>
       </c>
       <c r="B34" s="13">
-        <f>COUNTIF('Test Cases'!$F$2:$F$192,$A34)</f>
+        <f>COUNTIF('Test Cases'!$F$2:$F$208,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A34,'Test Cases'!$T$2:$T$192,"Not Run")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A34,'Test Cases'!$T$2:$T$208,"Not Run")</f>
         <v/>
       </c>
       <c r="D34" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A34,'Test Cases'!$T$2:$T$192,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A34,'Test Cases'!$T$2:$T$208,"Pass")</f>
         <v/>
       </c>
       <c r="E34" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A34,'Test Cases'!$T$2:$T$192,"Fail")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A34,'Test Cases'!$T$2:$T$208,"Fail")</f>
         <v/>
       </c>
       <c r="F34" s="13">
-        <f>COUNTIFS('Test Cases'!$F$2:$F$192,$A34,'Test Cases'!$T$2:$T$192,"Blocked")</f>
+        <f>COUNTIFS('Test Cases'!$F$2:$F$208,$A34,'Test Cases'!$T$2:$T$208,"Blocked")</f>
         <v/>
       </c>
       <c r="G34" s="19">
-        <f>IFERROR(($B34-$C34-COUNTIFS('Test Cases'!$F$2:$F$192,$A34,'Test Cases'!$T$2:$T$192,"N/A"))/($B34-COUNTIFS('Test Cases'!$F$2:$F$192,$A34,'Test Cases'!$T$2:$T$192,"N/A")),0)</f>
+        <f>IFERROR(($B34-$C34-COUNTIFS('Test Cases'!$F$2:$F$208,$A34,'Test Cases'!$T$2:$T$208,"N/A"))/($B34-COUNTIFS('Test Cases'!$F$2:$F$208,$A34,'Test Cases'!$T$2:$T$208,"N/A")),0)</f>
         <v/>
       </c>
       <c r="H34" s="25" t="inlineStr">
@@ -37141,6 +39098,7 @@
       <c r="L34" s="26" t="n"/>
       <c r="M34" s="27" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
@@ -37167,7 +39125,7 @@
         </is>
       </c>
       <c r="B37" s="25">
-        <f>IF(COUNTIFS('Test Cases'!$F$2:$F$192,"Critical",'Test Cases'!$T$2:$T$192,"Not Run")=0,"YES","NO - "&amp;COUNTIFS('Test Cases'!$F$2:$F$192,"Critical",'Test Cases'!$T$2:$T$192,"Not Run")&amp;" not run")</f>
+        <f>IF(COUNTIFS('Test Cases'!$F$2:$F$208,"Critical",'Test Cases'!$T$2:$T$208,"Not Run")=0,"YES","NO - "&amp;COUNTIFS('Test Cases'!$F$2:$F$208,"Critical",'Test Cases'!$T$2:$T$208,"Not Run")&amp;" not run")</f>
         <v/>
       </c>
       <c r="C37" s="26" t="n"/>
@@ -37181,7 +39139,7 @@
         </is>
       </c>
       <c r="B38" s="25">
-        <f>IF(COUNTIFS('Test Cases'!$F$2:$F$192,"Critical",'Test Cases'!$T$2:$T$192,"Fail")=0,"YES","NO - "&amp;COUNTIFS('Test Cases'!$F$2:$F$192,"Critical",'Test Cases'!$T$2:$T$192,"Fail")&amp;" failed")</f>
+        <f>IF(COUNTIFS('Test Cases'!$F$2:$F$208,"Critical",'Test Cases'!$T$2:$T$208,"Fail")=0,"YES","NO - "&amp;COUNTIFS('Test Cases'!$F$2:$F$208,"Critical",'Test Cases'!$T$2:$T$208,"Fail")&amp;" failed")</f>
         <v/>
       </c>
       <c r="C38" s="26" t="n"/>
@@ -37195,7 +39153,7 @@
         </is>
       </c>
       <c r="B39" s="25">
-        <f>IF(COUNTIFS('Test Cases'!$F$2:$F$192,"High",'Test Cases'!$T$2:$T$192,"Not Run")=0,"YES","NO - "&amp;COUNTIFS('Test Cases'!$F$2:$F$192,"High",'Test Cases'!$T$2:$T$192,"Not Run")&amp;" not run")</f>
+        <f>IF(COUNTIFS('Test Cases'!$F$2:$F$208,"High",'Test Cases'!$T$2:$T$208,"Not Run")=0,"YES","NO - "&amp;COUNTIFS('Test Cases'!$F$2:$F$208,"High",'Test Cases'!$T$2:$T$208,"Not Run")&amp;" not run")</f>
         <v/>
       </c>
       <c r="C39" s="26" t="n"/>
@@ -37209,7 +39167,7 @@
         </is>
       </c>
       <c r="B40" s="25">
-        <f>IF(COUNTIFS('Test Cases'!$F$2:$F$192,"High",'Test Cases'!$T$2:$T$192,"Fail")=0,"YES","NO - "&amp;COUNTIFS('Test Cases'!$F$2:$F$192,"High",'Test Cases'!$T$2:$T$192,"Fail")&amp;" failed")</f>
+        <f>IF(COUNTIFS('Test Cases'!$F$2:$F$208,"High",'Test Cases'!$T$2:$T$208,"Fail")=0,"YES","NO - "&amp;COUNTIFS('Test Cases'!$F$2:$F$208,"High",'Test Cases'!$T$2:$T$208,"Fail")&amp;" failed")</f>
         <v/>
       </c>
       <c r="C40" s="26" t="n"/>
@@ -37223,7 +39181,7 @@
         </is>
       </c>
       <c r="B41" s="25">
-        <f>IF(COUNTIF('Test Cases'!$T$2:$T$192,"Blocked")=0,"YES","NO - "&amp;COUNTIF('Test Cases'!$T$2:$T$192,"Blocked")&amp;" blocked")</f>
+        <f>IF(COUNTIF('Test Cases'!$T$2:$T$208,"Blocked")=0,"YES","NO - "&amp;COUNTIF('Test Cases'!$T$2:$T$208,"Blocked")&amp;" blocked")</f>
         <v/>
       </c>
       <c r="C41" s="26" t="n"/>
@@ -37258,6 +39216,7 @@
       <c r="D43" s="26" t="n"/>
       <c r="E43" s="27" t="n"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
@@ -37289,7 +39248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -39115,6 +41074,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="24" t="inlineStr">
         <is>
@@ -39542,6 +41502,263 @@
       <c r="P28" s="25" t="n"/>
       <c r="Q28" s="25" t="n"/>
       <c r="R28" s="25" t="inlineStr">
+        <is>
+          <t>Not Retested</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>MUS-QA-026</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-019</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>Footer inquiry form (제작 문의하기) is not an accessible modal dialog</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>production and dev-1 / Chromium desktop</t>
+        </is>
+      </c>
+      <c r="I29" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous session on /kr.</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="inlineStr">
+        <is>
+          <t>1. Open /kr.
+2. Click 제작 문의하기 in the footer CTA band.
+3. Inspect the form in the accessibility tree; press Escape; then click 취소.</t>
+        </is>
+      </c>
+      <c r="K29" s="25" t="inlineStr">
+        <is>
+          <t>The form is exposed as a dialog with an accessible name (role="dialog", aria-modal, labelled by 문의), focus moves into it, Escape closes it, and focus returns to 제작 문의하기 on close (WCAG 2.1 4.1.2, 2.4.3).</t>
+        </is>
+      </c>
+      <c r="L29" s="25" t="inlineStr">
+        <is>
+          <t>.inquiry-modal has no role, aria-modal or name; focus stays on the trigger button; Escape leaves it open; 취소 closes it but focus falls to &lt;body&gt;.</t>
+        </is>
+      </c>
+      <c r="M29" s="25" t="inlineStr">
+        <is>
+          <t>MS-NAV-019 (test.fail), tests/e2e/storefront/navigation/footer.spec.ts; read-only exploration on production 2026-10-30.</t>
+        </is>
+      </c>
+      <c r="N29" s="25" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="O29" s="25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P29" s="25" t="n"/>
+      <c r="Q29" s="25" t="n"/>
+      <c r="R29" s="25" t="inlineStr">
+        <is>
+          <t>Not Retested</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>MUS-QA-027</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-014; MS-CHK-011</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>Checkout: three info icons have no accessible name, and the 위탁배송 sender fields reuse the recipient labels</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G30" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="H30" s="25" t="inlineStr">
+        <is>
+          <t>production and dev-1 / Chromium desktop</t>
+        </is>
+      </c>
+      <c r="I30" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item.</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="inlineStr">
+        <is>
+          <t>1. Add any item to the cart as a guest and open /kr/checkout.
+2. Inspect the info icons next to 이메일 주소, 도로명 주소 and 위탁배송 이용하기 in the accessibility tree.
+3. Tick 위탁배송 이용하기 and inspect the new fields.</t>
+        </is>
+      </c>
+      <c r="K30" s="25" t="inlineStr">
+        <is>
+          <t>Each icon button has a name (as the 배송비 icon has 배송비 정보 보기). The sender block has its own labels or a group name (e.g. 보내는 분) so it can be told apart from the recipient fields (WCAG 2.1 4.1.2, 1.3.1).</t>
+        </is>
+      </c>
+      <c r="L30" s="25" t="inlineStr">
+        <is>
+          <t>The three .ui-tooltip-icon-trigger buttons are announced as a bare "button". With 위탁배송 on there are two textboxes named 성함 and two named 회사명 (선택사항), with no grouping label.</t>
+        </is>
+      </c>
+      <c r="M30" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-014 (test.fail) and MS-CHK-011, tests/e2e/storefront/checkout/checkout-page.spec.ts; production and dev-1, 2026-10-30.</t>
+        </is>
+      </c>
+      <c r="N30" s="25" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="O30" s="25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P30" s="25" t="n"/>
+      <c r="Q30" s="25" t="n"/>
+      <c r="R30" s="25" t="inlineStr">
+        <is>
+          <t>Not Retested</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>MUS-QA-028</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>MS-CHK-002</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>Checkout company field placeholder misspelt 화사명 (should be 회사명)</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>Storefront</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>production and dev-1 / Chromium desktop</t>
+        </is>
+      </c>
+      <c r="I31" s="25" t="inlineStr">
+        <is>
+          <t>Anonymous guest cart with one item.</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="inlineStr">
+        <is>
+          <t>1. Add any item to the cart as a guest and open /kr/checkout.
+2. Read the placeholder of 회사명 (선택사항).</t>
+        </is>
+      </c>
+      <c r="K31" s="25" t="inlineStr">
+        <is>
+          <t>The placeholder reads 회사명을 입력해 주세요.</t>
+        </is>
+      </c>
+      <c r="L31" s="25" t="inlineStr">
+        <is>
+          <t>The placeholder reads 화사명을 입력해 주세요 (also in the 위탁배송 sender block).</t>
+        </is>
+      </c>
+      <c r="M31" s="25" t="inlineStr">
+        <is>
+          <t>Read-only exploration on production and dev-1, 2026-10-30. Not asserted by a test.</t>
+        </is>
+      </c>
+      <c r="N31" s="25" t="inlineStr">
+        <is>
+          <t>Claude / Playwright</t>
+        </is>
+      </c>
+      <c r="O31" s="25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P31" s="25" t="n"/>
+      <c r="Q31" s="25" t="n"/>
+      <c r="R31" s="25" t="inlineStr">
         <is>
           <t>Not Retested</t>
         </is>
@@ -39573,7 +41790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -39594,448 +41811,533 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23 - production exploration and regression coverage</t>
+          <t>2026-10-30 - dev-1 run, failing and flaky fixes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="51" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>New coverage</t>
+          <t>Copy and redesign</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11 read-only regression cases for root entry, FAQ footer deep links/reload, public content and search recovery/navigation. Stronger answer and filtering assertions for MS-DSC-004/005.</t>
+          <t>Checkout address is now a Kakao postcode search (MS-CHK-002 asserts the disabled 우편번호 field and 주소 찾기). Licenses footer label is 오픈소스고지 (MS-DSC-014). Confirmed on production.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="51" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Removed automation</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29 historical pricing/visual workbook cases marked Withdrawn to match the user-requested code removal; IDs retained. Coverage formulas and filters extended to include new cases.</t>
+          <t>MS-CHK-001: guest checkout is behind Cloudflare Turnstile on dev environments; marked test.fixme until a test site key or QA bypass exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Flaky fixes</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MS-CRT-005 waits for the guest-cart merge request; MS-DSC-012/013 find policy sections by title and wait for the popup to leave about:blank; MS-SHT-004 drops a redundant reload; guard forgives "Failed to fetch" only when an API fetch was seen aborted by navigation.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15 - workbook v1.3, suites</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Defect retest</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Static CDN woff2 CORS defect fixed (Access-Control-Allow-Origin: *); MS-API-009 expected-failure removed.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38.25" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Sub-Area</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Sub-Area now names the suite a case belongs to (for example Registration, Change password, Guest order lookup), instead of a short label per case: 175 cases in 42 suites. Each automated suite is one Playwright spec file, and the suite name is that file's test.describe title. Planned admin cases are grouped into the suites their specs will use.</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Footer suite</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>New Footer suite (MS-NAV-012 to 019, footer.spec.ts) from read-only production exploration: column links, new-tab links, 고객리뷰, contact and business details, the FTC 사업자정보확인 lookup and the CTAs. MUS-QA-026 logged for the inquiry form's dialog accessibility. Storefront URL checks now poll the URL (currentPath) instead of toHaveURL(predicate), which also waits for the load event.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38.25" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>Playwright Spec</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Spec files moved into one folder per module: navigation, configuration, sheet-size-rules, cart, checkout, inquiry and ux replace smoke, purchasing, validation and regression. checkout-destructive.spec.ts is now guest-checkout-payment.spec.ts. MS-AUTH-029 moved to the Guest order lookup suite and MS-CRT-005 to the new Guest cart merge suite. Test titles, tags and test logic are unchanged; still 2,473 tests.</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Checkout redesign</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MS-CHK-007 to 014 cover the redesigned checkout without submitting: payment options and 무통장 입금, the Kakao address search, 일반 배송 dates and fee, 위탁배송, info tips, the checkout 로그인 and 주문 요약 수정. MUS-QA-027 (nameless info icons, duplicate sender labels) and MUS-QA-028 (화사명 typo) logged.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38.25" customHeight="1"/>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14 - workbook v1.2, module-based TC IDs</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-23 - production exploration and regression coverage</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>TC IDs</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>MS-V2-### and MS-ADM-### are replaced by MS-&lt;MODULE&gt;-###, so an ID names its module (the Area): NAV, DSC, CFG, SHT, CRT, CHK, AUTH, ACC, INQ, API, UX, ADMO (admin order processing) and ADMA (admin access &amp; order management), numbered 001 upward in workbook order. MS-PRC-*, MS-SEC-* and MS-WAF-* are unchanged. 140 cases renamed.</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>New coverage</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11 read-only regression cases for root entry, FAQ footer deep links/reload, public content and search recovery/navigation. Stronger answer and filtering assertions for MS-DSC-004/005.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="38.25" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>Legacy ID</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>New column Y keeps each renamed case's previous ID. Older entries in this changelog, past Allure history and defect evidence still use the old IDs; look them up in that column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="38.25" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Suite</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Playwright test titles, comments, fixtures and docs renamed to match (178 test titles; no test logic changed; still 2,473 tests). Defect Log TC IDs and the cross-references in the other tabs updated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25.5" customHeight="1"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Removed automation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>29 historical pricing/visual workbook cases marked Withdrawn to match the user-requested code removal; IDs retained. Coverage formulas and filters extended to include new cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="38.25" customHeight="1"/>
+    <row r="16" ht="25.5" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15 - workbook v1.3, suites</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14 - workbook v1.1, MS-ADM-001 re-run, storefront explored</t>
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Sub-Area</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Sub-Area now names the suite a case belongs to (for example Registration, Change password, Guest order lookup), instead of a short label per case: 175 cases in 42 suites. Each automated suite is one Playwright spec file, and the suite name is that file's test.describe title. Planned admin cases are grouped into the suites their specs will use.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="28" t="inlineStr">
         <is>
-          <t>MS-ADM-001</t>
+          <t>Playwright Spec</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Re-run on static-1 (AO-2609180003-dev, AO-2609090017-dev) and updated for four product changes: the proof-approval dialog needs an acknowledgement tick before 최종 시안 승인; A-FPA is labelled 최종 승인 완료; Move to Production is gone, so Mark as Printing moves the order to 제작 진행 중 and the item straight to 인쇄 진행 중 (no PO); completed orders moved to 이전 내역, and an order search with no match shows 주문을 찾을 수 없습니다. Every step passes on the updated code (see Tester Notes on the case).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>Admin recording</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>A failed run showed that Playwright's failure screenshot and error context capture every open page, the admin panel included - the suite promised they did not. Admin specs now turn screenshots and traces off, and the adminPage fixture refuses to start otherwise.</t>
-        </is>
-      </c>
-    </row>
+          <t>Spec files moved into one folder per module: navigation, configuration, sheet-size-rules, cart, checkout, inquiry and ux replace smoke, purchasing, validation and regression. checkout-destructive.spec.ts is now guest-checkout-payment.spec.ts. MS-AUTH-029 moved to the Guest order lookup suite and MS-CRT-005 to the new Guest cart merge suite. Test titles, tags and test logic are unchanged; still 2,473 tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>Cases</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>MS-ADM-016 (Move to Production) withdrawn. MS-ADM-006, 013, 014, 015, 017, 020, 022, 030 and 031 updated to the new flow; Business Rules and Glossary likewise.</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14 - workbook v1.2, module-based TC IDs</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>Defects</t>
+          <t>TC IDs</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>MUS-QA-004 and MUS-QA-007 retested as fixed. MUS-QA-001 still reproduces for the printing and shipping entries. New: MUS-QA-010 and MUS-QA-011 (Low, to confirm).</t>
+          <t>MS-V2-### and MS-ADM-### are replaced by MS-&lt;MODULE&gt;-###, so an ID names its module (the Area): NAV, DSC, CFG, SHT, CRT, CHK, AUTH, ACC, INQ, API, UX, ADMO (admin order processing) and ADMA (admin access &amp; order management), numbered 001 upward in workbook order. MS-PRC-*, MS-SEC-* and MS-WAF-* are unchanged. 140 cases renamed.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>Environments</t>
+          <t>Legacy ID</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Instructions, gating, the Test Plan, Test Data and pricing ids now use the current environment names (static-1..8; development-1..4 retired and development-static/-static-2 renamed on 2026-09-25), and the CI schedule no longer lists the removed nightly regression. Historical "verified on development-N" notes are kept as they were.</t>
+          <t>New column Y keeps each renamed case's previous ID. Older entries in this changelog, past Allure history and defect evidence still use the old IDs; look them up in that column.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>Seed orders</t>
+          <t>Suite</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Re-checked on 2026-10-14: AO-2609180004-dev had been used elsewhere and AO-2609070004/0005-dev have two items, so one unused candidate is left (AO-2609070006-dev).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>Admin login</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>dev-static-1 has a tester OTP endpoint that returns the admin verification code; noted under MS-ADM-002 as a way to run admin cases without a person. Not used by the suite yet.</t>
-        </is>
-      </c>
-    </row>
+          <t>Playwright test titles, comments, fixtures and docs renamed to match (178 test titles; no test logic changed; still 2,473 tests). Defect Log TC IDs and the cross-references in the other tabs updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Storefront run</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Production-safe storefront specs (pricing excluded) before the updates: production 132 passed / 27 failed / 5 flaky; static-1 131 / 28 / 5. After: production 162 passed, 2 failed and 3 flaky (a tier-price repaint race, fixed and then 32/32 twice; transient 502s), 5 skipped; static-1 165 passed, 0 failed, 2 flaky (a network blip; MS-V2-035's timeout, now 90 s and passing on both), 5 skipped. Pricing on production: 261 of 2,286 failed, all on the replaced lettering and transfer tables; after the re-export 272/272 for those two and the other 2,016 unchanged and passing.</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14 - workbook v1.1, MS-ADM-001 re-run, storefront explored</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25.5" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>Order chooser</t>
+          <t>MS-ADM-001</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>다음 단계 now opens 어떻게 주문하시겠어요? (with a file / in the studio / file later), live on production. MS-V2-050 and 053 updated; new MS-V2-115.</t>
+          <t>Re-run on static-1 (AO-2609180003-dev, AO-2609090017-dev) and updated for four product changes: the proof-approval dialog needs an acknowledgement tick before 최종 시안 승인; A-FPA is labelled 최종 승인 완료; Move to Production is gone, so Mark as Printing moves the order to 제작 진행 중 and the item straight to 인쇄 진행 중 (no PO); completed orders moved to 이전 내역, and an order search with no match shows 주문을 찾을 수 없습니다. Every step passes on the updated code (see Tester Notes on the case).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>Design studio</t>
+          <t>Admin recording</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>New web studio (?studio=1): carries size and quantity over, prices 5% lower, refuses low-resolution designs. New MS-V2-116 and 117 (automated, production-safe) and MS-V2-118 (planned: add-to-cart blocked by MUS-QA-015). New fixture studio-design.png.</t>
+          <t>A failed run showed that Playwright's failure screenshot and error context capture every open page, the admin panel included - the suite promised they did not. Admin specs now turn screenshots and traces off, and the adminPage fixture refuses to start otherwise.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>Header and footer</t>
+          <t>Cases</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Nav items open a product menu instead of the category page (MS-V2-002 rewritten, MS-V2-035 updated); the footer was redesigned (MS-V2-001, 020, 039).</t>
+          <t>MS-ADM-016 (Move to Production) withdrawn. MS-ADM-006, 013, 014, 015, 017, 020, 022, 030 and 031 updated to the new flow; Business Rules and Glossary likewise.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>Copy and options</t>
+          <t>Defects</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>PVC 매트 is now 무광 화이트; sheet stickers show a discount on every tier (MS-V2-052 rewritten); rounded-roll, rounded-sheet and transfer H1s renamed back; production's category cards reverted to pre-rename names (MUS-QA-016).</t>
+          <t>MUS-QA-004 and MUS-QA-007 retested as fixed. MUS-QA-001 still reproduces for the printing and shipping entries. New: MUS-QA-010 and MUS-QA-011 (Low, to confirm).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>Suite fixes</t>
+          <t>Environments</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>selectSize waits for the size re-quote (stale tier prices failed the money-path tests); quantity tiers match the whole number (5 had been picking 50시트); category menu and review carousel clicks wait for Nuxt hydration (new waitForNuxtHydration); addToCart handles both the chooser and the older upload dialog (풀 컬러 레터링); the unused-preload warning is benign on every first-party host; new allowStudioModelLoadNoise guard option.</t>
+          <t>Instructions, gating, the Test Plan, Test Data and pricing ids now use the current environment names (static-1..8; development-1..4 retired and development-static/-static-2 renamed on 2026-09-25), and the CI schedule no longer lists the removed nightly regression. Historical "verified on development-N" notes are kept as they were.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>Seed orders</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Production replaced the vinyl-lettering and transfer-sticker tables on 2026-09-29 (ids 69 and 72; same rates on rungs 1-300, new rungs 500-5,000): CSVs re-exported, registry updated, now production-only baselines. The known interpolation overcharge checks are pinned to their quantities (the longer ladder had moved the sampled quantity off them and hidden that the overcharge is still live). Pricing now 2,288 tests.</t>
+          <t>Re-checked on 2026-10-14: AO-2609180004-dev had been used elsewhere and AO-2609070004/0005-dev have two items, so one unused candidate is left (AO-2609070006-dev).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="28" t="inlineStr">
         <is>
+          <t>Admin login</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>dev-static-1 has a tester OTP endpoint that returns the admin verification code; noted under MS-ADM-002 as a way to run admin cases without a person. Not used by the suite yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Storefront run</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Production-safe storefront specs (pricing excluded) before the updates: production 132 passed / 27 failed / 5 flaky; static-1 131 / 28 / 5. After: production 162 passed, 2 failed and 3 flaky (a tier-price repaint race, fixed and then 32/32 twice; transient 502s), 5 skipped; static-1 165 passed, 0 failed, 2 flaky (a network blip; MS-V2-035's timeout, now 90 s and passing on both), 5 skipped. Pricing on production: 261 of 2,286 failed, all on the replaced lettering and transfer tables; after the re-export 272/272 for those two and the other 2,016 unchanged and passing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>Order chooser</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>다음 단계 now opens 어떻게 주문하시겠어요? (with a file / in the studio / file later), live on production. MS-V2-050 and 053 updated; new MS-V2-115.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Design studio</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>New web studio (?studio=1): carries size and quantity over, prices 5% lower, refuses low-resolution designs. New MS-V2-116 and 117 (automated, production-safe) and MS-V2-118 (planned: add-to-cart blocked by MUS-QA-015). New fixture studio-design.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>Header and footer</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Nav items open a product menu instead of the category page (MS-V2-002 rewritten, MS-V2-035 updated); the footer was redesigned (MS-V2-001, 020, 039).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>Copy and options</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>PVC 매트 is now 무광 화이트; sheet stickers show a discount on every tier (MS-V2-052 rewritten); rounded-roll, rounded-sheet and transfer H1s renamed back; production's category cards reverted to pre-rename names (MUS-QA-016).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>Suite fixes</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>selectSize waits for the size re-quote (stale tier prices failed the money-path tests); quantity tiers match the whole number (5 had been picking 50시트); category menu and review carousel clicks wait for Nuxt hydration (new waitForNuxtHydration); addToCart handles both the chooser and the older upload dialog (풀 컬러 레터링); the unused-preload warning is benign on every first-party host; new allowStudioModelLoadNoise guard option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Production replaced the vinyl-lettering and transfer-sticker tables on 2026-09-29 (ids 69 and 72; same rates on rungs 1-300, new rungs 500-5,000): CSVs re-exported, registry updated, now production-only baselines. The known interpolation overcharge checks are pinned to their quantities (the longer ladder had moved the sampled quantity off them and hidden that the overcharge is still live). Pricing now 2,288 tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
           <t>Storefront defects</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>MUS-QA-012 to 020 logged (search button name, /dev/ assets on production, page weight, studio confirmation lock, pre-rename names, English FAQ on static-1, size-range mismatch, selection state not exposed, lettering 500-rung rate).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>2026-09-25 - workbook v1, suite reorganised</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Workbook</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>This workbook replaces test-case.md as the test case source. Steps and expected results were re-derived from the spec code (the code is the source of truth); where test-case.md described more than the code checks, the case says so in Reference Notes, and three cases are marked Partial (MS-V2-012, 017, 018).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Admin panel</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Added the admin panel to the suite: MS-ADM-001 (storefront-to-admin order processing: design upload, rejection and resubmission, pass, proof, customer approval, production, printing, shipping, delivery) plus planned admin cases (MS-ADM-002 onward).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Folders</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Specs moved to tests/e2e/storefront/&lt;area&gt;/ and tests/e2e/admin/&lt;area&gt;/; page objects to tests/pom/storefront/ and tests/pom/admin/. Same 2,468 tests before and after (verified by comparing the test lists).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Docs</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>New docs/RUNNING.md, docs/ARCHITECTURE.md, docs/CONVENTIONS.md; README.md is now a short entry point.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Defects</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Nine defects/questions from exploratory testing logged (MUS-QA-001 to 009).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>KNOWN SUITE ISSUES (not product defects)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>dev-static-1 checkout</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Cloudflare check before payment blocks automated browsers; guest checkout there shows no OTP popup on email blur. MS-V2-025 is verified on development-3 only.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Upload dialog (dev-static-1)</t>
+          <t>Workbook</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>The product upload dialog button is now 파일로 주문하기 and the file-type copy reads 'ai · psd · pdf · eps · tif · png · jpg'. ProductV2Page.expectDesignUploadModal and MS-V2-053 will fail when this reaches production - update storefront-data.ts then.</t>
+          <t>This workbook replaces test-case.md as the test case source. Steps and expected results were re-derived from the spec code (the code is the source of truth); where test-case.md described more than the code checks, the case says so in Reference Notes, and three cases are marked Partial (MS-V2-012, 017, 018).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>MS-V2-058</t>
+          <t>Admin panel</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Marked test.fixme (known alt-text defect on the size guide); skipped until fixed.</t>
+          <t>Added the admin panel to the suite: MS-ADM-001 (storefront-to-admin order processing: design upload, rejection and resubmission, pass, proof, customer approval, production, printing, shipping, delivery) plus planned admin cases (MS-ADM-002 onward).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Folders</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Specs moved to tests/e2e/storefront/&lt;area&gt;/ and tests/e2e/admin/&lt;area&gt;/; page objects to tests/pom/storefront/ and tests/pom/admin/. Same 2,468 tests before and after (verified by comparing the test lists).</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10 - test-case.md v1</t>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Docs</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>New docs/RUNNING.md, docs/ARCHITECTURE.md, docs/CONVENTIONS.md; README.md is now a short entry point.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>Defects</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Nine defects/questions from exploratory testing logged (MUS-QA-001 to 009).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>KNOWN SUITE ISSUES (not product defects)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>dev-static-1 checkout</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Cloudflare check before payment blocks automated browsers; guest checkout there shows no OTP popup on email blur. MS-V2-025 is verified on development-3 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Upload dialog (dev-static-1)</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>The product upload dialog button is now 파일로 주문하기 and the file-type copy reads 'ai · psd · pdf · eps · tif · png · jpg'. ProductV2Page.expectDesignUploadModal and MS-V2-053 will fail when this reaches production - update storefront-data.ts then.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>MS-V2-058</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Marked test.fixme (known alt-text defect on the size guide); skipped until fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 - test-case.md v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Storefront v2 test case matrix (MS-V2-001 onward) and automation standards, now carried by this workbook and docs/CONVENTIONS.md.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>2026-10-23 - testing tiers</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Added 5 API cases (8 total), stronger metadata contracts, 5-case critical UI selection, API/PR gate/deployment/release tiers, and tested dev E2E preflight. Destructive toggles removed from generic manual workflow.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>2026-10-23 - dev-2 regression audit</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Recorded desktop baseline, focused replays, Firefox/WebKit critical checks and mobile initial/recheck. Corrected checkout feedback selector and redundant footer/mobile navigation; added sanitized diagnostics and optional JSON reporting. Logged MUS-QA-022 to 024; five existing CFG-015 fixmes remain unverified.</t>
         </is>
